--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127303157</v>
+        <v>127300985</v>
       </c>
       <c r="B2" t="n">
         <v>57657</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581900</v>
+        <v>582154</v>
       </c>
       <c r="R2" t="n">
-        <v>6957106</v>
+        <v>6956940</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Både färska och äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127300985</v>
+        <v>127303157</v>
       </c>
       <c r="B3" t="n">
         <v>57657</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582154</v>
+        <v>581900</v>
       </c>
       <c r="R3" t="n">
-        <v>6956940</v>
+        <v>6957106</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Både färska och äldre ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>127299551</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>127302308</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127300124</v>
+        <v>127299890</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,39 +1312,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582206</v>
+        <v>582226</v>
       </c>
       <c r="R8" t="n">
-        <v>6956758</v>
+        <v>6956692</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,11 +1372,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,45 +1398,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299754</v>
+        <v>127300097</v>
       </c>
       <c r="B9" t="n">
-        <v>98353</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582249</v>
+        <v>582206</v>
       </c>
       <c r="R9" t="n">
-        <v>6956701</v>
+        <v>6956758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,45 +1499,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127299890</v>
+        <v>127300854</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582226</v>
+        <v>582162</v>
       </c>
       <c r="R10" t="n">
-        <v>6956692</v>
+        <v>6956952</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,6 +1579,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,37 +1610,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127300097</v>
+        <v>127299838</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1677,6 +1686,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1917,54 +1931,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127300854</v>
+        <v>127299754</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582162</v>
+        <v>582249</v>
       </c>
       <c r="R14" t="n">
-        <v>6956952</v>
+        <v>6956701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,11 +2002,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127301182</v>
+        <v>127302377</v>
       </c>
       <c r="B15" t="n">
-        <v>91284</v>
+        <v>91621</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582156</v>
+        <v>581842</v>
       </c>
       <c r="R15" t="n">
-        <v>6957038</v>
+        <v>6957024</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2125,50 +2125,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127301633</v>
+        <v>127301182</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>91290</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582057</v>
+        <v>582156</v>
       </c>
       <c r="R16" t="n">
-        <v>6957055</v>
+        <v>6957038</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2201,11 +2196,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2232,32 +2222,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127302377</v>
+        <v>127302258</v>
       </c>
       <c r="B17" t="n">
-        <v>91615</v>
+        <v>98359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2267,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581842</v>
+        <v>581887</v>
       </c>
       <c r="R17" t="n">
-        <v>6957024</v>
+        <v>6956944</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2329,7 +2319,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127301388</v>
+        <v>127301633</v>
       </c>
       <c r="B18" t="n">
         <v>57657</v>
@@ -2369,10 +2359,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582136</v>
+        <v>582057</v>
       </c>
       <c r="R18" t="n">
-        <v>6957002</v>
+        <v>6957055</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2399,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2436,45 +2426,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127302258</v>
+        <v>127301388</v>
       </c>
       <c r="B19" t="n">
-        <v>98353</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581887</v>
+        <v>582136</v>
       </c>
       <c r="R19" t="n">
-        <v>6956944</v>
+        <v>6957002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2507,6 +2502,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,7 +2533,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127300573</v>
+        <v>127301650</v>
       </c>
       <c r="B20" t="n">
         <v>57657</v>
@@ -2569,17 +2569,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582225</v>
+        <v>582068</v>
       </c>
       <c r="R20" t="n">
-        <v>6956940</v>
+        <v>6957026</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2640,10 +2640,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127300032</v>
+        <v>127300573</v>
       </c>
       <c r="B21" t="n">
-        <v>91319</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,34 +2651,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582219</v>
+        <v>582225</v>
       </c>
       <c r="R21" t="n">
-        <v>6956755</v>
+        <v>6956940</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,6 +2716,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2737,38 +2747,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127301650</v>
+        <v>127302739</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2777,13 +2786,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582068</v>
+        <v>581843</v>
       </c>
       <c r="R22" t="n">
-        <v>6957026</v>
+        <v>6957061</v>
       </c>
       <c r="S22" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2813,11 +2822,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2844,45 +2848,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127302141</v>
+        <v>127300032</v>
       </c>
       <c r="B23" t="n">
-        <v>97314</v>
+        <v>91325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581925</v>
+        <v>582219</v>
       </c>
       <c r="R23" t="n">
-        <v>6957009</v>
+        <v>6956755</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,32 +2945,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127302739</v>
+        <v>127302871</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>97326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2980,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581843</v>
+        <v>581866</v>
       </c>
       <c r="R24" t="n">
-        <v>6957061</v>
+        <v>6957054</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3042,7 +3046,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127302871</v>
+        <v>127302141</v>
       </c>
       <c r="B25" t="n">
         <v>97320</v>
@@ -3053,16 +3057,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3070,21 +3074,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581866</v>
+        <v>581925</v>
       </c>
       <c r="R25" t="n">
-        <v>6957054</v>
+        <v>6957009</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,45 +3143,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127300730</v>
+        <v>127300382</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582186</v>
+        <v>582237</v>
       </c>
       <c r="R26" t="n">
-        <v>6956930</v>
+        <v>6956894</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3214,11 +3218,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3248,7 +3247,7 @@
         <v>127302555</v>
       </c>
       <c r="B27" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3342,49 +3341,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127300270</v>
+        <v>127300730</v>
       </c>
       <c r="B28" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582284</v>
+        <v>582186</v>
       </c>
       <c r="R28" t="n">
-        <v>6956848</v>
+        <v>6956930</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3417,6 +3412,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3443,49 +3443,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300382</v>
+        <v>127300070</v>
       </c>
       <c r="B29" t="n">
-        <v>98436</v>
+        <v>91325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582237</v>
+        <v>582196</v>
       </c>
       <c r="R29" t="n">
-        <v>6956894</v>
+        <v>6956710</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,6 +3514,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3544,45 +3545,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127300070</v>
+        <v>127300270</v>
       </c>
       <c r="B30" t="n">
-        <v>91319</v>
+        <v>98442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582196</v>
+        <v>582284</v>
       </c>
       <c r="R30" t="n">
-        <v>6956710</v>
+        <v>6956848</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,11 +3620,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3646,45 +3646,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127302334</v>
+        <v>127302187</v>
       </c>
       <c r="B31" t="n">
-        <v>91615</v>
+        <v>98442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581864</v>
+        <v>581887</v>
       </c>
       <c r="R31" t="n">
-        <v>6957010</v>
+        <v>6957012</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3743,10 +3747,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127302173</v>
+        <v>127302334</v>
       </c>
       <c r="B32" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3778,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581887</v>
+        <v>581864</v>
       </c>
       <c r="R32" t="n">
-        <v>6957012</v>
+        <v>6957010</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3840,39 +3844,35 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127302187</v>
+        <v>127302173</v>
       </c>
       <c r="B33" t="n">
-        <v>98436</v>
+        <v>91621</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
@@ -3944,7 +3944,7 @@
         <v>127302336</v>
       </c>
       <c r="B34" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>127300230</v>
       </c>
       <c r="B37" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127300073</v>
+        <v>127301350</v>
       </c>
       <c r="B38" t="n">
-        <v>91615</v>
+        <v>57657</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4369,34 +4369,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582196</v>
+        <v>582135</v>
       </c>
       <c r="R38" t="n">
-        <v>6956710</v>
+        <v>6957030</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4429,6 +4434,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4455,10 +4465,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127302387</v>
+        <v>127301261</v>
       </c>
       <c r="B39" t="n">
-        <v>91615</v>
+        <v>57657</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,34 +4476,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581850</v>
+        <v>582156</v>
       </c>
       <c r="R39" t="n">
-        <v>6957027</v>
+        <v>6957038</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4526,6 +4541,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4555,7 +4575,7 @@
         <v>127302275</v>
       </c>
       <c r="B40" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4649,10 +4669,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127301350</v>
+        <v>127302387</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>91621</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4660,39 +4680,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582135</v>
+        <v>581850</v>
       </c>
       <c r="R41" t="n">
-        <v>6957030</v>
+        <v>6957027</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4725,11 +4740,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4756,10 +4766,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127301261</v>
+        <v>127300073</v>
       </c>
       <c r="B42" t="n">
-        <v>57657</v>
+        <v>91621</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4767,39 +4777,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582156</v>
+        <v>582196</v>
       </c>
       <c r="R42" t="n">
-        <v>6957038</v>
+        <v>6956710</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4832,11 +4837,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4863,10 +4863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127302594</v>
+        <v>127299697</v>
       </c>
       <c r="B43" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,39 +4874,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581831</v>
+        <v>582264</v>
       </c>
       <c r="R43" t="n">
-        <v>6957049</v>
+        <v>6956698</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4939,11 +4934,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4970,10 +4960,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127299697</v>
+        <v>127300324</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4981,21 +4971,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5005,10 +4995,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582264</v>
+        <v>582237</v>
       </c>
       <c r="R44" t="n">
-        <v>6956698</v>
+        <v>6956894</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5041,6 +5031,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5067,7 +5062,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127300324</v>
+        <v>127302594</v>
       </c>
       <c r="B45" t="n">
         <v>57657</v>
@@ -5096,16 +5091,21 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582237</v>
+        <v>581831</v>
       </c>
       <c r="R45" t="n">
-        <v>6956894</v>
+        <v>6957049</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5172,7 +5172,7 @@
         <v>127303284</v>
       </c>
       <c r="B46" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5280,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127300916</v>
+        <v>127302103</v>
       </c>
       <c r="B47" t="n">
-        <v>91773</v>
+        <v>98442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5291,34 +5291,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>582172</v>
+        <v>581922</v>
       </c>
       <c r="R47" t="n">
-        <v>6956985</v>
+        <v>6957019</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,6 +5360,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5377,10 +5391,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127302103</v>
+        <v>127300916</v>
       </c>
       <c r="B48" t="n">
-        <v>98436</v>
+        <v>91779</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5388,43 +5402,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581922</v>
+        <v>582172</v>
       </c>
       <c r="R48" t="n">
-        <v>6957019</v>
+        <v>6956985</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5457,11 +5462,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5809,10 +5809,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127300633</v>
+        <v>127299666</v>
       </c>
       <c r="B52" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>582186</v>
+        <v>582264</v>
       </c>
       <c r="R52" t="n">
-        <v>6956930</v>
+        <v>6956698</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5884,11 +5884,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5915,52 +5910,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127302307</v>
+        <v>127301605</v>
       </c>
       <c r="B53" t="n">
-        <v>98353</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581865</v>
+        <v>582068</v>
       </c>
       <c r="R53" t="n">
-        <v>6956984</v>
+        <v>6957026</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6016,10 +6007,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127301605</v>
+        <v>127300188</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6047,17 +6038,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582068</v>
+        <v>582277</v>
       </c>
       <c r="R54" t="n">
-        <v>6957026</v>
+        <v>6956837</v>
       </c>
       <c r="S54" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6113,42 +6104,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127301471</v>
+        <v>127302307</v>
       </c>
       <c r="B55" t="n">
-        <v>98436</v>
+        <v>98359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6157,10 +6143,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582122</v>
+        <v>581865</v>
       </c>
       <c r="R55" t="n">
-        <v>6957012</v>
+        <v>6956984</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6193,11 +6179,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6224,10 +6205,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127299666</v>
+        <v>127300633</v>
       </c>
       <c r="B56" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6254,7 +6235,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6263,10 +6244,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582264</v>
+        <v>582186</v>
       </c>
       <c r="R56" t="n">
-        <v>6956698</v>
+        <v>6956930</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6299,6 +6280,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6325,45 +6311,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127300188</v>
+        <v>127301471</v>
       </c>
       <c r="B57" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>582277</v>
+        <v>582122</v>
       </c>
       <c r="R57" t="n">
-        <v>6956837</v>
+        <v>6957012</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6396,6 +6391,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6425,7 +6425,7 @@
         <v>127299508</v>
       </c>
       <c r="B58" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>127302082</v>
       </c>
       <c r="B59" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>127302257</v>
       </c>
       <c r="B60" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127302049</v>
+        <v>127299437</v>
       </c>
       <c r="B61" t="n">
         <v>57657</v>
@@ -6758,14 +6758,14 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581894</v>
+        <v>582322</v>
       </c>
       <c r="R61" t="n">
-        <v>6957012</v>
+        <v>6956708</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6829,7 +6829,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127302243</v>
+        <v>127302049</v>
       </c>
       <c r="B62" t="n">
         <v>57657</v>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581956</v>
+        <v>581894</v>
       </c>
       <c r="R62" t="n">
-        <v>6956930</v>
+        <v>6957012</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6936,45 +6936,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127299731</v>
+        <v>127302243</v>
       </c>
       <c r="B63" t="n">
-        <v>98353</v>
+        <v>57657</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582264</v>
+        <v>581956</v>
       </c>
       <c r="R63" t="n">
-        <v>6956698</v>
+        <v>6956930</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7007,6 +7012,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7033,50 +7043,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127299437</v>
+        <v>127299731</v>
       </c>
       <c r="B64" t="n">
-        <v>57657</v>
+        <v>98359</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582322</v>
+        <v>582264</v>
       </c>
       <c r="R64" t="n">
-        <v>6956708</v>
+        <v>6956698</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7109,11 +7114,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7140,10 +7140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127302544</v>
+        <v>127302060</v>
       </c>
       <c r="B65" t="n">
-        <v>91319</v>
+        <v>91621</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7151,21 +7151,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7175,10 +7175,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581837</v>
+        <v>581894</v>
       </c>
       <c r="R65" t="n">
-        <v>6957037</v>
+        <v>6957012</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7237,10 +7237,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127300173</v>
+        <v>127302544</v>
       </c>
       <c r="B66" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7248,39 +7248,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>582260</v>
+        <v>581837</v>
       </c>
       <c r="R66" t="n">
-        <v>6956842</v>
+        <v>6957037</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7313,11 +7308,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7344,10 +7334,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127302060</v>
+        <v>127300173</v>
       </c>
       <c r="B67" t="n">
-        <v>91615</v>
+        <v>57657</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7355,34 +7345,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581894</v>
+        <v>582260</v>
       </c>
       <c r="R67" t="n">
-        <v>6957012</v>
+        <v>6956842</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7415,6 +7410,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127302308</v>
+        <v>127302215</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,34 +1108,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581865</v>
+        <v>581908</v>
       </c>
       <c r="R6" t="n">
-        <v>6956984</v>
+        <v>6956967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,6 +1173,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127302215</v>
+        <v>127302308</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,39 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581908</v>
+        <v>581865</v>
       </c>
       <c r="R7" t="n">
-        <v>6956967</v>
+        <v>6956984</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1275,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299890</v>
+        <v>127303073</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,34 +1312,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582226</v>
+        <v>581907</v>
       </c>
       <c r="R8" t="n">
-        <v>6956692</v>
+        <v>6957060</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,6 +1377,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,37 +1408,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127300097</v>
+        <v>127300124</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1473,6 +1484,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,54 +1515,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127300854</v>
+        <v>127303143</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582162</v>
+        <v>581903</v>
       </c>
       <c r="R10" t="n">
-        <v>6956952</v>
+        <v>6957081</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,7 +1595,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
+          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299838</v>
+        <v>127299890</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1621,39 +1633,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582206</v>
+        <v>582226</v>
       </c>
       <c r="R11" t="n">
-        <v>6956758</v>
+        <v>6956692</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,11 +1693,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1717,50 +1719,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127303073</v>
+        <v>127300097</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581907</v>
+        <v>582206</v>
       </c>
       <c r="R12" t="n">
-        <v>6957060</v>
+        <v>6956758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,11 +1794,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,50 +1820,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127303143</v>
+        <v>127300854</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581903</v>
+        <v>582162</v>
       </c>
       <c r="R13" t="n">
-        <v>6957081</v>
+        <v>6956952</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2125,45 +2125,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127301182</v>
+        <v>127301633</v>
       </c>
       <c r="B16" t="n">
-        <v>91290</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582156</v>
+        <v>582057</v>
       </c>
       <c r="R16" t="n">
-        <v>6957038</v>
+        <v>6957055</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,6 +2201,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2222,45 +2232,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127302258</v>
+        <v>127301388</v>
       </c>
       <c r="B17" t="n">
-        <v>98359</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581887</v>
+        <v>582136</v>
       </c>
       <c r="R17" t="n">
-        <v>6956944</v>
+        <v>6957002</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,6 +2308,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,50 +2339,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127301633</v>
+        <v>127301182</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>91290</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582057</v>
+        <v>582156</v>
       </c>
       <c r="R18" t="n">
-        <v>6957055</v>
+        <v>6957038</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2395,11 +2410,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2426,50 +2436,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127301388</v>
+        <v>127302258</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>98359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582136</v>
+        <v>581887</v>
       </c>
       <c r="R19" t="n">
-        <v>6957002</v>
+        <v>6956944</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,11 +2507,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127301650</v>
+        <v>127300032</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,42 +2544,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582068</v>
+        <v>582219</v>
       </c>
       <c r="R20" t="n">
-        <v>6957026</v>
+        <v>6956755</v>
       </c>
       <c r="S20" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2609,11 +2604,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2640,7 +2630,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127300573</v>
+        <v>127301650</v>
       </c>
       <c r="B21" t="n">
         <v>57657</v>
@@ -2676,17 +2666,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582225</v>
+        <v>582068</v>
       </c>
       <c r="R21" t="n">
-        <v>6956940</v>
+        <v>6957026</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,7 +2710,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2747,49 +2737,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127302739</v>
+        <v>127300573</v>
       </c>
       <c r="B22" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581843</v>
+        <v>582225</v>
       </c>
       <c r="R22" t="n">
-        <v>6957061</v>
+        <v>6956940</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,6 +2813,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2848,45 +2844,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127300032</v>
+        <v>127302739</v>
       </c>
       <c r="B23" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582219</v>
+        <v>581843</v>
       </c>
       <c r="R23" t="n">
-        <v>6956755</v>
+        <v>6957061</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3143,49 +3143,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127300382</v>
+        <v>127300070</v>
       </c>
       <c r="B26" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582237</v>
+        <v>582196</v>
       </c>
       <c r="R26" t="n">
-        <v>6956894</v>
+        <v>6956710</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3218,6 +3214,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3443,45 +3444,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300070</v>
+        <v>127300382</v>
       </c>
       <c r="B29" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582196</v>
+        <v>582237</v>
       </c>
       <c r="R29" t="n">
-        <v>6956710</v>
+        <v>6956894</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3514,11 +3519,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3646,49 +3646,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127302187</v>
+        <v>127302336</v>
       </c>
       <c r="B31" t="n">
-        <v>98442</v>
+        <v>91621</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581887</v>
+        <v>581858</v>
       </c>
       <c r="R31" t="n">
-        <v>6957012</v>
+        <v>6957026</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3941,45 +3937,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127302336</v>
+        <v>127302187</v>
       </c>
       <c r="B34" t="n">
-        <v>91621</v>
+        <v>98442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581858</v>
+        <v>581887</v>
       </c>
       <c r="R34" t="n">
-        <v>6957026</v>
+        <v>6957012</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4572,32 +4572,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127302275</v>
+        <v>127302387</v>
       </c>
       <c r="B40" t="n">
-        <v>97320</v>
+        <v>91621</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581923</v>
+        <v>581850</v>
       </c>
       <c r="R40" t="n">
-        <v>6956949</v>
+        <v>6957027</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4669,7 +4669,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127302387</v>
+        <v>127300073</v>
       </c>
       <c r="B41" t="n">
         <v>91621</v>
@@ -4700,14 +4700,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581850</v>
+        <v>582196</v>
       </c>
       <c r="R41" t="n">
-        <v>6957027</v>
+        <v>6956710</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4766,45 +4766,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127300073</v>
+        <v>127302275</v>
       </c>
       <c r="B42" t="n">
-        <v>91621</v>
+        <v>97320</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582196</v>
+        <v>581923</v>
       </c>
       <c r="R42" t="n">
-        <v>6956710</v>
+        <v>6956949</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127299697</v>
+        <v>127300324</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582264</v>
+        <v>582237</v>
       </c>
       <c r="R43" t="n">
-        <v>6956698</v>
+        <v>6956894</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4934,6 +4934,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4960,10 +4965,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127300324</v>
+        <v>127299697</v>
       </c>
       <c r="B44" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4971,21 +4976,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4995,10 +5000,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582237</v>
+        <v>582264</v>
       </c>
       <c r="R44" t="n">
-        <v>6956894</v>
+        <v>6956698</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5031,11 +5036,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127303284</v>
+        <v>127300916</v>
       </c>
       <c r="B46" t="n">
-        <v>98442</v>
+        <v>91779</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5180,43 +5180,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581899</v>
+        <v>582172</v>
       </c>
       <c r="R46" t="n">
-        <v>6957139</v>
+        <v>6956985</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5249,11 +5240,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5280,42 +5266,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127302103</v>
+        <v>127301651</v>
       </c>
       <c r="B47" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5324,10 +5306,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581922</v>
+        <v>582042</v>
       </c>
       <c r="R47" t="n">
-        <v>6957019</v>
+        <v>6957055</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5364,7 +5346,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5391,10 +5373,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127300916</v>
+        <v>127303284</v>
       </c>
       <c r="B48" t="n">
-        <v>91779</v>
+        <v>98442</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5402,34 +5384,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>582172</v>
+        <v>581899</v>
       </c>
       <c r="R48" t="n">
-        <v>6956985</v>
+        <v>6957139</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5462,6 +5453,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5488,38 +5484,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127301651</v>
+        <v>127302103</v>
       </c>
       <c r="B49" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>582042</v>
+        <v>581922</v>
       </c>
       <c r="R49" t="n">
-        <v>6957055</v>
+        <v>6957019</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5809,52 +5809,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127299666</v>
+        <v>127301605</v>
       </c>
       <c r="B52" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>582264</v>
+        <v>582068</v>
       </c>
       <c r="R52" t="n">
-        <v>6956698</v>
+        <v>6957026</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5910,7 +5906,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127301605</v>
+        <v>127300188</v>
       </c>
       <c r="B53" t="n">
         <v>79014</v>
@@ -5941,17 +5937,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582068</v>
+        <v>582277</v>
       </c>
       <c r="R53" t="n">
-        <v>6957026</v>
+        <v>6956837</v>
       </c>
       <c r="S53" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6007,45 +6003,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127300188</v>
+        <v>127302307</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>98359</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582277</v>
+        <v>581865</v>
       </c>
       <c r="R54" t="n">
-        <v>6956837</v>
+        <v>6956984</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6104,49 +6104,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127302307</v>
+        <v>127300776</v>
       </c>
       <c r="B55" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581865</v>
+        <v>582186</v>
       </c>
       <c r="R55" t="n">
-        <v>6956984</v>
+        <v>6956930</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6179,6 +6184,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>16 av dom blommar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6205,7 +6215,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127300633</v>
+        <v>127299666</v>
       </c>
       <c r="B56" t="n">
         <v>98442</v>
@@ -6235,7 +6245,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6244,10 +6254,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582186</v>
+        <v>582264</v>
       </c>
       <c r="R56" t="n">
-        <v>6956930</v>
+        <v>6956698</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6280,11 +6290,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6422,45 +6427,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127299508</v>
+        <v>127302082</v>
       </c>
       <c r="B58" t="n">
-        <v>97320</v>
+        <v>91343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>582284</v>
+        <v>581890</v>
       </c>
       <c r="R58" t="n">
-        <v>6956732</v>
+        <v>6957003</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,45 +6524,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127302082</v>
+        <v>127299508</v>
       </c>
       <c r="B59" t="n">
-        <v>91343</v>
+        <v>97320</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581890</v>
+        <v>582284</v>
       </c>
       <c r="R59" t="n">
-        <v>6957003</v>
+        <v>6956732</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6722,7 +6727,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127299437</v>
+        <v>127302049</v>
       </c>
       <c r="B61" t="n">
         <v>57657</v>
@@ -6758,14 +6763,14 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>582322</v>
+        <v>581894</v>
       </c>
       <c r="R61" t="n">
-        <v>6956708</v>
+        <v>6957012</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6802,7 +6807,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6829,7 +6834,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127302049</v>
+        <v>127302243</v>
       </c>
       <c r="B62" t="n">
         <v>57657</v>
@@ -6869,10 +6874,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581894</v>
+        <v>581956</v>
       </c>
       <c r="R62" t="n">
-        <v>6957012</v>
+        <v>6956930</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6909,7 +6914,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6936,7 +6941,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127302243</v>
+        <v>127299437</v>
       </c>
       <c r="B63" t="n">
         <v>57657</v>
@@ -6972,14 +6977,14 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581956</v>
+        <v>582322</v>
       </c>
       <c r="R63" t="n">
-        <v>6956930</v>
+        <v>6956708</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7016,7 +7021,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -889,49 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299551</v>
+        <v>127302308</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582275</v>
+        <v>581865</v>
       </c>
       <c r="R4" t="n">
-        <v>6956695</v>
+        <v>6956984</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,50 +986,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127301930</v>
+        <v>127299551</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581958</v>
+        <v>582275</v>
       </c>
       <c r="R5" t="n">
-        <v>6957039</v>
+        <v>6956695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,11 +1061,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1087,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127302215</v>
+        <v>127301930</v>
       </c>
       <c r="B6" t="n">
         <v>57657</v>
@@ -1137,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581908</v>
+        <v>581958</v>
       </c>
       <c r="R6" t="n">
-        <v>6956967</v>
+        <v>6957039</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127302308</v>
+        <v>127302215</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1205,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581865</v>
+        <v>581908</v>
       </c>
       <c r="R7" t="n">
-        <v>6956984</v>
+        <v>6956967</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -3143,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127300070</v>
+        <v>127300730</v>
       </c>
       <c r="B26" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3154,21 +3154,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582196</v>
+        <v>582186</v>
       </c>
       <c r="R26" t="n">
-        <v>6956710</v>
+        <v>6956930</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ullticka på 2 lågor</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127300730</v>
+        <v>127300070</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582186</v>
+        <v>582196</v>
       </c>
       <c r="R28" t="n">
-        <v>6956930</v>
+        <v>6956710</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3646,45 +3646,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127302336</v>
+        <v>127302187</v>
       </c>
       <c r="B31" t="n">
-        <v>91621</v>
+        <v>98442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581858</v>
+        <v>581887</v>
       </c>
       <c r="R31" t="n">
-        <v>6957026</v>
+        <v>6957012</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3937,49 +3941,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127302187</v>
+        <v>127302336</v>
       </c>
       <c r="B34" t="n">
-        <v>98442</v>
+        <v>91621</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581887</v>
+        <v>581858</v>
       </c>
       <c r="R34" t="n">
-        <v>6957012</v>
+        <v>6957026</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5809,48 +5809,52 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127301605</v>
+        <v>127299666</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>582068</v>
+        <v>582264</v>
       </c>
       <c r="R52" t="n">
-        <v>6957026</v>
+        <v>6956698</v>
       </c>
       <c r="S52" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5906,45 +5910,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127300188</v>
+        <v>127301471</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582277</v>
+        <v>582122</v>
       </c>
       <c r="R53" t="n">
-        <v>6956837</v>
+        <v>6957012</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5977,6 +5990,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6003,49 +6021,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127302307</v>
+        <v>127300776</v>
       </c>
       <c r="B54" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581865</v>
+        <v>582186</v>
       </c>
       <c r="R54" t="n">
-        <v>6956984</v>
+        <v>6956930</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6078,6 +6101,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>16 av dom blommar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6104,57 +6132,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127300776</v>
+        <v>127301605</v>
       </c>
       <c r="B55" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582186</v>
+        <v>582068</v>
       </c>
       <c r="R55" t="n">
-        <v>6956930</v>
+        <v>6957026</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6184,11 +6203,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>16 av dom blommar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6215,49 +6229,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127299666</v>
+        <v>127300188</v>
       </c>
       <c r="B56" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582264</v>
+        <v>582277</v>
       </c>
       <c r="R56" t="n">
-        <v>6956698</v>
+        <v>6956837</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6316,42 +6326,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127301471</v>
+        <v>127302307</v>
       </c>
       <c r="B57" t="n">
-        <v>98442</v>
+        <v>98359</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6360,10 +6365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>582122</v>
+        <v>581865</v>
       </c>
       <c r="R57" t="n">
-        <v>6957012</v>
+        <v>6956984</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6396,11 +6401,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6427,45 +6427,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127302082</v>
+        <v>127299508</v>
       </c>
       <c r="B58" t="n">
-        <v>91343</v>
+        <v>97320</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581890</v>
+        <v>582284</v>
       </c>
       <c r="R58" t="n">
-        <v>6957003</v>
+        <v>6956732</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,45 +6524,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127299508</v>
+        <v>127302082</v>
       </c>
       <c r="B59" t="n">
-        <v>97320</v>
+        <v>91343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>582284</v>
+        <v>581890</v>
       </c>
       <c r="R59" t="n">
-        <v>6956732</v>
+        <v>6957003</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -889,45 +889,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127302308</v>
+        <v>127299551</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581865</v>
+        <v>582275</v>
       </c>
       <c r="R4" t="n">
-        <v>6956984</v>
+        <v>6956695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,49 +990,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299551</v>
+        <v>127301930</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582275</v>
+        <v>581958</v>
       </c>
       <c r="R5" t="n">
-        <v>6956695</v>
+        <v>6957039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127301930</v>
+        <v>127302215</v>
       </c>
       <c r="B6" t="n">
         <v>57657</v>
@@ -1127,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581958</v>
+        <v>581908</v>
       </c>
       <c r="R6" t="n">
-        <v>6957039</v>
+        <v>6956967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127302215</v>
+        <v>127302308</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,39 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581908</v>
+        <v>581865</v>
       </c>
       <c r="R7" t="n">
-        <v>6956967</v>
+        <v>6956984</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1275,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,50 +1301,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303073</v>
+        <v>127299754</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>98360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581907</v>
+        <v>582249</v>
       </c>
       <c r="R8" t="n">
-        <v>6957060</v>
+        <v>6956701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,11 +1372,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127300124</v>
+        <v>127299838</v>
       </c>
       <c r="B9" t="n">
         <v>57657</v>
@@ -1439,7 +1429,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1488,7 +1478,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,7 +1505,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127303143</v>
+        <v>127303073</v>
       </c>
       <c r="B10" t="n">
         <v>57657</v>
@@ -1546,7 +1536,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1555,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581903</v>
+        <v>581907</v>
       </c>
       <c r="R10" t="n">
-        <v>6957081</v>
+        <v>6957060</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1585,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299890</v>
+        <v>127303143</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,34 +1623,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582226</v>
+        <v>581903</v>
       </c>
       <c r="R11" t="n">
-        <v>6956692</v>
+        <v>6957081</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,6 +1688,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,7 +1722,7 @@
         <v>127300097</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,54 +1820,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127300854</v>
+        <v>127299890</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582162</v>
+        <v>582226</v>
       </c>
       <c r="R13" t="n">
-        <v>6956952</v>
+        <v>6956692</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,11 +1891,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1931,45 +1917,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299754</v>
+        <v>127300854</v>
       </c>
       <c r="B14" t="n">
-        <v>98359</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582249</v>
+        <v>582162</v>
       </c>
       <c r="R14" t="n">
-        <v>6956701</v>
+        <v>6956952</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,6 +1997,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,7 +2031,7 @@
         <v>127302377</v>
       </c>
       <c r="B15" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>127301182</v>
       </c>
       <c r="B18" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>127302258</v>
       </c>
       <c r="B19" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,45 +2533,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127300032</v>
+        <v>127302871</v>
       </c>
       <c r="B20" t="n">
-        <v>91325</v>
+        <v>97327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582219</v>
+        <v>581866</v>
       </c>
       <c r="R20" t="n">
-        <v>6956755</v>
+        <v>6957054</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2630,53 +2634,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127301650</v>
+        <v>127302141</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>97321</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582068</v>
+        <v>581925</v>
       </c>
       <c r="R21" t="n">
-        <v>6957026</v>
+        <v>6957009</v>
       </c>
       <c r="S21" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2706,11 +2705,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2844,49 +2838,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127302739</v>
+        <v>127300032</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581843</v>
+        <v>582219</v>
       </c>
       <c r="R23" t="n">
-        <v>6957061</v>
+        <v>6956755</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2945,37 +2935,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127302871</v>
+        <v>127301650</v>
       </c>
       <c r="B24" t="n">
-        <v>97326</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2984,13 +2975,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581866</v>
+        <v>582068</v>
       </c>
       <c r="R24" t="n">
-        <v>6957054</v>
+        <v>6957026</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3020,6 +3011,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3046,45 +3042,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127302141</v>
+        <v>127302739</v>
       </c>
       <c r="B25" t="n">
-        <v>97320</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581925</v>
+        <v>581843</v>
       </c>
       <c r="R25" t="n">
-        <v>6957009</v>
+        <v>6957061</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,45 +3143,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127300730</v>
+        <v>127300382</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582186</v>
+        <v>582237</v>
       </c>
       <c r="R26" t="n">
-        <v>6956930</v>
+        <v>6956894</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3214,11 +3218,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3248,7 +3247,7 @@
         <v>127302555</v>
       </c>
       <c r="B27" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3342,45 +3341,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127300070</v>
+        <v>127300270</v>
       </c>
       <c r="B28" t="n">
-        <v>91325</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582196</v>
+        <v>582284</v>
       </c>
       <c r="R28" t="n">
-        <v>6956710</v>
+        <v>6956848</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3413,11 +3416,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3444,49 +3442,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300382</v>
+        <v>127300070</v>
       </c>
       <c r="B29" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582237</v>
+        <v>582196</v>
       </c>
       <c r="R29" t="n">
-        <v>6956894</v>
+        <v>6956710</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3519,6 +3513,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3545,49 +3544,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127300270</v>
+        <v>127300730</v>
       </c>
       <c r="B30" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582284</v>
+        <v>582186</v>
       </c>
       <c r="R30" t="n">
-        <v>6956848</v>
+        <v>6956930</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3620,6 +3615,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3646,49 +3646,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127302187</v>
+        <v>127302334</v>
       </c>
       <c r="B31" t="n">
-        <v>98442</v>
+        <v>91622</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581887</v>
+        <v>581864</v>
       </c>
       <c r="R31" t="n">
-        <v>6957012</v>
+        <v>6957010</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3747,45 +3743,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127302334</v>
+        <v>127302187</v>
       </c>
       <c r="B32" t="n">
-        <v>91621</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581864</v>
+        <v>581887</v>
       </c>
       <c r="R32" t="n">
-        <v>6957010</v>
+        <v>6957012</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,7 +3847,7 @@
         <v>127302173</v>
       </c>
       <c r="B33" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>127302336</v>
       </c>
       <c r="B34" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127300496</v>
+        <v>127300820</v>
       </c>
       <c r="B35" t="n">
         <v>57657</v>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582255</v>
+        <v>582193</v>
       </c>
       <c r="R35" t="n">
-        <v>6956910</v>
+        <v>6956952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127300820</v>
+        <v>127300496</v>
       </c>
       <c r="B36" t="n">
         <v>57657</v>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582193</v>
+        <v>582255</v>
       </c>
       <c r="R36" t="n">
-        <v>6956952</v>
+        <v>6956910</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,7 +4255,7 @@
         <v>127300230</v>
       </c>
       <c r="B37" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127301350</v>
+        <v>127300073</v>
       </c>
       <c r="B38" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4369,39 +4369,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582135</v>
+        <v>582196</v>
       </c>
       <c r="R38" t="n">
-        <v>6957030</v>
+        <v>6956710</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,11 +4429,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4465,7 +4455,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127301261</v>
+        <v>127301350</v>
       </c>
       <c r="B39" t="n">
         <v>57657</v>
@@ -4505,10 +4495,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582156</v>
+        <v>582135</v>
       </c>
       <c r="R39" t="n">
-        <v>6957038</v>
+        <v>6957030</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4572,10 +4562,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127302387</v>
+        <v>127301261</v>
       </c>
       <c r="B40" t="n">
-        <v>91621</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4583,34 +4573,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581850</v>
+        <v>582156</v>
       </c>
       <c r="R40" t="n">
-        <v>6957027</v>
+        <v>6957038</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4643,6 +4638,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4669,10 +4669,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127300073</v>
+        <v>127302387</v>
       </c>
       <c r="B41" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4700,14 +4700,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582196</v>
+        <v>581850</v>
       </c>
       <c r="R41" t="n">
-        <v>6956710</v>
+        <v>6957027</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
         <v>127302275</v>
       </c>
       <c r="B42" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127300324</v>
+        <v>127299697</v>
       </c>
       <c r="B43" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582237</v>
+        <v>582264</v>
       </c>
       <c r="R43" t="n">
-        <v>6956894</v>
+        <v>6956698</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4934,11 +4934,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4965,10 +4960,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127299697</v>
+        <v>127300324</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4976,21 +4971,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5000,10 +4995,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582264</v>
+        <v>582237</v>
       </c>
       <c r="R44" t="n">
-        <v>6956698</v>
+        <v>6956894</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5036,6 +5031,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127300916</v>
+        <v>127302103</v>
       </c>
       <c r="B46" t="n">
-        <v>91779</v>
+        <v>98443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5180,34 +5180,43 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582172</v>
+        <v>581922</v>
       </c>
       <c r="R46" t="n">
-        <v>6956985</v>
+        <v>6957019</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5240,6 +5249,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5373,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127303284</v>
+        <v>127300916</v>
       </c>
       <c r="B48" t="n">
-        <v>98442</v>
+        <v>91780</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5384,43 +5398,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581899</v>
+        <v>582172</v>
       </c>
       <c r="R48" t="n">
-        <v>6957139</v>
+        <v>6956985</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5453,11 +5458,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5484,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127302103</v>
+        <v>127303284</v>
       </c>
       <c r="B49" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581922</v>
+        <v>581899</v>
       </c>
       <c r="R49" t="n">
-        <v>6957019</v>
+        <v>6957139</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
+          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5809,52 +5809,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127299666</v>
+        <v>127301605</v>
       </c>
       <c r="B52" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>582264</v>
+        <v>582068</v>
       </c>
       <c r="R52" t="n">
-        <v>6956698</v>
+        <v>6957026</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5910,54 +5906,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127301471</v>
+        <v>127300188</v>
       </c>
       <c r="B53" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582122</v>
+        <v>582277</v>
       </c>
       <c r="R53" t="n">
-        <v>6957012</v>
+        <v>6956837</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5990,11 +5977,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6021,10 +6003,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127300776</v>
+        <v>127299666</v>
       </c>
       <c r="B54" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6051,12 +6033,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6065,10 +6042,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582186</v>
+        <v>582264</v>
       </c>
       <c r="R54" t="n">
-        <v>6956930</v>
+        <v>6956698</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,11 +6078,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>16 av dom blommar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6132,48 +6104,52 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127301605</v>
+        <v>127302307</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582068</v>
+        <v>581865</v>
       </c>
       <c r="R55" t="n">
-        <v>6957026</v>
+        <v>6956984</v>
       </c>
       <c r="S55" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6229,45 +6205,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127300188</v>
+        <v>127300633</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582277</v>
+        <v>582186</v>
       </c>
       <c r="R56" t="n">
-        <v>6956837</v>
+        <v>6956930</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6300,6 +6280,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6326,37 +6311,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127302307</v>
+        <v>127301471</v>
       </c>
       <c r="B57" t="n">
-        <v>98359</v>
+        <v>98443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6365,10 +6355,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581865</v>
+        <v>582122</v>
       </c>
       <c r="R57" t="n">
-        <v>6956984</v>
+        <v>6957012</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6401,6 +6391,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6430,7 +6425,7 @@
         <v>127299508</v>
       </c>
       <c r="B58" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6527,7 +6522,7 @@
         <v>127302082</v>
       </c>
       <c r="B59" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6624,7 +6619,7 @@
         <v>127302257</v>
       </c>
       <c r="B60" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6727,7 +6722,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127302049</v>
+        <v>127299437</v>
       </c>
       <c r="B61" t="n">
         <v>57657</v>
@@ -6763,14 +6758,14 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581894</v>
+        <v>582322</v>
       </c>
       <c r="R61" t="n">
-        <v>6957012</v>
+        <v>6956708</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6807,7 +6802,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6834,7 +6829,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127302243</v>
+        <v>127302049</v>
       </c>
       <c r="B62" t="n">
         <v>57657</v>
@@ -6874,10 +6869,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581956</v>
+        <v>581894</v>
       </c>
       <c r="R62" t="n">
-        <v>6956930</v>
+        <v>6957012</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6914,7 +6909,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6941,7 +6936,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127299437</v>
+        <v>127302243</v>
       </c>
       <c r="B63" t="n">
         <v>57657</v>
@@ -6977,14 +6972,14 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582322</v>
+        <v>581956</v>
       </c>
       <c r="R63" t="n">
-        <v>6956708</v>
+        <v>6956930</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7021,7 +7016,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7051,7 +7046,7 @@
         <v>127299731</v>
       </c>
       <c r="B64" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7145,10 +7140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127302060</v>
+        <v>127300173</v>
       </c>
       <c r="B65" t="n">
-        <v>91621</v>
+        <v>57657</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7156,34 +7151,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581894</v>
+        <v>582260</v>
       </c>
       <c r="R65" t="n">
-        <v>6957012</v>
+        <v>6956842</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7216,6 +7216,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7242,10 +7247,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127302544</v>
+        <v>127300974</v>
       </c>
       <c r="B66" t="n">
-        <v>91325</v>
+        <v>57657</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7253,34 +7258,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581837</v>
+        <v>582172</v>
       </c>
       <c r="R66" t="n">
-        <v>6957037</v>
+        <v>6956985</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7313,6 +7323,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7339,10 +7354,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127300173</v>
+        <v>127302060</v>
       </c>
       <c r="B67" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7350,39 +7365,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>582260</v>
+        <v>581894</v>
       </c>
       <c r="R67" t="n">
-        <v>6956842</v>
+        <v>6957012</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7415,11 +7425,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7446,10 +7451,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127300974</v>
+        <v>127302544</v>
       </c>
       <c r="B68" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7457,39 +7462,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>582172</v>
+        <v>581837</v>
       </c>
       <c r="R68" t="n">
-        <v>6956985</v>
+        <v>6957037</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7522,11 +7522,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127301930</v>
+        <v>127302308</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,39 +1001,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581958</v>
+        <v>581865</v>
       </c>
       <c r="R5" t="n">
-        <v>6957039</v>
+        <v>6956984</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,11 +1061,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1087,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127302215</v>
+        <v>127301930</v>
       </c>
       <c r="B6" t="n">
         <v>57657</v>
@@ -1137,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581908</v>
+        <v>581958</v>
       </c>
       <c r="R6" t="n">
-        <v>6956967</v>
+        <v>6957039</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127302308</v>
+        <v>127302215</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1205,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581865</v>
+        <v>581908</v>
       </c>
       <c r="R7" t="n">
-        <v>6956984</v>
+        <v>6956967</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,45 +1301,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299754</v>
+        <v>127303073</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582249</v>
+        <v>581907</v>
       </c>
       <c r="R8" t="n">
-        <v>6956701</v>
+        <v>6957060</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,6 +1377,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,7 +1408,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299838</v>
+        <v>127300124</v>
       </c>
       <c r="B9" t="n">
         <v>57657</v>
@@ -1429,7 +1439,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1478,7 +1488,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,7 +1515,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127303073</v>
+        <v>127303143</v>
       </c>
       <c r="B10" t="n">
         <v>57657</v>
@@ -1536,7 +1546,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1545,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581907</v>
+        <v>581903</v>
       </c>
       <c r="R10" t="n">
-        <v>6957060</v>
+        <v>6957081</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,7 +1595,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,50 +1622,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127303143</v>
+        <v>127299754</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>98360</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581903</v>
+        <v>582249</v>
       </c>
       <c r="R11" t="n">
-        <v>6957081</v>
+        <v>6956701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,11 +1693,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,45 +1820,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299890</v>
+        <v>127300854</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582226</v>
+        <v>582162</v>
       </c>
       <c r="R13" t="n">
-        <v>6956692</v>
+        <v>6956952</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,6 +1900,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,54 +1931,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127300854</v>
+        <v>127299890</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582162</v>
+        <v>582226</v>
       </c>
       <c r="R14" t="n">
-        <v>6956952</v>
+        <v>6956692</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,11 +2002,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127302377</v>
+        <v>127301182</v>
       </c>
       <c r="B15" t="n">
-        <v>91622</v>
+        <v>91291</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581842</v>
+        <v>582156</v>
       </c>
       <c r="R15" t="n">
-        <v>6957024</v>
+        <v>6957038</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2125,50 +2125,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127301633</v>
+        <v>127302258</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>98360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582057</v>
+        <v>581887</v>
       </c>
       <c r="R16" t="n">
-        <v>6957055</v>
+        <v>6956944</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2201,11 +2196,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2232,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127301388</v>
+        <v>127302377</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2243,39 +2233,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582136</v>
+        <v>581842</v>
       </c>
       <c r="R17" t="n">
-        <v>6957002</v>
+        <v>6957024</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,11 +2293,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2339,45 +2319,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127301182</v>
+        <v>127301633</v>
       </c>
       <c r="B18" t="n">
-        <v>91291</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582156</v>
+        <v>582057</v>
       </c>
       <c r="R18" t="n">
-        <v>6957038</v>
+        <v>6957055</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,6 +2395,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2436,45 +2426,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127302258</v>
+        <v>127301388</v>
       </c>
       <c r="B19" t="n">
-        <v>98360</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581887</v>
+        <v>582136</v>
       </c>
       <c r="R19" t="n">
-        <v>6956944</v>
+        <v>6957002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2507,6 +2502,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,37 +2533,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127302871</v>
+        <v>127301650</v>
       </c>
       <c r="B20" t="n">
-        <v>97327</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2572,13 +2573,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581866</v>
+        <v>582068</v>
       </c>
       <c r="R20" t="n">
-        <v>6957054</v>
+        <v>6957026</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2608,6 +2609,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2634,45 +2640,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127302141</v>
+        <v>127302739</v>
       </c>
       <c r="B21" t="n">
-        <v>97321</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581925</v>
+        <v>581843</v>
       </c>
       <c r="R21" t="n">
-        <v>6957009</v>
+        <v>6957061</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2935,38 +2945,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127301650</v>
+        <v>127302871</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>97327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2975,13 +2984,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582068</v>
+        <v>581866</v>
       </c>
       <c r="R24" t="n">
-        <v>6957026</v>
+        <v>6957054</v>
       </c>
       <c r="S24" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3011,11 +3020,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3042,49 +3046,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127302739</v>
+        <v>127302141</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>97321</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581843</v>
+        <v>581925</v>
       </c>
       <c r="R25" t="n">
-        <v>6957061</v>
+        <v>6957009</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127300382</v>
+        <v>127300270</v>
       </c>
       <c r="B26" t="n">
         <v>98443</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582237</v>
+        <v>582284</v>
       </c>
       <c r="R26" t="n">
-        <v>6956894</v>
+        <v>6956848</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3244,45 +3244,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127302555</v>
+        <v>127300382</v>
       </c>
       <c r="B27" t="n">
-        <v>105478</v>
+        <v>98443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581837</v>
+        <v>582237</v>
       </c>
       <c r="R27" t="n">
-        <v>6957037</v>
+        <v>6956894</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,49 +3345,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127300270</v>
+        <v>127302555</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>105478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582284</v>
+        <v>581837</v>
       </c>
       <c r="R28" t="n">
-        <v>6956848</v>
+        <v>6957037</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300070</v>
+        <v>127300730</v>
       </c>
       <c r="B29" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3453,21 +3453,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582196</v>
+        <v>582186</v>
       </c>
       <c r="R29" t="n">
-        <v>6956710</v>
+        <v>6956930</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ullticka på 2 lågor</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127300730</v>
+        <v>127300070</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582186</v>
+        <v>582196</v>
       </c>
       <c r="R30" t="n">
-        <v>6956930</v>
+        <v>6956710</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4358,45 +4358,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127300073</v>
+        <v>127302275</v>
       </c>
       <c r="B38" t="n">
-        <v>91622</v>
+        <v>97321</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582196</v>
+        <v>581923</v>
       </c>
       <c r="R38" t="n">
-        <v>6956710</v>
+        <v>6956949</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127301350</v>
+        <v>127300073</v>
       </c>
       <c r="B39" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,39 +4466,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582135</v>
+        <v>582196</v>
       </c>
       <c r="R39" t="n">
-        <v>6957030</v>
+        <v>6956710</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4531,11 +4526,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4562,7 +4552,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127301261</v>
+        <v>127301350</v>
       </c>
       <c r="B40" t="n">
         <v>57657</v>
@@ -4602,10 +4592,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582156</v>
+        <v>582135</v>
       </c>
       <c r="R40" t="n">
-        <v>6957038</v>
+        <v>6957030</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4669,10 +4659,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127302387</v>
+        <v>127301261</v>
       </c>
       <c r="B41" t="n">
-        <v>91622</v>
+        <v>57657</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4680,34 +4670,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581850</v>
+        <v>582156</v>
       </c>
       <c r="R41" t="n">
-        <v>6957027</v>
+        <v>6957038</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4740,6 +4735,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4766,32 +4766,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127302275</v>
+        <v>127302387</v>
       </c>
       <c r="B42" t="n">
-        <v>97321</v>
+        <v>91622</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581923</v>
+        <v>581850</v>
       </c>
       <c r="R42" t="n">
-        <v>6956949</v>
+        <v>6957027</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127299697</v>
+        <v>127300324</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582264</v>
+        <v>582237</v>
       </c>
       <c r="R43" t="n">
-        <v>6956698</v>
+        <v>6956894</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4934,6 +4934,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4960,7 +4965,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127300324</v>
+        <v>127302594</v>
       </c>
       <c r="B44" t="n">
         <v>57657</v>
@@ -4989,16 +4994,21 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582237</v>
+        <v>581831</v>
       </c>
       <c r="R44" t="n">
-        <v>6956894</v>
+        <v>6957049</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5035,7 +5045,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5062,10 +5072,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127302594</v>
+        <v>127299697</v>
       </c>
       <c r="B45" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5073,39 +5083,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581831</v>
+        <v>582264</v>
       </c>
       <c r="R45" t="n">
-        <v>6957049</v>
+        <v>6956698</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5138,11 +5143,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127302308</v>
+        <v>127301930</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,34 +1001,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581865</v>
+        <v>581958</v>
       </c>
       <c r="R5" t="n">
-        <v>6956984</v>
+        <v>6957039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127301930</v>
+        <v>127302215</v>
       </c>
       <c r="B6" t="n">
         <v>57657</v>
@@ -1127,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581958</v>
+        <v>581908</v>
       </c>
       <c r="R6" t="n">
-        <v>6957039</v>
+        <v>6956967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127302215</v>
+        <v>127302308</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,39 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581908</v>
+        <v>581865</v>
       </c>
       <c r="R7" t="n">
-        <v>6956967</v>
+        <v>6956984</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1275,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1622,32 +1622,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299754</v>
+        <v>127299890</v>
       </c>
       <c r="B11" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582249</v>
+        <v>582226</v>
       </c>
       <c r="R11" t="n">
-        <v>6956701</v>
+        <v>6956692</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,49 +1719,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127300097</v>
+        <v>127299754</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582206</v>
+        <v>582249</v>
       </c>
       <c r="R12" t="n">
-        <v>6956758</v>
+        <v>6956701</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1816,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127300854</v>
+        <v>127300097</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -1850,12 +1846,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1864,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582162</v>
+        <v>582206</v>
       </c>
       <c r="R13" t="n">
-        <v>6956952</v>
+        <v>6956758</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,11 +1891,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1931,45 +1917,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299890</v>
+        <v>127300854</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582226</v>
+        <v>582162</v>
       </c>
       <c r="R14" t="n">
-        <v>6956692</v>
+        <v>6956952</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,6 +1997,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127301182</v>
+        <v>127302377</v>
       </c>
       <c r="B15" t="n">
-        <v>91291</v>
+        <v>91622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582156</v>
+        <v>581842</v>
       </c>
       <c r="R15" t="n">
-        <v>6957038</v>
+        <v>6957024</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2125,10 +2125,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127302258</v>
+        <v>127301182</v>
       </c>
       <c r="B16" t="n">
-        <v>98360</v>
+        <v>91291</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2136,21 +2136,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581887</v>
+        <v>582156</v>
       </c>
       <c r="R16" t="n">
-        <v>6956944</v>
+        <v>6957038</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127302377</v>
+        <v>127301633</v>
       </c>
       <c r="B17" t="n">
-        <v>91622</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2233,34 +2233,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581842</v>
+        <v>582057</v>
       </c>
       <c r="R17" t="n">
-        <v>6957024</v>
+        <v>6957055</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,6 +2298,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,7 +2329,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127301633</v>
+        <v>127301388</v>
       </c>
       <c r="B18" t="n">
         <v>57657</v>
@@ -2359,10 +2369,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582057</v>
+        <v>582136</v>
       </c>
       <c r="R18" t="n">
-        <v>6957055</v>
+        <v>6957002</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2399,7 +2409,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2426,50 +2436,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127301388</v>
+        <v>127302258</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>98360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582136</v>
+        <v>581887</v>
       </c>
       <c r="R19" t="n">
-        <v>6957002</v>
+        <v>6956944</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,11 +2507,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127301650</v>
+        <v>127300032</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,42 +2544,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582068</v>
+        <v>582219</v>
       </c>
       <c r="R20" t="n">
-        <v>6957026</v>
+        <v>6956755</v>
       </c>
       <c r="S20" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2609,11 +2604,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2741,7 +2731,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127300573</v>
+        <v>127301650</v>
       </c>
       <c r="B22" t="n">
         <v>57657</v>
@@ -2777,17 +2767,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582225</v>
+        <v>582068</v>
       </c>
       <c r="R22" t="n">
-        <v>6956940</v>
+        <v>6957026</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2821,7 +2811,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2848,10 +2838,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127300032</v>
+        <v>127300573</v>
       </c>
       <c r="B23" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,34 +2849,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582219</v>
+        <v>582225</v>
       </c>
       <c r="R23" t="n">
-        <v>6956755</v>
+        <v>6956940</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,6 +2914,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3143,49 +3143,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127300270</v>
+        <v>127300070</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582284</v>
+        <v>582196</v>
       </c>
       <c r="R26" t="n">
-        <v>6956848</v>
+        <v>6956710</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3218,6 +3214,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3244,49 +3245,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127300382</v>
+        <v>127300730</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582237</v>
+        <v>582186</v>
       </c>
       <c r="R27" t="n">
-        <v>6956894</v>
+        <v>6956930</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3319,6 +3316,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3345,45 +3347,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127302555</v>
+        <v>127300270</v>
       </c>
       <c r="B28" t="n">
-        <v>105478</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581837</v>
+        <v>582284</v>
       </c>
       <c r="R28" t="n">
-        <v>6957037</v>
+        <v>6956848</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,45 +3448,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300730</v>
+        <v>127300382</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582186</v>
+        <v>582237</v>
       </c>
       <c r="R29" t="n">
-        <v>6956930</v>
+        <v>6956894</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,11 +3523,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3544,45 +3549,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127300070</v>
+        <v>127302555</v>
       </c>
       <c r="B30" t="n">
-        <v>91326</v>
+        <v>105478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582196</v>
+        <v>581837</v>
       </c>
       <c r="R30" t="n">
-        <v>6956710</v>
+        <v>6957037</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,11 +3620,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3743,39 +3743,35 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127302187</v>
+        <v>127302173</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>91622</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
@@ -3844,7 +3840,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127302173</v>
+        <v>127302336</v>
       </c>
       <c r="B33" t="n">
         <v>91622</v>
@@ -3879,10 +3875,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581887</v>
+        <v>581858</v>
       </c>
       <c r="R33" t="n">
-        <v>6957012</v>
+        <v>6957026</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,45 +3937,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127302336</v>
+        <v>127302187</v>
       </c>
       <c r="B34" t="n">
-        <v>91622</v>
+        <v>98443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581858</v>
+        <v>581887</v>
       </c>
       <c r="R34" t="n">
-        <v>6957026</v>
+        <v>6957012</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4038,7 +4038,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127300820</v>
+        <v>127300496</v>
       </c>
       <c r="B35" t="n">
         <v>57657</v>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582193</v>
+        <v>582255</v>
       </c>
       <c r="R35" t="n">
-        <v>6956952</v>
+        <v>6956910</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127300496</v>
+        <v>127300820</v>
       </c>
       <c r="B36" t="n">
         <v>57657</v>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582255</v>
+        <v>582193</v>
       </c>
       <c r="R36" t="n">
-        <v>6956910</v>
+        <v>6956952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,32 +4358,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127302275</v>
+        <v>127302387</v>
       </c>
       <c r="B38" t="n">
-        <v>97321</v>
+        <v>91622</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581923</v>
+        <v>581850</v>
       </c>
       <c r="R38" t="n">
-        <v>6956949</v>
+        <v>6957027</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4766,32 +4766,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127302387</v>
+        <v>127302275</v>
       </c>
       <c r="B42" t="n">
-        <v>91622</v>
+        <v>97321</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581850</v>
+        <v>581923</v>
       </c>
       <c r="R42" t="n">
-        <v>6957027</v>
+        <v>6956949</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127300324</v>
+        <v>127299697</v>
       </c>
       <c r="B43" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582237</v>
+        <v>582264</v>
       </c>
       <c r="R43" t="n">
-        <v>6956894</v>
+        <v>6956698</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4934,11 +4934,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4965,7 +4960,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127302594</v>
+        <v>127300324</v>
       </c>
       <c r="B44" t="n">
         <v>57657</v>
@@ -4994,21 +4989,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581831</v>
+        <v>582237</v>
       </c>
       <c r="R44" t="n">
-        <v>6957049</v>
+        <v>6956894</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5045,7 +5035,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5072,10 +5062,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127299697</v>
+        <v>127302594</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,34 +5073,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582264</v>
+        <v>581831</v>
       </c>
       <c r="R45" t="n">
-        <v>6956698</v>
+        <v>6957049</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5143,6 +5138,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5169,42 +5169,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127302103</v>
+        <v>127301651</v>
       </c>
       <c r="B46" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5213,10 +5209,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581922</v>
+        <v>582042</v>
       </c>
       <c r="R46" t="n">
-        <v>6957019</v>
+        <v>6957055</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5253,7 +5249,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5280,38 +5276,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127301651</v>
+        <v>127303284</v>
       </c>
       <c r="B47" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5320,10 +5320,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>582042</v>
+        <v>581899</v>
       </c>
       <c r="R47" t="n">
-        <v>6957055</v>
+        <v>6957139</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5387,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127300916</v>
+        <v>127302103</v>
       </c>
       <c r="B48" t="n">
-        <v>91780</v>
+        <v>98443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5398,34 +5398,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>582172</v>
+        <v>581922</v>
       </c>
       <c r="R48" t="n">
-        <v>6956985</v>
+        <v>6957019</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5458,6 +5467,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5484,10 +5498,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127303284</v>
+        <v>127300916</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>91780</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5495,43 +5509,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581899</v>
+        <v>582172</v>
       </c>
       <c r="R49" t="n">
-        <v>6957139</v>
+        <v>6956985</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5564,11 +5569,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5906,45 +5906,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127300188</v>
+        <v>127301471</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582277</v>
+        <v>582122</v>
       </c>
       <c r="R53" t="n">
-        <v>6956837</v>
+        <v>6957012</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5977,6 +5986,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6003,7 +6017,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127299666</v>
+        <v>127300633</v>
       </c>
       <c r="B54" t="n">
         <v>98443</v>
@@ -6033,7 +6047,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6042,10 +6056,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582264</v>
+        <v>582186</v>
       </c>
       <c r="R54" t="n">
-        <v>6956698</v>
+        <v>6956930</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6078,6 +6092,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6104,49 +6123,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127302307</v>
+        <v>127299666</v>
       </c>
       <c r="B55" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581865</v>
+        <v>582264</v>
       </c>
       <c r="R55" t="n">
-        <v>6956984</v>
+        <v>6956698</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6205,49 +6224,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127300633</v>
+        <v>127300188</v>
       </c>
       <c r="B56" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582186</v>
+        <v>582277</v>
       </c>
       <c r="R56" t="n">
-        <v>6956930</v>
+        <v>6956837</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6280,11 +6295,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6311,42 +6321,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127301471</v>
+        <v>127302307</v>
       </c>
       <c r="B57" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6355,10 +6360,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>582122</v>
+        <v>581865</v>
       </c>
       <c r="R57" t="n">
-        <v>6957012</v>
+        <v>6956984</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6391,11 +6396,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6422,45 +6422,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127299508</v>
+        <v>127302082</v>
       </c>
       <c r="B58" t="n">
-        <v>97321</v>
+        <v>91344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>582284</v>
+        <v>581890</v>
       </c>
       <c r="R58" t="n">
-        <v>6956732</v>
+        <v>6957003</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,45 +6519,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127302082</v>
+        <v>127299508</v>
       </c>
       <c r="B59" t="n">
-        <v>91344</v>
+        <v>97321</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581890</v>
+        <v>582284</v>
       </c>
       <c r="R59" t="n">
-        <v>6957003</v>
+        <v>6956732</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6722,50 +6722,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127299437</v>
+        <v>127299731</v>
       </c>
       <c r="B61" t="n">
-        <v>57657</v>
+        <v>98360</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>582322</v>
+        <v>582264</v>
       </c>
       <c r="R61" t="n">
-        <v>6956708</v>
+        <v>6956698</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6798,11 +6793,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6829,7 +6819,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127302049</v>
+        <v>127299437</v>
       </c>
       <c r="B62" t="n">
         <v>57657</v>
@@ -6865,14 +6855,14 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581894</v>
+        <v>582322</v>
       </c>
       <c r="R62" t="n">
-        <v>6957012</v>
+        <v>6956708</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6909,7 +6899,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6936,7 +6926,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127302243</v>
+        <v>127302049</v>
       </c>
       <c r="B63" t="n">
         <v>57657</v>
@@ -6976,10 +6966,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581956</v>
+        <v>581894</v>
       </c>
       <c r="R63" t="n">
-        <v>6956930</v>
+        <v>6957012</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7016,7 +7006,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7043,45 +7033,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127299731</v>
+        <v>127302243</v>
       </c>
       <c r="B64" t="n">
-        <v>98360</v>
+        <v>57657</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582264</v>
+        <v>581956</v>
       </c>
       <c r="R64" t="n">
-        <v>6956698</v>
+        <v>6956930</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7114,6 +7109,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7140,10 +7140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127300173</v>
+        <v>127302544</v>
       </c>
       <c r="B65" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7151,39 +7151,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582260</v>
+        <v>581837</v>
       </c>
       <c r="R65" t="n">
-        <v>6956842</v>
+        <v>6957037</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7216,11 +7211,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7247,10 +7237,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127300974</v>
+        <v>127302060</v>
       </c>
       <c r="B66" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7258,39 +7248,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>582172</v>
+        <v>581894</v>
       </c>
       <c r="R66" t="n">
-        <v>6956985</v>
+        <v>6957012</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7323,11 +7308,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7354,10 +7334,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127302060</v>
+        <v>127300173</v>
       </c>
       <c r="B67" t="n">
-        <v>91622</v>
+        <v>57657</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7365,34 +7345,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581894</v>
+        <v>582260</v>
       </c>
       <c r="R67" t="n">
-        <v>6957012</v>
+        <v>6956842</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7425,6 +7410,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7451,10 +7441,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127302544</v>
+        <v>127300974</v>
       </c>
       <c r="B68" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7462,34 +7452,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581837</v>
+        <v>582172</v>
       </c>
       <c r="R68" t="n">
-        <v>6957037</v>
+        <v>6956985</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7522,6 +7517,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -889,49 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299551</v>
+        <v>127301930</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582275</v>
+        <v>581958</v>
       </c>
       <c r="R4" t="n">
-        <v>6956695</v>
+        <v>6957039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127301930</v>
+        <v>127302215</v>
       </c>
       <c r="B5" t="n">
         <v>57657</v>
@@ -1030,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581958</v>
+        <v>581908</v>
       </c>
       <c r="R5" t="n">
-        <v>6957039</v>
+        <v>6956967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,50 +1103,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127302215</v>
+        <v>127299551</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581908</v>
+        <v>582275</v>
       </c>
       <c r="R6" t="n">
-        <v>6956967</v>
+        <v>6956695</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,11 +1178,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,7 +1301,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303073</v>
+        <v>127299838</v>
       </c>
       <c r="B8" t="n">
         <v>57657</v>
@@ -1337,14 +1337,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581907</v>
+        <v>582206</v>
       </c>
       <c r="R8" t="n">
-        <v>6957060</v>
+        <v>6956758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,50 +1408,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127300124</v>
+        <v>127299754</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>98360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582206</v>
+        <v>582249</v>
       </c>
       <c r="R9" t="n">
-        <v>6956758</v>
+        <v>6956701</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,11 +1479,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,7 +1505,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127303143</v>
+        <v>127303073</v>
       </c>
       <c r="B10" t="n">
         <v>57657</v>
@@ -1546,7 +1536,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1555,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581903</v>
+        <v>581907</v>
       </c>
       <c r="R10" t="n">
-        <v>6957081</v>
+        <v>6957060</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1585,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299890</v>
+        <v>127303143</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,34 +1623,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582226</v>
+        <v>581903</v>
       </c>
       <c r="R11" t="n">
-        <v>6956692</v>
+        <v>6957081</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,6 +1688,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,45 +1719,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299754</v>
+        <v>127300097</v>
       </c>
       <c r="B12" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582249</v>
+        <v>582206</v>
       </c>
       <c r="R12" t="n">
-        <v>6956701</v>
+        <v>6956758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,7 +1820,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127300097</v>
+        <v>127300854</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -1846,7 +1850,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1855,10 +1864,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582206</v>
+        <v>582162</v>
       </c>
       <c r="R13" t="n">
-        <v>6956758</v>
+        <v>6956952</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,6 +1900,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,54 +1931,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127300854</v>
+        <v>127299890</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582162</v>
+        <v>582226</v>
       </c>
       <c r="R14" t="n">
-        <v>6956952</v>
+        <v>6956692</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,11 +2002,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2533,45 +2533,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127300032</v>
+        <v>127302739</v>
       </c>
       <c r="B20" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582219</v>
+        <v>581843</v>
       </c>
       <c r="R20" t="n">
-        <v>6956755</v>
+        <v>6957061</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2630,32 +2634,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127302739</v>
+        <v>127302871</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>97327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2669,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581843</v>
+        <v>581866</v>
       </c>
       <c r="R21" t="n">
-        <v>6957061</v>
+        <v>6957054</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2731,53 +2735,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127301650</v>
+        <v>127302141</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>97321</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582068</v>
+        <v>581925</v>
       </c>
       <c r="R22" t="n">
-        <v>6957026</v>
+        <v>6957009</v>
       </c>
       <c r="S22" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2807,11 +2806,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2838,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127300573</v>
+        <v>127300032</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2849,39 +2843,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582225</v>
+        <v>582219</v>
       </c>
       <c r="R23" t="n">
-        <v>6956940</v>
+        <v>6956755</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2914,11 +2903,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2945,49 +2929,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127302871</v>
+        <v>127300573</v>
       </c>
       <c r="B24" t="n">
-        <v>97327</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581866</v>
+        <v>582225</v>
       </c>
       <c r="R24" t="n">
-        <v>6957054</v>
+        <v>6956940</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3020,6 +3005,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3046,48 +3036,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127302141</v>
+        <v>127301650</v>
       </c>
       <c r="B25" t="n">
-        <v>97321</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581925</v>
+        <v>582068</v>
       </c>
       <c r="R25" t="n">
-        <v>6957009</v>
+        <v>6957026</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3117,6 +3112,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127303284</v>
+        <v>127300916</v>
       </c>
       <c r="B47" t="n">
-        <v>98443</v>
+        <v>91780</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5287,43 +5287,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581899</v>
+        <v>582172</v>
       </c>
       <c r="R47" t="n">
-        <v>6957139</v>
+        <v>6956985</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5356,11 +5347,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5387,7 +5373,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127302103</v>
+        <v>127303284</v>
       </c>
       <c r="B48" t="n">
         <v>98443</v>
@@ -5417,7 +5403,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5431,10 +5417,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581922</v>
+        <v>581899</v>
       </c>
       <c r="R48" t="n">
-        <v>6957019</v>
+        <v>6957139</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5471,7 +5457,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
+          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5498,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127300916</v>
+        <v>127302103</v>
       </c>
       <c r="B49" t="n">
-        <v>91780</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5509,34 +5495,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>582172</v>
+        <v>581922</v>
       </c>
       <c r="R49" t="n">
-        <v>6956985</v>
+        <v>6957019</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,6 +5564,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -1301,7 +1301,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299838</v>
+        <v>127303073</v>
       </c>
       <c r="B8" t="n">
         <v>57657</v>
@@ -1337,14 +1337,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582206</v>
+        <v>581907</v>
       </c>
       <c r="R8" t="n">
-        <v>6956758</v>
+        <v>6957060</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,45 +1408,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299754</v>
+        <v>127300124</v>
       </c>
       <c r="B9" t="n">
-        <v>98360</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582249</v>
+        <v>582206</v>
       </c>
       <c r="R9" t="n">
-        <v>6956701</v>
+        <v>6956758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,6 +1484,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,7 +1515,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127303073</v>
+        <v>127303143</v>
       </c>
       <c r="B10" t="n">
         <v>57657</v>
@@ -1536,7 +1546,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1545,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581907</v>
+        <v>581903</v>
       </c>
       <c r="R10" t="n">
-        <v>6957060</v>
+        <v>6957081</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,7 +1595,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127303143</v>
+        <v>127299890</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,39 +1633,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581903</v>
+        <v>582226</v>
       </c>
       <c r="R11" t="n">
-        <v>6957081</v>
+        <v>6956692</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,11 +1693,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,49 +1719,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127300097</v>
+        <v>127299754</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582206</v>
+        <v>582249</v>
       </c>
       <c r="R12" t="n">
-        <v>6956758</v>
+        <v>6956701</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1816,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127300854</v>
+        <v>127300097</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -1850,12 +1846,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1864,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582162</v>
+        <v>582206</v>
       </c>
       <c r="R13" t="n">
-        <v>6956952</v>
+        <v>6956758</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,11 +1891,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1931,45 +1917,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299890</v>
+        <v>127300854</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582226</v>
+        <v>582162</v>
       </c>
       <c r="R14" t="n">
-        <v>6956692</v>
+        <v>6956952</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,6 +1997,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -4863,10 +4863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127299697</v>
+        <v>127300324</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582264</v>
+        <v>582237</v>
       </c>
       <c r="R43" t="n">
-        <v>6956698</v>
+        <v>6956894</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4934,6 +4934,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4960,7 +4965,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127300324</v>
+        <v>127302594</v>
       </c>
       <c r="B44" t="n">
         <v>57657</v>
@@ -4989,16 +4994,21 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582237</v>
+        <v>581831</v>
       </c>
       <c r="R44" t="n">
-        <v>6956894</v>
+        <v>6957049</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5035,7 +5045,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5062,10 +5072,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127302594</v>
+        <v>127299697</v>
       </c>
       <c r="B45" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5073,39 +5083,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581831</v>
+        <v>582264</v>
       </c>
       <c r="R45" t="n">
-        <v>6957049</v>
+        <v>6956698</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5138,11 +5143,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5169,38 +5169,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127301651</v>
+        <v>127303284</v>
       </c>
       <c r="B46" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5209,10 +5213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582042</v>
+        <v>581899</v>
       </c>
       <c r="R46" t="n">
-        <v>6957055</v>
+        <v>6957139</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5249,7 +5253,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5276,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127300916</v>
+        <v>127302103</v>
       </c>
       <c r="B47" t="n">
-        <v>91780</v>
+        <v>98443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5287,34 +5291,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>582172</v>
+        <v>581922</v>
       </c>
       <c r="R47" t="n">
-        <v>6956985</v>
+        <v>6957019</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5347,6 +5360,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5373,42 +5391,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127303284</v>
+        <v>127301651</v>
       </c>
       <c r="B48" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5417,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581899</v>
+        <v>582042</v>
       </c>
       <c r="R48" t="n">
-        <v>6957139</v>
+        <v>6957055</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5457,7 +5471,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>10 blommar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5484,10 +5498,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127302103</v>
+        <v>127300916</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>91780</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5495,43 +5509,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581922</v>
+        <v>582172</v>
       </c>
       <c r="R49" t="n">
-        <v>6957019</v>
+        <v>6956985</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5564,11 +5569,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7140,10 +7140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127302544</v>
+        <v>127302060</v>
       </c>
       <c r="B65" t="n">
-        <v>91326</v>
+        <v>91622</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7151,21 +7151,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7175,10 +7175,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581837</v>
+        <v>581894</v>
       </c>
       <c r="R65" t="n">
-        <v>6957037</v>
+        <v>6957012</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7237,10 +7237,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127302060</v>
+        <v>127302544</v>
       </c>
       <c r="B66" t="n">
-        <v>91622</v>
+        <v>91326</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7248,21 +7248,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581894</v>
+        <v>581837</v>
       </c>
       <c r="R66" t="n">
-        <v>6957012</v>
+        <v>6957037</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127300985</v>
+        <v>127303157</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582154</v>
+        <v>581900</v>
       </c>
       <c r="R2" t="n">
-        <v>6956940</v>
+        <v>6957106</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Både färska och äldre ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127303157</v>
+        <v>127300985</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581900</v>
+        <v>582154</v>
       </c>
       <c r="R3" t="n">
-        <v>6957106</v>
+        <v>6956940</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Både färska och äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,50 +889,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127301930</v>
+        <v>127299551</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581958</v>
+        <v>582275</v>
       </c>
       <c r="R4" t="n">
-        <v>6957039</v>
+        <v>6956695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127302215</v>
+        <v>127302308</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1001,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581908</v>
+        <v>581865</v>
       </c>
       <c r="R5" t="n">
-        <v>6956967</v>
+        <v>6956984</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1061,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,49 +1087,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299551</v>
+        <v>127301930</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582275</v>
+        <v>581958</v>
       </c>
       <c r="R6" t="n">
-        <v>6956695</v>
+        <v>6957039</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,6 +1163,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127302308</v>
+        <v>127302215</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1205,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581865</v>
+        <v>581908</v>
       </c>
       <c r="R7" t="n">
-        <v>6956984</v>
+        <v>6956967</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,7 +1304,7 @@
         <v>127303073</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>127300124</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>127303143</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>127299890</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>127299754</v>
       </c>
       <c r="B12" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>127300097</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>127300854</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127302377</v>
+        <v>127301633</v>
       </c>
       <c r="B15" t="n">
-        <v>91622</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,34 +2039,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581842</v>
+        <v>582057</v>
       </c>
       <c r="R15" t="n">
-        <v>6957024</v>
+        <v>6957055</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,6 +2104,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2125,45 +2135,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127301182</v>
+        <v>127301388</v>
       </c>
       <c r="B16" t="n">
-        <v>91291</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582156</v>
+        <v>582136</v>
       </c>
       <c r="R16" t="n">
-        <v>6957038</v>
+        <v>6957002</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,6 +2211,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2222,10 +2242,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127301633</v>
+        <v>127302377</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>91626</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2233,39 +2253,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582057</v>
+        <v>581842</v>
       </c>
       <c r="R17" t="n">
-        <v>6957055</v>
+        <v>6957024</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,11 +2313,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2329,50 +2339,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127301388</v>
+        <v>127301182</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>91295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582136</v>
+        <v>582156</v>
       </c>
       <c r="R18" t="n">
-        <v>6957002</v>
+        <v>6957038</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2405,11 +2410,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,7 +2439,7 @@
         <v>127302258</v>
       </c>
       <c r="B19" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,32 +2533,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127302739</v>
+        <v>127302871</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>97331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581843</v>
+        <v>581866</v>
       </c>
       <c r="R20" t="n">
-        <v>6957061</v>
+        <v>6957054</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127302871</v>
+        <v>127302141</v>
       </c>
       <c r="B21" t="n">
-        <v>97327</v>
+        <v>97325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2645,16 +2645,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2662,21 +2662,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581866</v>
+        <v>581925</v>
       </c>
       <c r="R21" t="n">
-        <v>6957054</v>
+        <v>6957009</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,45 +2731,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127302141</v>
+        <v>127300032</v>
       </c>
       <c r="B22" t="n">
-        <v>97321</v>
+        <v>91330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581925</v>
+        <v>582219</v>
       </c>
       <c r="R22" t="n">
-        <v>6957009</v>
+        <v>6956755</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127300032</v>
+        <v>127300573</v>
       </c>
       <c r="B23" t="n">
-        <v>91326</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,34 +2839,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582219</v>
+        <v>582225</v>
       </c>
       <c r="R23" t="n">
-        <v>6956755</v>
+        <v>6956940</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,6 +2904,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2929,10 +2935,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127300573</v>
+        <v>127301650</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,17 +2971,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582225</v>
+        <v>582068</v>
       </c>
       <c r="R24" t="n">
-        <v>6956940</v>
+        <v>6957026</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3009,7 +3015,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3036,38 +3042,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127301650</v>
+        <v>127302739</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3076,13 +3081,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582068</v>
+        <v>581843</v>
       </c>
       <c r="R25" t="n">
-        <v>6957026</v>
+        <v>6957061</v>
       </c>
       <c r="S25" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3112,11 +3117,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3146,7 +3146,7 @@
         <v>127300070</v>
       </c>
       <c r="B26" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>127300730</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3347,49 +3347,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127300270</v>
+        <v>127302555</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>105484</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582284</v>
+        <v>581837</v>
       </c>
       <c r="R28" t="n">
-        <v>6956848</v>
+        <v>6957037</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3448,10 +3444,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300382</v>
+        <v>127300270</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3478,7 +3474,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3487,10 +3483,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582237</v>
+        <v>582284</v>
       </c>
       <c r="R29" t="n">
-        <v>6956894</v>
+        <v>6956848</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3549,45 +3545,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127302555</v>
+        <v>127300382</v>
       </c>
       <c r="B30" t="n">
-        <v>105478</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581837</v>
+        <v>582237</v>
       </c>
       <c r="R30" t="n">
-        <v>6957037</v>
+        <v>6956894</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3646,45 +3646,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127302334</v>
+        <v>127302187</v>
       </c>
       <c r="B31" t="n">
-        <v>91622</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581864</v>
+        <v>581887</v>
       </c>
       <c r="R31" t="n">
-        <v>6957010</v>
+        <v>6957012</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3743,10 +3747,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127302173</v>
+        <v>127302334</v>
       </c>
       <c r="B32" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3778,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581887</v>
+        <v>581864</v>
       </c>
       <c r="R32" t="n">
-        <v>6957012</v>
+        <v>6957010</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3840,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127302336</v>
+        <v>127302173</v>
       </c>
       <c r="B33" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3875,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581858</v>
+        <v>581887</v>
       </c>
       <c r="R33" t="n">
-        <v>6957026</v>
+        <v>6957012</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,49 +3941,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127302187</v>
+        <v>127302336</v>
       </c>
       <c r="B34" t="n">
-        <v>98443</v>
+        <v>91626</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581887</v>
+        <v>581858</v>
       </c>
       <c r="R34" t="n">
-        <v>6957012</v>
+        <v>6957026</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4038,10 +4038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127300496</v>
+        <v>127300820</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582255</v>
+        <v>582193</v>
       </c>
       <c r="R35" t="n">
-        <v>6956910</v>
+        <v>6956952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127300820</v>
+        <v>127300496</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582193</v>
+        <v>582255</v>
       </c>
       <c r="R36" t="n">
-        <v>6956952</v>
+        <v>6956910</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,7 +4255,7 @@
         <v>127300230</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>127302387</v>
       </c>
       <c r="B38" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>127300073</v>
       </c>
       <c r="B39" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4552,10 +4552,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127301350</v>
+        <v>127301261</v>
       </c>
       <c r="B40" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582135</v>
+        <v>582156</v>
       </c>
       <c r="R40" t="n">
-        <v>6957030</v>
+        <v>6957038</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4659,10 +4659,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127301261</v>
+        <v>127301350</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582156</v>
+        <v>582135</v>
       </c>
       <c r="R41" t="n">
-        <v>6957038</v>
+        <v>6957030</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
         <v>127302275</v>
       </c>
       <c r="B42" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127300324</v>
+        <v>127299697</v>
       </c>
       <c r="B43" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582237</v>
+        <v>582264</v>
       </c>
       <c r="R43" t="n">
-        <v>6956894</v>
+        <v>6956698</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4934,11 +4934,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4968,7 +4963,7 @@
         <v>127302594</v>
       </c>
       <c r="B44" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5072,10 +5067,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127299697</v>
+        <v>127300324</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,21 +5078,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5107,10 +5102,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582264</v>
+        <v>582237</v>
       </c>
       <c r="R45" t="n">
-        <v>6956698</v>
+        <v>6956894</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5143,6 +5138,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5172,7 +5172,7 @@
         <v>127303284</v>
       </c>
       <c r="B46" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>127302103</v>
       </c>
       <c r="B47" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5391,50 +5391,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127301651</v>
+        <v>127300916</v>
       </c>
       <c r="B48" t="n">
-        <v>57657</v>
+        <v>91784</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>582042</v>
+        <v>582172</v>
       </c>
       <c r="R48" t="n">
-        <v>6957055</v>
+        <v>6956985</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5467,11 +5462,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5498,45 +5488,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127300916</v>
+        <v>127301651</v>
       </c>
       <c r="B49" t="n">
-        <v>91780</v>
+        <v>57661</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>582172</v>
+        <v>582042</v>
       </c>
       <c r="R49" t="n">
-        <v>6956985</v>
+        <v>6957055</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,6 +5564,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5598,7 +5598,7 @@
         <v>127300716</v>
       </c>
       <c r="B50" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>127299940</v>
       </c>
       <c r="B51" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>127301605</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5906,54 +5906,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127301471</v>
+        <v>127300188</v>
       </c>
       <c r="B53" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582122</v>
+        <v>582277</v>
       </c>
       <c r="R53" t="n">
-        <v>6957012</v>
+        <v>6956837</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5986,11 +5977,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6017,10 +6003,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127300633</v>
+        <v>127299666</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6047,7 +6033,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6056,10 +6042,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582186</v>
+        <v>582264</v>
       </c>
       <c r="R54" t="n">
-        <v>6956930</v>
+        <v>6956698</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6092,11 +6078,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6123,10 +6104,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127299666</v>
+        <v>127300633</v>
       </c>
       <c r="B55" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6153,7 +6134,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6162,10 +6143,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582264</v>
+        <v>582186</v>
       </c>
       <c r="R55" t="n">
-        <v>6956698</v>
+        <v>6956930</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6198,6 +6179,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6224,45 +6210,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127300188</v>
+        <v>127301471</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582277</v>
+        <v>582122</v>
       </c>
       <c r="R56" t="n">
-        <v>6956837</v>
+        <v>6957012</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,6 +6290,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6324,7 +6324,7 @@
         <v>127302307</v>
       </c>
       <c r="B57" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>127302082</v>
       </c>
       <c r="B58" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>127299508</v>
       </c>
       <c r="B59" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>127302257</v>
       </c>
       <c r="B60" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>127299731</v>
       </c>
       <c r="B61" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>127299437</v>
       </c>
       <c r="B62" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6926,10 +6926,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127302049</v>
+        <v>127302243</v>
       </c>
       <c r="B63" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581894</v>
+        <v>581956</v>
       </c>
       <c r="R63" t="n">
-        <v>6957012</v>
+        <v>6956930</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7033,10 +7033,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127302243</v>
+        <v>127302049</v>
       </c>
       <c r="B64" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581956</v>
+        <v>581894</v>
       </c>
       <c r="R64" t="n">
-        <v>6956930</v>
+        <v>6957012</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7143,7 +7143,7 @@
         <v>127302060</v>
       </c>
       <c r="B65" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>127302544</v>
       </c>
       <c r="B66" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>127300173</v>
       </c>
       <c r="B67" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>127300974</v>
       </c>
       <c r="B68" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127303157</v>
+        <v>127300985</v>
       </c>
       <c r="B2" t="n">
         <v>57661</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581900</v>
+        <v>582154</v>
       </c>
       <c r="R2" t="n">
-        <v>6957106</v>
+        <v>6956940</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Både färska och äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127300985</v>
+        <v>127303157</v>
       </c>
       <c r="B3" t="n">
         <v>57661</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582154</v>
+        <v>581900</v>
       </c>
       <c r="R3" t="n">
-        <v>6956940</v>
+        <v>6957106</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Både färska och äldre ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127302308</v>
+        <v>127301930</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,34 +1001,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581865</v>
+        <v>581958</v>
       </c>
       <c r="R5" t="n">
-        <v>6956984</v>
+        <v>6957039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127301930</v>
+        <v>127302215</v>
       </c>
       <c r="B6" t="n">
         <v>57661</v>
@@ -1127,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581958</v>
+        <v>581908</v>
       </c>
       <c r="R6" t="n">
-        <v>6957039</v>
+        <v>6956967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127302215</v>
+        <v>127302308</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,39 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581908</v>
+        <v>581865</v>
       </c>
       <c r="R7" t="n">
-        <v>6956967</v>
+        <v>6956984</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1275,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,50 +1301,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303073</v>
+        <v>127299754</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581907</v>
+        <v>582249</v>
       </c>
       <c r="R8" t="n">
-        <v>6957060</v>
+        <v>6956701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,11 +1372,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127300124</v>
+        <v>127303073</v>
       </c>
       <c r="B9" t="n">
         <v>57661</v>
@@ -1439,19 +1429,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582206</v>
+        <v>581907</v>
       </c>
       <c r="R9" t="n">
-        <v>6956758</v>
+        <v>6957060</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1505,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127303143</v>
+        <v>127300124</v>
       </c>
       <c r="B10" t="n">
         <v>57661</v>
@@ -1551,14 +1541,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581903</v>
+        <v>582206</v>
       </c>
       <c r="R10" t="n">
-        <v>6957081</v>
+        <v>6956758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1585,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299890</v>
+        <v>127303143</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,34 +1623,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582226</v>
+        <v>581903</v>
       </c>
       <c r="R11" t="n">
-        <v>6956692</v>
+        <v>6957081</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,6 +1688,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,32 +1719,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299754</v>
+        <v>127299890</v>
       </c>
       <c r="B12" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582249</v>
+        <v>582226</v>
       </c>
       <c r="R12" t="n">
-        <v>6956701</v>
+        <v>6956692</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2028,50 +2028,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127301633</v>
+        <v>127302258</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582057</v>
+        <v>581887</v>
       </c>
       <c r="R15" t="n">
-        <v>6957055</v>
+        <v>6956944</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,11 +2099,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2135,50 +2125,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127301388</v>
+        <v>127301182</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>91295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582136</v>
+        <v>582156</v>
       </c>
       <c r="R16" t="n">
-        <v>6957002</v>
+        <v>6957038</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,11 +2196,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2242,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127302377</v>
+        <v>127301633</v>
       </c>
       <c r="B17" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2253,34 +2233,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581842</v>
+        <v>582057</v>
       </c>
       <c r="R17" t="n">
-        <v>6957024</v>
+        <v>6957055</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2313,6 +2298,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2339,45 +2329,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127301182</v>
+        <v>127301388</v>
       </c>
       <c r="B18" t="n">
-        <v>91295</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582156</v>
+        <v>582136</v>
       </c>
       <c r="R18" t="n">
-        <v>6957038</v>
+        <v>6957002</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,6 +2405,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2436,32 +2436,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127302258</v>
+        <v>127302377</v>
       </c>
       <c r="B19" t="n">
-        <v>98364</v>
+        <v>91626</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581887</v>
+        <v>581842</v>
       </c>
       <c r="R19" t="n">
-        <v>6956944</v>
+        <v>6957024</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2533,49 +2533,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127302871</v>
+        <v>127300032</v>
       </c>
       <c r="B20" t="n">
-        <v>97331</v>
+        <v>91330</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581866</v>
+        <v>582219</v>
       </c>
       <c r="R20" t="n">
-        <v>6957054</v>
+        <v>6956755</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,45 +2630,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127302141</v>
+        <v>127302739</v>
       </c>
       <c r="B21" t="n">
-        <v>97325</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581925</v>
+        <v>581843</v>
       </c>
       <c r="R21" t="n">
-        <v>6957009</v>
+        <v>6957061</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127300032</v>
+        <v>127301650</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,37 +2742,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582219</v>
+        <v>582068</v>
       </c>
       <c r="R22" t="n">
-        <v>6956755</v>
+        <v>6957026</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2802,6 +2807,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2935,38 +2945,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127301650</v>
+        <v>127302871</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>97331</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2975,13 +2984,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582068</v>
+        <v>581866</v>
       </c>
       <c r="R24" t="n">
-        <v>6957026</v>
+        <v>6957054</v>
       </c>
       <c r="S24" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3011,11 +3020,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3042,49 +3046,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127302739</v>
+        <v>127302141</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>97325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581843</v>
+        <v>581925</v>
       </c>
       <c r="R25" t="n">
-        <v>6957061</v>
+        <v>6957009</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300270</v>
+        <v>127300382</v>
       </c>
       <c r="B29" t="n">
         <v>98447</v>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582284</v>
+        <v>582237</v>
       </c>
       <c r="R29" t="n">
-        <v>6956848</v>
+        <v>6956894</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,7 +3545,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127300382</v>
+        <v>127300270</v>
       </c>
       <c r="B30" t="n">
         <v>98447</v>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582237</v>
+        <v>582284</v>
       </c>
       <c r="R30" t="n">
-        <v>6956894</v>
+        <v>6956848</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4038,7 +4038,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127300820</v>
+        <v>127300496</v>
       </c>
       <c r="B35" t="n">
         <v>57661</v>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582193</v>
+        <v>582255</v>
       </c>
       <c r="R35" t="n">
-        <v>6956952</v>
+        <v>6956910</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127300496</v>
+        <v>127300820</v>
       </c>
       <c r="B36" t="n">
         <v>57661</v>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582255</v>
+        <v>582193</v>
       </c>
       <c r="R36" t="n">
-        <v>6956910</v>
+        <v>6956952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127302387</v>
+        <v>127301350</v>
       </c>
       <c r="B38" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4369,34 +4369,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581850</v>
+        <v>582135</v>
       </c>
       <c r="R38" t="n">
-        <v>6957027</v>
+        <v>6957030</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4429,6 +4434,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4455,10 +4465,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127300073</v>
+        <v>127301261</v>
       </c>
       <c r="B39" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,34 +4476,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582196</v>
+        <v>582156</v>
       </c>
       <c r="R39" t="n">
-        <v>6956710</v>
+        <v>6957038</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4526,6 +4541,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4552,10 +4572,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127301261</v>
+        <v>127302387</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4563,39 +4583,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582156</v>
+        <v>581850</v>
       </c>
       <c r="R40" t="n">
-        <v>6957038</v>
+        <v>6957027</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4628,11 +4643,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4659,10 +4669,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127301350</v>
+        <v>127300073</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4670,39 +4680,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582135</v>
+        <v>582196</v>
       </c>
       <c r="R41" t="n">
-        <v>6957030</v>
+        <v>6956710</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4735,11 +4740,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4960,7 +4960,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127302594</v>
+        <v>127300324</v>
       </c>
       <c r="B44" t="n">
         <v>57661</v>
@@ -4989,21 +4989,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581831</v>
+        <v>582237</v>
       </c>
       <c r="R44" t="n">
-        <v>6957049</v>
+        <v>6956894</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5040,7 +5035,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5067,7 +5062,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127300324</v>
+        <v>127302594</v>
       </c>
       <c r="B45" t="n">
         <v>57661</v>
@@ -5096,16 +5091,21 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582237</v>
+        <v>581831</v>
       </c>
       <c r="R45" t="n">
-        <v>6956894</v>
+        <v>6957049</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5169,42 +5169,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127303284</v>
+        <v>127301651</v>
       </c>
       <c r="B46" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5213,10 +5209,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581899</v>
+        <v>582042</v>
       </c>
       <c r="R46" t="n">
-        <v>6957139</v>
+        <v>6957055</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5253,7 +5249,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>10 blommar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5280,10 +5276,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127302103</v>
+        <v>127300916</v>
       </c>
       <c r="B47" t="n">
-        <v>98447</v>
+        <v>91784</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5291,43 +5287,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581922</v>
+        <v>582172</v>
       </c>
       <c r="R47" t="n">
-        <v>6957019</v>
+        <v>6956985</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5360,11 +5347,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5391,10 +5373,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127300916</v>
+        <v>127303284</v>
       </c>
       <c r="B48" t="n">
-        <v>91784</v>
+        <v>98447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5402,34 +5384,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>582172</v>
+        <v>581899</v>
       </c>
       <c r="R48" t="n">
-        <v>6956985</v>
+        <v>6957139</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5462,6 +5453,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5488,38 +5484,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127301651</v>
+        <v>127302103</v>
       </c>
       <c r="B49" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>582042</v>
+        <v>581922</v>
       </c>
       <c r="R49" t="n">
-        <v>6957055</v>
+        <v>6957019</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5809,48 +5809,52 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127301605</v>
+        <v>127299666</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>582068</v>
+        <v>582264</v>
       </c>
       <c r="R52" t="n">
-        <v>6957026</v>
+        <v>6956698</v>
       </c>
       <c r="S52" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5906,45 +5910,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127300188</v>
+        <v>127300633</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582277</v>
+        <v>582186</v>
       </c>
       <c r="R53" t="n">
-        <v>6956837</v>
+        <v>6956930</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5977,6 +5985,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6003,7 +6016,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127299666</v>
+        <v>127301471</v>
       </c>
       <c r="B54" t="n">
         <v>98447</v>
@@ -6033,19 +6046,24 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582264</v>
+        <v>582122</v>
       </c>
       <c r="R54" t="n">
-        <v>6956698</v>
+        <v>6957012</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6078,6 +6096,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6104,52 +6127,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127300633</v>
+        <v>127301605</v>
       </c>
       <c r="B55" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582186</v>
+        <v>582068</v>
       </c>
       <c r="R55" t="n">
-        <v>6956930</v>
+        <v>6957026</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6179,11 +6198,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6210,54 +6224,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127301471</v>
+        <v>127300188</v>
       </c>
       <c r="B56" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582122</v>
+        <v>582277</v>
       </c>
       <c r="R56" t="n">
-        <v>6957012</v>
+        <v>6956837</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6290,11 +6295,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6422,45 +6422,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127302082</v>
+        <v>127299508</v>
       </c>
       <c r="B58" t="n">
-        <v>91348</v>
+        <v>97325</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581890</v>
+        <v>582284</v>
       </c>
       <c r="R58" t="n">
-        <v>6957003</v>
+        <v>6956732</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,45 +6519,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127299508</v>
+        <v>127302082</v>
       </c>
       <c r="B59" t="n">
-        <v>97325</v>
+        <v>91348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>582284</v>
+        <v>581890</v>
       </c>
       <c r="R59" t="n">
-        <v>6956732</v>
+        <v>6957003</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6722,45 +6722,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127299731</v>
+        <v>127299437</v>
       </c>
       <c r="B61" t="n">
-        <v>98364</v>
+        <v>57661</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>582264</v>
+        <v>582322</v>
       </c>
       <c r="R61" t="n">
-        <v>6956698</v>
+        <v>6956708</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6793,6 +6798,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6819,50 +6829,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127299437</v>
+        <v>127299731</v>
       </c>
       <c r="B62" t="n">
-        <v>57661</v>
+        <v>98364</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>582322</v>
+        <v>582264</v>
       </c>
       <c r="R62" t="n">
-        <v>6956708</v>
+        <v>6956698</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6895,11 +6900,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6926,7 +6926,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127302243</v>
+        <v>127302049</v>
       </c>
       <c r="B63" t="n">
         <v>57661</v>
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581956</v>
+        <v>581894</v>
       </c>
       <c r="R63" t="n">
-        <v>6956930</v>
+        <v>6957012</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7033,7 +7033,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127302049</v>
+        <v>127302243</v>
       </c>
       <c r="B64" t="n">
         <v>57661</v>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581894</v>
+        <v>581956</v>
       </c>
       <c r="R64" t="n">
-        <v>6957012</v>
+        <v>6956930</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7140,10 +7140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127302060</v>
+        <v>127300173</v>
       </c>
       <c r="B65" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7151,34 +7151,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581894</v>
+        <v>582260</v>
       </c>
       <c r="R65" t="n">
-        <v>6957012</v>
+        <v>6956842</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7211,6 +7216,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7237,10 +7247,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127302544</v>
+        <v>127300974</v>
       </c>
       <c r="B66" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7248,34 +7258,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581837</v>
+        <v>582172</v>
       </c>
       <c r="R66" t="n">
-        <v>6957037</v>
+        <v>6956985</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7308,6 +7323,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7334,10 +7354,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127300173</v>
+        <v>127302060</v>
       </c>
       <c r="B67" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7345,39 +7365,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>582260</v>
+        <v>581894</v>
       </c>
       <c r="R67" t="n">
-        <v>6956842</v>
+        <v>6957012</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7410,11 +7425,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7441,10 +7451,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127300974</v>
+        <v>127302544</v>
       </c>
       <c r="B68" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7452,39 +7462,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>582172</v>
+        <v>581837</v>
       </c>
       <c r="R68" t="n">
-        <v>6956985</v>
+        <v>6957037</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7517,11 +7522,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -1301,45 +1301,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299754</v>
+        <v>127300097</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582249</v>
+        <v>582206</v>
       </c>
       <c r="R8" t="n">
-        <v>6956701</v>
+        <v>6956758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,50 +1402,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303073</v>
+        <v>127300854</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581907</v>
+        <v>582162</v>
       </c>
       <c r="R9" t="n">
-        <v>6957060</v>
+        <v>6956952</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,7 +1486,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,7 +1513,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127300124</v>
+        <v>127299838</v>
       </c>
       <c r="B10" t="n">
         <v>57661</v>
@@ -1536,7 +1544,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1585,7 +1593,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,7 +1620,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127303143</v>
+        <v>127303073</v>
       </c>
       <c r="B11" t="n">
         <v>57661</v>
@@ -1643,7 +1651,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1652,10 +1660,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581903</v>
+        <v>581907</v>
       </c>
       <c r="R11" t="n">
-        <v>6957081</v>
+        <v>6957060</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,7 +1700,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299890</v>
+        <v>127303143</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,34 +1738,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582226</v>
+        <v>581903</v>
       </c>
       <c r="R12" t="n">
-        <v>6956692</v>
+        <v>6957081</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1790,6 +1803,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,49 +1834,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127300097</v>
+        <v>127299890</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582206</v>
+        <v>582226</v>
       </c>
       <c r="R13" t="n">
-        <v>6956758</v>
+        <v>6956692</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,54 +1931,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127300854</v>
+        <v>127299754</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582162</v>
+        <v>582249</v>
       </c>
       <c r="R14" t="n">
-        <v>6956952</v>
+        <v>6956701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,11 +2002,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2533,45 +2533,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127300032</v>
+        <v>127302739</v>
       </c>
       <c r="B20" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582219</v>
+        <v>581843</v>
       </c>
       <c r="R20" t="n">
-        <v>6956755</v>
+        <v>6957061</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2630,32 +2634,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127302739</v>
+        <v>127302871</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>97331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2669,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581843</v>
+        <v>581866</v>
       </c>
       <c r="R21" t="n">
-        <v>6957061</v>
+        <v>6957054</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2731,53 +2735,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127301650</v>
+        <v>127302141</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>97325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582068</v>
+        <v>581925</v>
       </c>
       <c r="R22" t="n">
-        <v>6957026</v>
+        <v>6957009</v>
       </c>
       <c r="S22" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2807,11 +2806,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2838,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127300573</v>
+        <v>127300032</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2849,39 +2843,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582225</v>
+        <v>582219</v>
       </c>
       <c r="R23" t="n">
-        <v>6956940</v>
+        <v>6956755</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2914,11 +2903,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2945,37 +2929,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127302871</v>
+        <v>127301650</v>
       </c>
       <c r="B24" t="n">
-        <v>97331</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2984,13 +2969,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581866</v>
+        <v>582068</v>
       </c>
       <c r="R24" t="n">
-        <v>6957054</v>
+        <v>6957026</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3020,6 +3005,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3046,45 +3036,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127302141</v>
+        <v>127300573</v>
       </c>
       <c r="B25" t="n">
-        <v>97325</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581925</v>
+        <v>582225</v>
       </c>
       <c r="R25" t="n">
-        <v>6957009</v>
+        <v>6956940</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,6 +3112,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -5169,38 +5169,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127301651</v>
+        <v>127303284</v>
       </c>
       <c r="B46" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5209,10 +5213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582042</v>
+        <v>581899</v>
       </c>
       <c r="R46" t="n">
-        <v>6957055</v>
+        <v>6957139</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5249,7 +5253,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5276,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127300916</v>
+        <v>127302103</v>
       </c>
       <c r="B47" t="n">
-        <v>91784</v>
+        <v>98447</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5287,34 +5291,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>582172</v>
+        <v>581922</v>
       </c>
       <c r="R47" t="n">
-        <v>6956985</v>
+        <v>6957019</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5347,6 +5360,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5373,42 +5391,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127303284</v>
+        <v>127301651</v>
       </c>
       <c r="B48" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5417,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581899</v>
+        <v>582042</v>
       </c>
       <c r="R48" t="n">
-        <v>6957139</v>
+        <v>6957055</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5457,7 +5471,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>10 blommar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5484,10 +5498,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127302103</v>
+        <v>127300916</v>
       </c>
       <c r="B49" t="n">
-        <v>98447</v>
+        <v>91784</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5495,43 +5509,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581922</v>
+        <v>582172</v>
       </c>
       <c r="R49" t="n">
-        <v>6957019</v>
+        <v>6956985</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5564,11 +5569,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5910,49 +5910,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127300633</v>
+        <v>127302307</v>
       </c>
       <c r="B53" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582186</v>
+        <v>581865</v>
       </c>
       <c r="R53" t="n">
-        <v>6956930</v>
+        <v>6956984</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5985,11 +5985,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6016,57 +6011,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127301471</v>
+        <v>127301605</v>
       </c>
       <c r="B54" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582122</v>
+        <v>582068</v>
       </c>
       <c r="R54" t="n">
-        <v>6957012</v>
+        <v>6957026</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6096,11 +6082,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6127,7 +6108,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127301605</v>
+        <v>127300188</v>
       </c>
       <c r="B55" t="n">
         <v>79018</v>
@@ -6158,17 +6139,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582068</v>
+        <v>582277</v>
       </c>
       <c r="R55" t="n">
-        <v>6957026</v>
+        <v>6956837</v>
       </c>
       <c r="S55" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6224,45 +6205,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127300188</v>
+        <v>127300633</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582277</v>
+        <v>582186</v>
       </c>
       <c r="R56" t="n">
-        <v>6956837</v>
+        <v>6956930</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,6 +6280,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6321,37 +6311,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127302307</v>
+        <v>127301471</v>
       </c>
       <c r="B57" t="n">
-        <v>98364</v>
+        <v>98447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6360,10 +6355,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581865</v>
+        <v>582122</v>
       </c>
       <c r="R57" t="n">
-        <v>6956984</v>
+        <v>6957012</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6396,6 +6391,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6422,45 +6422,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127299508</v>
+        <v>127302082</v>
       </c>
       <c r="B58" t="n">
-        <v>97325</v>
+        <v>91348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>582284</v>
+        <v>581890</v>
       </c>
       <c r="R58" t="n">
-        <v>6956732</v>
+        <v>6957003</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,45 +6519,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127302082</v>
+        <v>127299508</v>
       </c>
       <c r="B59" t="n">
-        <v>91348</v>
+        <v>97325</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581890</v>
+        <v>582284</v>
       </c>
       <c r="R59" t="n">
-        <v>6957003</v>
+        <v>6956732</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7140,10 +7140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127300173</v>
+        <v>127302544</v>
       </c>
       <c r="B65" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7151,39 +7151,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582260</v>
+        <v>581837</v>
       </c>
       <c r="R65" t="n">
-        <v>6956842</v>
+        <v>6957037</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7216,11 +7211,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7451,10 +7441,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127302544</v>
+        <v>127300173</v>
       </c>
       <c r="B68" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7462,34 +7452,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581837</v>
+        <v>582260</v>
       </c>
       <c r="R68" t="n">
-        <v>6957037</v>
+        <v>6956842</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7522,6 +7517,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -2533,49 +2533,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127302739</v>
+        <v>127300032</v>
       </c>
       <c r="B20" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581843</v>
+        <v>582219</v>
       </c>
       <c r="R20" t="n">
-        <v>6957061</v>
+        <v>6956755</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,32 +2630,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127302871</v>
+        <v>127302739</v>
       </c>
       <c r="B21" t="n">
-        <v>97331</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2673,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581866</v>
+        <v>581843</v>
       </c>
       <c r="R21" t="n">
-        <v>6957054</v>
+        <v>6957061</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,48 +2731,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127302141</v>
+        <v>127301650</v>
       </c>
       <c r="B22" t="n">
-        <v>97325</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581925</v>
+        <v>582068</v>
       </c>
       <c r="R22" t="n">
-        <v>6957009</v>
+        <v>6957026</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2806,6 +2807,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2832,10 +2838,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127300032</v>
+        <v>127300573</v>
       </c>
       <c r="B23" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,34 +2849,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582219</v>
+        <v>582225</v>
       </c>
       <c r="R23" t="n">
-        <v>6956755</v>
+        <v>6956940</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,6 +2914,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2929,38 +2945,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127301650</v>
+        <v>127302871</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>97331</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2969,13 +2984,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582068</v>
+        <v>581866</v>
       </c>
       <c r="R24" t="n">
-        <v>6957026</v>
+        <v>6957054</v>
       </c>
       <c r="S24" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3005,11 +3020,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3036,50 +3046,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127300573</v>
+        <v>127302141</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>97325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582225</v>
+        <v>581925</v>
       </c>
       <c r="R25" t="n">
-        <v>6956940</v>
+        <v>6957009</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3112,11 +3117,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3143,45 +3143,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127300070</v>
+        <v>127302555</v>
       </c>
       <c r="B26" t="n">
-        <v>91330</v>
+        <v>105484</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582196</v>
+        <v>581837</v>
       </c>
       <c r="R26" t="n">
-        <v>6956710</v>
+        <v>6957037</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3214,11 +3214,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3245,45 +3240,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127300730</v>
+        <v>127300270</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582186</v>
+        <v>582284</v>
       </c>
       <c r="R27" t="n">
-        <v>6956930</v>
+        <v>6956848</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3316,11 +3315,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3347,45 +3341,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127302555</v>
+        <v>127300382</v>
       </c>
       <c r="B28" t="n">
-        <v>105484</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581837</v>
+        <v>582237</v>
       </c>
       <c r="R28" t="n">
-        <v>6957037</v>
+        <v>6956894</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,49 +3442,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300382</v>
+        <v>127300070</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582237</v>
+        <v>582196</v>
       </c>
       <c r="R29" t="n">
-        <v>6956894</v>
+        <v>6956710</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3519,6 +3513,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3545,49 +3544,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127300270</v>
+        <v>127300730</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582284</v>
+        <v>582186</v>
       </c>
       <c r="R30" t="n">
-        <v>6956848</v>
+        <v>6956930</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3620,6 +3615,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5169,42 +5169,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127303284</v>
+        <v>127301651</v>
       </c>
       <c r="B46" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5213,10 +5209,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581899</v>
+        <v>582042</v>
       </c>
       <c r="R46" t="n">
-        <v>6957139</v>
+        <v>6957055</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5253,7 +5249,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>10 blommar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5280,10 +5276,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127302103</v>
+        <v>127300916</v>
       </c>
       <c r="B47" t="n">
-        <v>98447</v>
+        <v>91784</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5291,43 +5287,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581922</v>
+        <v>582172</v>
       </c>
       <c r="R47" t="n">
-        <v>6957019</v>
+        <v>6956985</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5360,11 +5347,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5391,38 +5373,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127301651</v>
+        <v>127303284</v>
       </c>
       <c r="B48" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5431,10 +5417,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>582042</v>
+        <v>581899</v>
       </c>
       <c r="R48" t="n">
-        <v>6957055</v>
+        <v>6957139</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5471,7 +5457,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5498,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127300916</v>
+        <v>127302103</v>
       </c>
       <c r="B49" t="n">
-        <v>91784</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5509,34 +5495,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>582172</v>
+        <v>581922</v>
       </c>
       <c r="R49" t="n">
-        <v>6956985</v>
+        <v>6957019</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,6 +5564,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -889,49 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299551</v>
+        <v>127302308</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582275</v>
+        <v>581865</v>
       </c>
       <c r="R4" t="n">
-        <v>6956695</v>
+        <v>6956984</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1204,45 +1200,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127302308</v>
+        <v>127299551</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581865</v>
+        <v>582275</v>
       </c>
       <c r="R7" t="n">
-        <v>6956984</v>
+        <v>6956695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,37 +1301,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127300097</v>
+        <v>127299838</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1376,6 +1377,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,54 +1408,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127300854</v>
+        <v>127299890</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582162</v>
+        <v>582226</v>
       </c>
       <c r="R9" t="n">
-        <v>6956952</v>
+        <v>6956692</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,11 +1479,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,50 +1505,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127299838</v>
+        <v>127299754</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>98365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582206</v>
+        <v>582249</v>
       </c>
       <c r="R10" t="n">
-        <v>6956758</v>
+        <v>6956701</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,11 +1576,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1834,45 +1816,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299890</v>
+        <v>127300097</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582226</v>
+        <v>582206</v>
       </c>
       <c r="R13" t="n">
-        <v>6956692</v>
+        <v>6956758</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,45 +1917,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299754</v>
+        <v>127300854</v>
       </c>
       <c r="B14" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582249</v>
+        <v>582162</v>
       </c>
       <c r="R14" t="n">
-        <v>6956701</v>
+        <v>6956952</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,6 +1997,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,7 +2031,7 @@
         <v>127302258</v>
       </c>
       <c r="B15" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,45 +2125,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127301182</v>
+        <v>127301633</v>
       </c>
       <c r="B16" t="n">
-        <v>91295</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582156</v>
+        <v>582057</v>
       </c>
       <c r="R16" t="n">
-        <v>6957038</v>
+        <v>6957055</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,6 +2201,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2222,7 +2232,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127301633</v>
+        <v>127301388</v>
       </c>
       <c r="B17" t="n">
         <v>57661</v>
@@ -2262,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582057</v>
+        <v>582136</v>
       </c>
       <c r="R17" t="n">
-        <v>6957055</v>
+        <v>6957002</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,7 +2312,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2329,10 +2339,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127301388</v>
+        <v>127302377</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,39 +2350,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582136</v>
+        <v>581842</v>
       </c>
       <c r="R18" t="n">
-        <v>6957002</v>
+        <v>6957024</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2405,11 +2410,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2436,32 +2436,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127302377</v>
+        <v>127301182</v>
       </c>
       <c r="B19" t="n">
-        <v>91626</v>
+        <v>91295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581842</v>
+        <v>582156</v>
       </c>
       <c r="R19" t="n">
-        <v>6957024</v>
+        <v>6957038</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2630,37 +2630,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127302739</v>
+        <v>127301650</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2669,13 +2670,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581843</v>
+        <v>582068</v>
       </c>
       <c r="R21" t="n">
-        <v>6957061</v>
+        <v>6957026</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2705,6 +2706,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2731,7 +2737,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127301650</v>
+        <v>127300573</v>
       </c>
       <c r="B22" t="n">
         <v>57661</v>
@@ -2767,17 +2773,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582068</v>
+        <v>582225</v>
       </c>
       <c r="R22" t="n">
-        <v>6957026</v>
+        <v>6956940</v>
       </c>
       <c r="S22" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2811,7 +2817,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2838,50 +2844,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127300573</v>
+        <v>127302739</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582225</v>
+        <v>581843</v>
       </c>
       <c r="R23" t="n">
-        <v>6956940</v>
+        <v>6957061</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2914,11 +2919,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3143,45 +3143,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127302555</v>
+        <v>127300730</v>
       </c>
       <c r="B26" t="n">
-        <v>105484</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581837</v>
+        <v>582186</v>
       </c>
       <c r="R26" t="n">
-        <v>6957037</v>
+        <v>6956930</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3214,6 +3214,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3240,49 +3245,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127300270</v>
+        <v>127302555</v>
       </c>
       <c r="B27" t="n">
-        <v>98447</v>
+        <v>105486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582284</v>
+        <v>581837</v>
       </c>
       <c r="R27" t="n">
-        <v>6956848</v>
+        <v>6957037</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,49 +3342,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127300382</v>
+        <v>127300070</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582237</v>
+        <v>582196</v>
       </c>
       <c r="R28" t="n">
-        <v>6956894</v>
+        <v>6956710</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,6 +3413,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3442,45 +3444,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300070</v>
+        <v>127300270</v>
       </c>
       <c r="B29" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582196</v>
+        <v>582284</v>
       </c>
       <c r="R29" t="n">
-        <v>6956710</v>
+        <v>6956848</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,11 +3519,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3544,45 +3545,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127300730</v>
+        <v>127300382</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582186</v>
+        <v>582237</v>
       </c>
       <c r="R30" t="n">
-        <v>6956930</v>
+        <v>6956894</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,11 +3620,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3646,49 +3646,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127302187</v>
+        <v>127302334</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>91626</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581887</v>
+        <v>581864</v>
       </c>
       <c r="R31" t="n">
-        <v>6957012</v>
+        <v>6957010</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3747,7 +3743,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127302334</v>
+        <v>127302173</v>
       </c>
       <c r="B32" t="n">
         <v>91626</v>
@@ -3782,10 +3778,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581864</v>
+        <v>581887</v>
       </c>
       <c r="R32" t="n">
-        <v>6957010</v>
+        <v>6957012</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,7 +3840,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127302173</v>
+        <v>127302336</v>
       </c>
       <c r="B33" t="n">
         <v>91626</v>
@@ -3879,10 +3875,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581887</v>
+        <v>581858</v>
       </c>
       <c r="R33" t="n">
-        <v>6957012</v>
+        <v>6957026</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,45 +3937,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127302336</v>
+        <v>127302187</v>
       </c>
       <c r="B34" t="n">
-        <v>91626</v>
+        <v>98448</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581858</v>
+        <v>581887</v>
       </c>
       <c r="R34" t="n">
-        <v>6957026</v>
+        <v>6957012</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4255,7 +4255,7 @@
         <v>127300230</v>
       </c>
       <c r="B37" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127301350</v>
+        <v>127302387</v>
       </c>
       <c r="B38" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4369,39 +4369,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582135</v>
+        <v>581850</v>
       </c>
       <c r="R38" t="n">
-        <v>6957030</v>
+        <v>6957027</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,11 +4429,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4465,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127301261</v>
+        <v>127300073</v>
       </c>
       <c r="B39" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4476,39 +4466,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582156</v>
+        <v>582196</v>
       </c>
       <c r="R39" t="n">
-        <v>6957038</v>
+        <v>6956710</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4541,11 +4526,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4572,10 +4552,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127302387</v>
+        <v>127301350</v>
       </c>
       <c r="B40" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4583,34 +4563,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581850</v>
+        <v>582135</v>
       </c>
       <c r="R40" t="n">
-        <v>6957027</v>
+        <v>6957030</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4643,6 +4628,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4669,10 +4659,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127300073</v>
+        <v>127301261</v>
       </c>
       <c r="B41" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4680,34 +4670,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582196</v>
+        <v>582156</v>
       </c>
       <c r="R41" t="n">
-        <v>6956710</v>
+        <v>6957038</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4740,6 +4735,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5169,38 +5169,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127301651</v>
+        <v>127303284</v>
       </c>
       <c r="B46" t="n">
-        <v>57661</v>
+        <v>98448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5209,10 +5213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582042</v>
+        <v>581899</v>
       </c>
       <c r="R46" t="n">
-        <v>6957055</v>
+        <v>6957139</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5249,7 +5253,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5276,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127300916</v>
+        <v>127302103</v>
       </c>
       <c r="B47" t="n">
-        <v>91784</v>
+        <v>98448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5287,34 +5291,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>582172</v>
+        <v>581922</v>
       </c>
       <c r="R47" t="n">
-        <v>6956985</v>
+        <v>6957019</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5347,6 +5360,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5373,10 +5391,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127303284</v>
+        <v>127300916</v>
       </c>
       <c r="B48" t="n">
-        <v>98447</v>
+        <v>91784</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5384,43 +5402,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581899</v>
+        <v>582172</v>
       </c>
       <c r="R48" t="n">
-        <v>6957139</v>
+        <v>6956985</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5453,11 +5462,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5484,42 +5488,38 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127302103</v>
+        <v>127301651</v>
       </c>
       <c r="B49" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581922</v>
+        <v>582042</v>
       </c>
       <c r="R49" t="n">
-        <v>6957019</v>
+        <v>6957055</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5812,7 +5812,7 @@
         <v>127299666</v>
       </c>
       <c r="B52" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5910,52 +5910,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127302307</v>
+        <v>127301605</v>
       </c>
       <c r="B53" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581865</v>
+        <v>582068</v>
       </c>
       <c r="R53" t="n">
-        <v>6956984</v>
+        <v>6957026</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6011,7 +6007,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127301605</v>
+        <v>127300188</v>
       </c>
       <c r="B54" t="n">
         <v>79018</v>
@@ -6042,17 +6038,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582068</v>
+        <v>582277</v>
       </c>
       <c r="R54" t="n">
-        <v>6957026</v>
+        <v>6956837</v>
       </c>
       <c r="S54" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6108,45 +6104,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127300188</v>
+        <v>127300776</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582277</v>
+        <v>582186</v>
       </c>
       <c r="R55" t="n">
-        <v>6956837</v>
+        <v>6956930</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6179,6 +6184,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>16 av dom blommar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6205,49 +6215,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127300633</v>
+        <v>127302307</v>
       </c>
       <c r="B56" t="n">
-        <v>98447</v>
+        <v>98365</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582186</v>
+        <v>581865</v>
       </c>
       <c r="R56" t="n">
-        <v>6956930</v>
+        <v>6956984</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6280,11 +6290,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6314,7 +6319,7 @@
         <v>127301471</v>
       </c>
       <c r="B57" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6422,45 +6427,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127302082</v>
+        <v>127299508</v>
       </c>
       <c r="B58" t="n">
-        <v>91348</v>
+        <v>97325</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581890</v>
+        <v>582284</v>
       </c>
       <c r="R58" t="n">
-        <v>6957003</v>
+        <v>6956732</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,45 +6524,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127299508</v>
+        <v>127302082</v>
       </c>
       <c r="B59" t="n">
-        <v>97325</v>
+        <v>91348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>582284</v>
+        <v>581890</v>
       </c>
       <c r="R59" t="n">
-        <v>6956732</v>
+        <v>6957003</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6832,7 +6837,7 @@
         <v>127299731</v>
       </c>
       <c r="B62" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7237,7 +7242,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127300974</v>
+        <v>127300173</v>
       </c>
       <c r="B66" t="n">
         <v>57661</v>
@@ -7268,19 +7273,19 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>582172</v>
+        <v>582260</v>
       </c>
       <c r="R66" t="n">
-        <v>6956985</v>
+        <v>6956842</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7344,10 +7349,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127302060</v>
+        <v>127300974</v>
       </c>
       <c r="B67" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7355,34 +7360,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581894</v>
+        <v>582172</v>
       </c>
       <c r="R67" t="n">
-        <v>6957012</v>
+        <v>6956985</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7415,6 +7425,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7441,10 +7456,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127300173</v>
+        <v>127302060</v>
       </c>
       <c r="B68" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7452,39 +7467,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>582260</v>
+        <v>581894</v>
       </c>
       <c r="R68" t="n">
-        <v>6956842</v>
+        <v>6957012</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7517,11 +7527,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127302258</v>
+        <v>127302377</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>91626</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581887</v>
+        <v>581842</v>
       </c>
       <c r="R15" t="n">
-        <v>6956944</v>
+        <v>6957024</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2339,32 +2339,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127302377</v>
+        <v>127301182</v>
       </c>
       <c r="B18" t="n">
-        <v>91626</v>
+        <v>91295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581842</v>
+        <v>582156</v>
       </c>
       <c r="R18" t="n">
-        <v>6957024</v>
+        <v>6957038</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127301182</v>
+        <v>127302258</v>
       </c>
       <c r="B19" t="n">
-        <v>91295</v>
+        <v>98365</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582156</v>
+        <v>581887</v>
       </c>
       <c r="R19" t="n">
-        <v>6957038</v>
+        <v>6956944</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -6727,50 +6727,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127299437</v>
+        <v>127299731</v>
       </c>
       <c r="B61" t="n">
-        <v>57661</v>
+        <v>98365</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>582322</v>
+        <v>582264</v>
       </c>
       <c r="R61" t="n">
-        <v>6956708</v>
+        <v>6956698</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6803,11 +6798,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6834,45 +6824,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127299731</v>
+        <v>127302049</v>
       </c>
       <c r="B62" t="n">
-        <v>98365</v>
+        <v>57661</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>582264</v>
+        <v>581894</v>
       </c>
       <c r="R62" t="n">
-        <v>6956698</v>
+        <v>6957012</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6905,6 +6900,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6931,7 +6931,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127302049</v>
+        <v>127302243</v>
       </c>
       <c r="B63" t="n">
         <v>57661</v>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581894</v>
+        <v>581956</v>
       </c>
       <c r="R63" t="n">
-        <v>6957012</v>
+        <v>6956930</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7038,7 +7038,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127302243</v>
+        <v>127299437</v>
       </c>
       <c r="B64" t="n">
         <v>57661</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581956</v>
+        <v>582322</v>
       </c>
       <c r="R64" t="n">
-        <v>6956930</v>
+        <v>6956708</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7551,6 +7551,107 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127728746</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91160</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6020</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Oljetagging</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Sistotrema raduloides</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Donk</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Bjärtbergsbäcken, Brattlandsåsen, Sillre, Mpd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>582190</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6956712</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127300985</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127303157</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,45 +889,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127302308</v>
+        <v>127299551</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581865</v>
+        <v>582275</v>
       </c>
       <c r="R4" t="n">
-        <v>6956984</v>
+        <v>6956695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127301930</v>
+        <v>127302308</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,39 +1001,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581958</v>
+        <v>581865</v>
       </c>
       <c r="R5" t="n">
-        <v>6957039</v>
+        <v>6956984</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1061,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127302215</v>
+        <v>127301930</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581908</v>
+        <v>581958</v>
       </c>
       <c r="R6" t="n">
-        <v>6956967</v>
+        <v>6957039</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,49 +1194,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299551</v>
+        <v>127302215</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582275</v>
+        <v>581908</v>
       </c>
       <c r="R7" t="n">
-        <v>6956695</v>
+        <v>6956967</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,50 +1301,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299838</v>
+        <v>127299754</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>98367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582206</v>
+        <v>582249</v>
       </c>
       <c r="R8" t="n">
-        <v>6956758</v>
+        <v>6956701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,11 +1372,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299890</v>
+        <v>127303073</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,34 +1409,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582226</v>
+        <v>581907</v>
       </c>
       <c r="R9" t="n">
-        <v>6956692</v>
+        <v>6957060</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,6 +1474,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,45 +1505,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127299754</v>
+        <v>127300124</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582249</v>
+        <v>582206</v>
       </c>
       <c r="R10" t="n">
-        <v>6956701</v>
+        <v>6956758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,6 +1581,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127303073</v>
+        <v>127303143</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,7 +1643,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1642,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581907</v>
+        <v>581903</v>
       </c>
       <c r="R11" t="n">
-        <v>6957060</v>
+        <v>6957081</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,7 +1692,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1709,50 +1719,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127303143</v>
+        <v>127300097</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581903</v>
+        <v>582206</v>
       </c>
       <c r="R12" t="n">
-        <v>6957081</v>
+        <v>6956758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,11 +1794,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127300097</v>
+        <v>127300854</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,7 +1850,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1855,10 +1864,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582206</v>
+        <v>582162</v>
       </c>
       <c r="R13" t="n">
-        <v>6956758</v>
+        <v>6956952</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,6 +1900,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,54 +1931,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127300854</v>
+        <v>127299890</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582162</v>
+        <v>582226</v>
       </c>
       <c r="R14" t="n">
-        <v>6956952</v>
+        <v>6956692</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,11 +2002,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,7 +2031,7 @@
         <v>127302377</v>
       </c>
       <c r="B15" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,50 +2125,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127301633</v>
+        <v>127301182</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>91297</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582057</v>
+        <v>582156</v>
       </c>
       <c r="R16" t="n">
-        <v>6957055</v>
+        <v>6957038</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2201,11 +2196,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2232,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127301388</v>
+        <v>127301633</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582136</v>
+        <v>582057</v>
       </c>
       <c r="R17" t="n">
-        <v>6957002</v>
+        <v>6957055</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,7 +2302,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2339,45 +2329,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127301182</v>
+        <v>127301388</v>
       </c>
       <c r="B18" t="n">
-        <v>91295</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582156</v>
+        <v>582136</v>
       </c>
       <c r="R18" t="n">
-        <v>6957038</v>
+        <v>6957002</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,6 +2405,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,7 +2439,7 @@
         <v>127302258</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127300032</v>
+        <v>127301650</v>
       </c>
       <c r="B20" t="n">
-        <v>91330</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,37 +2544,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582219</v>
+        <v>582068</v>
       </c>
       <c r="R20" t="n">
-        <v>6956755</v>
+        <v>6957026</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2604,6 +2609,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2630,10 +2640,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127301650</v>
+        <v>127300573</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,17 +2676,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582068</v>
+        <v>582225</v>
       </c>
       <c r="R21" t="n">
-        <v>6957026</v>
+        <v>6956940</v>
       </c>
       <c r="S21" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2710,7 +2720,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2737,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127300573</v>
+        <v>127300032</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>91332</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2748,39 +2758,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582225</v>
+        <v>582219</v>
       </c>
       <c r="R22" t="n">
-        <v>6956940</v>
+        <v>6956755</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2813,11 +2818,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2844,32 +2844,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127302739</v>
+        <v>127302871</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>97333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2883,10 +2883,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581843</v>
+        <v>581866</v>
       </c>
       <c r="R23" t="n">
-        <v>6957061</v>
+        <v>6957054</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2945,10 +2945,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127302871</v>
+        <v>127302141</v>
       </c>
       <c r="B24" t="n">
-        <v>97331</v>
+        <v>97327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,16 +2956,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2973,21 +2973,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581866</v>
+        <v>581925</v>
       </c>
       <c r="R24" t="n">
-        <v>6957054</v>
+        <v>6957009</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,45 +3042,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127302141</v>
+        <v>127302739</v>
       </c>
       <c r="B25" t="n">
-        <v>97325</v>
+        <v>98450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581925</v>
+        <v>581843</v>
       </c>
       <c r="R25" t="n">
-        <v>6957009</v>
+        <v>6957061</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127300730</v>
+        <v>127300070</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>91332</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3154,21 +3154,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582186</v>
+        <v>582196</v>
       </c>
       <c r="R26" t="n">
-        <v>6956930</v>
+        <v>6956710</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3248,7 +3248,7 @@
         <v>127302555</v>
       </c>
       <c r="B27" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3342,45 +3342,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127300070</v>
+        <v>127300270</v>
       </c>
       <c r="B28" t="n">
-        <v>91330</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582196</v>
+        <v>582284</v>
       </c>
       <c r="R28" t="n">
-        <v>6956710</v>
+        <v>6956848</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3413,11 +3417,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3444,10 +3443,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300270</v>
+        <v>127300382</v>
       </c>
       <c r="B29" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3474,7 +3473,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3483,10 +3482,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582284</v>
+        <v>582237</v>
       </c>
       <c r="R29" t="n">
-        <v>6956848</v>
+        <v>6956894</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,49 +3544,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127300382</v>
+        <v>127300730</v>
       </c>
       <c r="B30" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582237</v>
+        <v>582186</v>
       </c>
       <c r="R30" t="n">
-        <v>6956894</v>
+        <v>6956930</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3620,6 +3615,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3649,7 +3649,7 @@
         <v>127302334</v>
       </c>
       <c r="B31" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>127302173</v>
       </c>
       <c r="B32" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>127302336</v>
       </c>
       <c r="B33" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>127302187</v>
       </c>
       <c r="B34" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>127300496</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>127300820</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>127300230</v>
       </c>
       <c r="B37" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>127302387</v>
       </c>
       <c r="B38" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>127300073</v>
       </c>
       <c r="B39" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>127301350</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>127301261</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>127302275</v>
       </c>
       <c r="B42" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>127299697</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>127300324</v>
       </c>
       <c r="B44" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>127302594</v>
       </c>
       <c r="B45" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>127303284</v>
       </c>
       <c r="B46" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>127302103</v>
       </c>
       <c r="B47" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>127300916</v>
       </c>
       <c r="B48" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>127301651</v>
       </c>
       <c r="B49" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>127300716</v>
       </c>
       <c r="B50" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>127299940</v>
       </c>
       <c r="B51" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>127299666</v>
       </c>
       <c r="B52" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>127301605</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>127300188</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6104,10 +6104,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127300776</v>
+        <v>127300633</v>
       </c>
       <c r="B55" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6134,12 +6134,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6188,7 +6183,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>16 av dom blommar</t>
+          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6215,37 +6210,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127302307</v>
+        <v>127301471</v>
       </c>
       <c r="B56" t="n">
-        <v>98365</v>
+        <v>98450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581865</v>
+        <v>582122</v>
       </c>
       <c r="R56" t="n">
-        <v>6956984</v>
+        <v>6957012</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6290,6 +6290,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6316,42 +6321,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127301471</v>
+        <v>127302307</v>
       </c>
       <c r="B57" t="n">
-        <v>98448</v>
+        <v>98367</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>582122</v>
+        <v>581865</v>
       </c>
       <c r="R57" t="n">
-        <v>6957012</v>
+        <v>6956984</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6396,11 +6396,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6427,45 +6422,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127299508</v>
+        <v>127302082</v>
       </c>
       <c r="B58" t="n">
-        <v>97325</v>
+        <v>91350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>582284</v>
+        <v>581890</v>
       </c>
       <c r="R58" t="n">
-        <v>6956732</v>
+        <v>6957003</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,45 +6519,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127302082</v>
+        <v>127299508</v>
       </c>
       <c r="B59" t="n">
-        <v>91348</v>
+        <v>97327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581890</v>
+        <v>582284</v>
       </c>
       <c r="R59" t="n">
-        <v>6957003</v>
+        <v>6956732</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6624,7 +6619,7 @@
         <v>127302257</v>
       </c>
       <c r="B60" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6727,45 +6722,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127299731</v>
+        <v>127299437</v>
       </c>
       <c r="B61" t="n">
-        <v>98365</v>
+        <v>57663</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>582264</v>
+        <v>582322</v>
       </c>
       <c r="R61" t="n">
-        <v>6956698</v>
+        <v>6956708</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6798,6 +6798,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6824,50 +6829,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127302049</v>
+        <v>127299731</v>
       </c>
       <c r="B62" t="n">
-        <v>57661</v>
+        <v>98367</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581894</v>
+        <v>582264</v>
       </c>
       <c r="R62" t="n">
-        <v>6957012</v>
+        <v>6956698</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6900,11 +6900,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6931,10 +6926,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127302243</v>
+        <v>127302049</v>
       </c>
       <c r="B63" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6971,10 +6966,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581956</v>
+        <v>581894</v>
       </c>
       <c r="R63" t="n">
-        <v>6956930</v>
+        <v>6957012</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7011,7 +7006,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7038,10 +7033,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127299437</v>
+        <v>127302243</v>
       </c>
       <c r="B64" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7074,14 +7069,14 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582322</v>
+        <v>581956</v>
       </c>
       <c r="R64" t="n">
-        <v>6956708</v>
+        <v>6956930</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7118,7 +7113,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7145,10 +7140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127302544</v>
+        <v>127302060</v>
       </c>
       <c r="B65" t="n">
-        <v>91330</v>
+        <v>91628</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7156,21 +7151,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7180,10 +7175,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581837</v>
+        <v>581894</v>
       </c>
       <c r="R65" t="n">
-        <v>6957037</v>
+        <v>6957012</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7242,10 +7237,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127300173</v>
+        <v>127302544</v>
       </c>
       <c r="B66" t="n">
-        <v>57661</v>
+        <v>91332</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7253,39 +7248,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>582260</v>
+        <v>581837</v>
       </c>
       <c r="R66" t="n">
-        <v>6956842</v>
+        <v>6957037</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7318,11 +7308,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7349,10 +7334,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127300974</v>
+        <v>127300173</v>
       </c>
       <c r="B67" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7380,19 +7365,19 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>582172</v>
+        <v>582260</v>
       </c>
       <c r="R67" t="n">
-        <v>6956985</v>
+        <v>6956842</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7456,10 +7441,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127302060</v>
+        <v>127300974</v>
       </c>
       <c r="B68" t="n">
-        <v>91626</v>
+        <v>57663</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7467,34 +7452,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581894</v>
+        <v>582172</v>
       </c>
       <c r="R68" t="n">
-        <v>6957012</v>
+        <v>6956985</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7527,6 +7517,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7556,7 +7551,7 @@
         <v>127728746</v>
       </c>
       <c r="B69" t="n">
-        <v>91160</v>
+        <v>91162</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -889,49 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299551</v>
+        <v>127302308</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582275</v>
+        <v>581865</v>
       </c>
       <c r="R4" t="n">
-        <v>6956695</v>
+        <v>6956984</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127302308</v>
+        <v>127301930</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,34 +997,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581865</v>
+        <v>581958</v>
       </c>
       <c r="R5" t="n">
-        <v>6956984</v>
+        <v>6957039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127301930</v>
+        <v>127302215</v>
       </c>
       <c r="B6" t="n">
         <v>57663</v>
@@ -1127,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581958</v>
+        <v>581908</v>
       </c>
       <c r="R6" t="n">
-        <v>6957039</v>
+        <v>6956967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,50 +1200,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127302215</v>
+        <v>127299551</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581908</v>
+        <v>582275</v>
       </c>
       <c r="R7" t="n">
-        <v>6956967</v>
+        <v>6956695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1275,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127302377</v>
+        <v>127301182</v>
       </c>
       <c r="B15" t="n">
-        <v>91628</v>
+        <v>91297</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581842</v>
+        <v>582156</v>
       </c>
       <c r="R15" t="n">
-        <v>6957024</v>
+        <v>6957038</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2125,32 +2125,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127301182</v>
+        <v>127302377</v>
       </c>
       <c r="B16" t="n">
-        <v>91297</v>
+        <v>91628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582156</v>
+        <v>581842</v>
       </c>
       <c r="R16" t="n">
-        <v>6957038</v>
+        <v>6957024</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127301633</v>
+        <v>127301388</v>
       </c>
       <c r="B17" t="n">
         <v>57663</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582057</v>
+        <v>582136</v>
       </c>
       <c r="R17" t="n">
-        <v>6957055</v>
+        <v>6957002</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2329,7 +2329,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127301388</v>
+        <v>127301633</v>
       </c>
       <c r="B18" t="n">
         <v>57663</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582136</v>
+        <v>582057</v>
       </c>
       <c r="R18" t="n">
-        <v>6957002</v>
+        <v>6957055</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2844,32 +2844,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127302871</v>
+        <v>127302739</v>
       </c>
       <c r="B23" t="n">
-        <v>97333</v>
+        <v>98450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2883,10 +2883,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581866</v>
+        <v>581843</v>
       </c>
       <c r="R23" t="n">
-        <v>6957054</v>
+        <v>6957061</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2945,10 +2945,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127302141</v>
+        <v>127302871</v>
       </c>
       <c r="B24" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,16 +2956,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2973,17 +2973,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581925</v>
+        <v>581866</v>
       </c>
       <c r="R24" t="n">
-        <v>6957009</v>
+        <v>6957054</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3042,49 +3046,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127302739</v>
+        <v>127302141</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>97327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581843</v>
+        <v>581925</v>
       </c>
       <c r="R25" t="n">
-        <v>6957061</v>
+        <v>6957009</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3342,49 +3342,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127300270</v>
+        <v>127300730</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582284</v>
+        <v>582186</v>
       </c>
       <c r="R28" t="n">
-        <v>6956848</v>
+        <v>6956930</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3417,6 +3413,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3443,7 +3444,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300382</v>
+        <v>127300270</v>
       </c>
       <c r="B29" t="n">
         <v>98450</v>
@@ -3473,7 +3474,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3482,10 +3483,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582237</v>
+        <v>582284</v>
       </c>
       <c r="R29" t="n">
-        <v>6956894</v>
+        <v>6956848</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,45 +3545,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127300730</v>
+        <v>127300382</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582186</v>
+        <v>582237</v>
       </c>
       <c r="R30" t="n">
-        <v>6956930</v>
+        <v>6956894</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,11 +3620,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3646,45 +3646,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127302334</v>
+        <v>127302187</v>
       </c>
       <c r="B31" t="n">
-        <v>91628</v>
+        <v>98450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581864</v>
+        <v>581887</v>
       </c>
       <c r="R31" t="n">
-        <v>6957010</v>
+        <v>6957012</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3743,7 +3747,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127302173</v>
+        <v>127302334</v>
       </c>
       <c r="B32" t="n">
         <v>91628</v>
@@ -3778,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581887</v>
+        <v>581864</v>
       </c>
       <c r="R32" t="n">
-        <v>6957012</v>
+        <v>6957010</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3840,7 +3844,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127302336</v>
+        <v>127302173</v>
       </c>
       <c r="B33" t="n">
         <v>91628</v>
@@ -3875,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581858</v>
+        <v>581887</v>
       </c>
       <c r="R33" t="n">
-        <v>6957026</v>
+        <v>6957012</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,49 +3941,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127302187</v>
+        <v>127302336</v>
       </c>
       <c r="B34" t="n">
-        <v>98450</v>
+        <v>91628</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581887</v>
+        <v>581858</v>
       </c>
       <c r="R34" t="n">
-        <v>6957012</v>
+        <v>6957026</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127303284</v>
+        <v>127300916</v>
       </c>
       <c r="B46" t="n">
-        <v>98450</v>
+        <v>91786</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5180,43 +5180,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581899</v>
+        <v>582172</v>
       </c>
       <c r="R46" t="n">
-        <v>6957139</v>
+        <v>6956985</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5249,11 +5240,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5280,42 +5266,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127302103</v>
+        <v>127301651</v>
       </c>
       <c r="B47" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5324,10 +5306,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581922</v>
+        <v>582042</v>
       </c>
       <c r="R47" t="n">
-        <v>6957019</v>
+        <v>6957055</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5364,7 +5346,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5391,10 +5373,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127300916</v>
+        <v>127303284</v>
       </c>
       <c r="B48" t="n">
-        <v>91786</v>
+        <v>98450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5402,34 +5384,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>582172</v>
+        <v>581899</v>
       </c>
       <c r="R48" t="n">
-        <v>6956985</v>
+        <v>6957139</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5462,6 +5453,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5488,38 +5484,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127301651</v>
+        <v>127302103</v>
       </c>
       <c r="B49" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>582042</v>
+        <v>581922</v>
       </c>
       <c r="R49" t="n">
-        <v>6957055</v>
+        <v>6957019</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6104,49 +6104,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127300633</v>
+        <v>127302307</v>
       </c>
       <c r="B55" t="n">
-        <v>98450</v>
+        <v>98367</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582186</v>
+        <v>581865</v>
       </c>
       <c r="R55" t="n">
-        <v>6956930</v>
+        <v>6956984</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6179,11 +6179,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6210,7 +6205,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127301471</v>
+        <v>127300633</v>
       </c>
       <c r="B56" t="n">
         <v>98450</v>
@@ -6240,24 +6235,19 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582122</v>
+        <v>582186</v>
       </c>
       <c r="R56" t="n">
-        <v>6957012</v>
+        <v>6956930</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6294,7 +6284,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1 blommar</t>
+          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6321,37 +6311,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127302307</v>
+        <v>127301471</v>
       </c>
       <c r="B57" t="n">
-        <v>98367</v>
+        <v>98450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6360,10 +6355,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581865</v>
+        <v>582122</v>
       </c>
       <c r="R57" t="n">
-        <v>6956984</v>
+        <v>6957012</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6396,6 +6391,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6722,50 +6722,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127299437</v>
+        <v>127299731</v>
       </c>
       <c r="B61" t="n">
-        <v>57663</v>
+        <v>98367</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>582322</v>
+        <v>582264</v>
       </c>
       <c r="R61" t="n">
-        <v>6956708</v>
+        <v>6956698</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6798,11 +6793,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6829,45 +6819,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127299731</v>
+        <v>127299437</v>
       </c>
       <c r="B62" t="n">
-        <v>98367</v>
+        <v>57663</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>582264</v>
+        <v>582322</v>
       </c>
       <c r="R62" t="n">
-        <v>6956698</v>
+        <v>6956708</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6900,6 +6895,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -889,45 +889,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127302308</v>
+        <v>127299551</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581865</v>
+        <v>582275</v>
       </c>
       <c r="R4" t="n">
-        <v>6956984</v>
+        <v>6956695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1200,49 +1204,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299551</v>
+        <v>127302308</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582275</v>
+        <v>581865</v>
       </c>
       <c r="R7" t="n">
-        <v>6956695</v>
+        <v>6956984</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2329,50 +2329,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127301633</v>
+        <v>127302258</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>98367</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582057</v>
+        <v>581887</v>
       </c>
       <c r="R18" t="n">
-        <v>6957055</v>
+        <v>6956944</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2405,11 +2400,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2436,45 +2426,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127302258</v>
+        <v>127301633</v>
       </c>
       <c r="B19" t="n">
-        <v>98367</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581887</v>
+        <v>582057</v>
       </c>
       <c r="R19" t="n">
-        <v>6956944</v>
+        <v>6957055</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2507,6 +2502,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -5809,49 +5809,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127299666</v>
+        <v>127302307</v>
       </c>
       <c r="B52" t="n">
-        <v>98450</v>
+        <v>98367</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>582264</v>
+        <v>581865</v>
       </c>
       <c r="R52" t="n">
-        <v>6956698</v>
+        <v>6956984</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5910,48 +5910,52 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127301605</v>
+        <v>127299666</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582068</v>
+        <v>582264</v>
       </c>
       <c r="R53" t="n">
-        <v>6957026</v>
+        <v>6956698</v>
       </c>
       <c r="S53" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6007,7 +6011,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127300188</v>
+        <v>127301605</v>
       </c>
       <c r="B54" t="n">
         <v>79020</v>
@@ -6038,17 +6042,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582277</v>
+        <v>582068</v>
       </c>
       <c r="R54" t="n">
-        <v>6956837</v>
+        <v>6957026</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6104,49 +6108,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127302307</v>
+        <v>127300188</v>
       </c>
       <c r="B55" t="n">
-        <v>98367</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581865</v>
+        <v>582277</v>
       </c>
       <c r="R55" t="n">
-        <v>6956984</v>
+        <v>6956837</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6422,45 +6422,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127302082</v>
+        <v>127299508</v>
       </c>
       <c r="B58" t="n">
-        <v>91350</v>
+        <v>97327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581890</v>
+        <v>582284</v>
       </c>
       <c r="R58" t="n">
-        <v>6957003</v>
+        <v>6956732</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,45 +6519,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127299508</v>
+        <v>127302082</v>
       </c>
       <c r="B59" t="n">
-        <v>97327</v>
+        <v>91350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>582284</v>
+        <v>581890</v>
       </c>
       <c r="R59" t="n">
-        <v>6956732</v>
+        <v>6957003</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -889,49 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299551</v>
+        <v>127301930</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582275</v>
+        <v>581958</v>
       </c>
       <c r="R4" t="n">
-        <v>6956695</v>
+        <v>6957039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127301930</v>
+        <v>127302215</v>
       </c>
       <c r="B5" t="n">
         <v>57663</v>
@@ -1030,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581958</v>
+        <v>581908</v>
       </c>
       <c r="R5" t="n">
-        <v>6957039</v>
+        <v>6956967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,50 +1103,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127302215</v>
+        <v>127299551</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581908</v>
+        <v>582275</v>
       </c>
       <c r="R6" t="n">
-        <v>6956967</v>
+        <v>6956695</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,11 +1178,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,32 +1301,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299754</v>
+        <v>127299890</v>
       </c>
       <c r="B8" t="n">
-        <v>98367</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582249</v>
+        <v>582226</v>
       </c>
       <c r="R8" t="n">
-        <v>6956701</v>
+        <v>6956692</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1931,32 +1931,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299890</v>
+        <v>127299754</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>98367</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582226</v>
+        <v>582249</v>
       </c>
       <c r="R14" t="n">
-        <v>6956692</v>
+        <v>6956701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127301388</v>
+        <v>127301633</v>
       </c>
       <c r="B17" t="n">
         <v>57663</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582136</v>
+        <v>582057</v>
       </c>
       <c r="R17" t="n">
-        <v>6957002</v>
+        <v>6957055</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2329,45 +2329,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127302258</v>
+        <v>127301388</v>
       </c>
       <c r="B18" t="n">
-        <v>98367</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581887</v>
+        <v>582136</v>
       </c>
       <c r="R18" t="n">
-        <v>6956944</v>
+        <v>6957002</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,6 +2405,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2426,50 +2436,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127301633</v>
+        <v>127302258</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>98367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582057</v>
+        <v>581887</v>
       </c>
       <c r="R19" t="n">
-        <v>6957055</v>
+        <v>6956944</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,11 +2507,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127301650</v>
+        <v>127300032</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,42 +2544,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582068</v>
+        <v>582219</v>
       </c>
       <c r="R20" t="n">
-        <v>6957026</v>
+        <v>6956755</v>
       </c>
       <c r="S20" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2609,11 +2604,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2640,7 +2630,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127300573</v>
+        <v>127301650</v>
       </c>
       <c r="B21" t="n">
         <v>57663</v>
@@ -2676,17 +2666,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582225</v>
+        <v>582068</v>
       </c>
       <c r="R21" t="n">
-        <v>6956940</v>
+        <v>6957026</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,7 +2710,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2747,10 +2737,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127300032</v>
+        <v>127300573</v>
       </c>
       <c r="B22" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,34 +2748,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582219</v>
+        <v>582225</v>
       </c>
       <c r="R22" t="n">
-        <v>6956755</v>
+        <v>6956940</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,6 +2813,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2844,32 +2844,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127302739</v>
+        <v>127302871</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>97333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2883,10 +2883,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581843</v>
+        <v>581866</v>
       </c>
       <c r="R23" t="n">
-        <v>6957061</v>
+        <v>6957054</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2945,10 +2945,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127302871</v>
+        <v>127302141</v>
       </c>
       <c r="B24" t="n">
-        <v>97333</v>
+        <v>97327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,16 +2956,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2973,21 +2973,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581866</v>
+        <v>581925</v>
       </c>
       <c r="R24" t="n">
-        <v>6957054</v>
+        <v>6957009</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,45 +3042,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127302141</v>
+        <v>127302739</v>
       </c>
       <c r="B25" t="n">
-        <v>97327</v>
+        <v>98450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581925</v>
+        <v>581843</v>
       </c>
       <c r="R25" t="n">
-        <v>6957009</v>
+        <v>6957061</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,45 +3143,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127300070</v>
+        <v>127300270</v>
       </c>
       <c r="B26" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582196</v>
+        <v>582284</v>
       </c>
       <c r="R26" t="n">
-        <v>6956710</v>
+        <v>6956848</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3214,11 +3218,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3245,45 +3244,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127302555</v>
+        <v>127300382</v>
       </c>
       <c r="B27" t="n">
-        <v>105488</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581837</v>
+        <v>582237</v>
       </c>
       <c r="R27" t="n">
-        <v>6957037</v>
+        <v>6956894</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,10 +3345,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127300730</v>
+        <v>127300070</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3353,21 +3356,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3380,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582186</v>
+        <v>582196</v>
       </c>
       <c r="R28" t="n">
-        <v>6956930</v>
+        <v>6956710</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3417,7 +3420,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3444,49 +3447,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300270</v>
+        <v>127300730</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582284</v>
+        <v>582186</v>
       </c>
       <c r="R29" t="n">
-        <v>6956848</v>
+        <v>6956930</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3519,6 +3518,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3545,49 +3549,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127300382</v>
+        <v>127302555</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>105488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582237</v>
+        <v>581837</v>
       </c>
       <c r="R30" t="n">
-        <v>6956894</v>
+        <v>6957037</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127302334</v>
+        <v>127302336</v>
       </c>
       <c r="B32" t="n">
         <v>91628</v>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581864</v>
+        <v>581858</v>
       </c>
       <c r="R32" t="n">
-        <v>6957010</v>
+        <v>6957026</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127302173</v>
+        <v>127302334</v>
       </c>
       <c r="B33" t="n">
         <v>91628</v>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581887</v>
+        <v>581864</v>
       </c>
       <c r="R33" t="n">
-        <v>6957012</v>
+        <v>6957010</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,7 +3941,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127302336</v>
+        <v>127302173</v>
       </c>
       <c r="B34" t="n">
         <v>91628</v>
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581858</v>
+        <v>581887</v>
       </c>
       <c r="R34" t="n">
-        <v>6957026</v>
+        <v>6957012</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5169,45 +5169,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127300916</v>
+        <v>127301651</v>
       </c>
       <c r="B46" t="n">
-        <v>91786</v>
+        <v>57663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582172</v>
+        <v>582042</v>
       </c>
       <c r="R46" t="n">
-        <v>6956985</v>
+        <v>6957055</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5240,6 +5245,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5266,38 +5276,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127301651</v>
+        <v>127303284</v>
       </c>
       <c r="B47" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5306,10 +5320,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>582042</v>
+        <v>581899</v>
       </c>
       <c r="R47" t="n">
-        <v>6957055</v>
+        <v>6957139</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5346,7 +5360,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5373,7 +5387,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127303284</v>
+        <v>127302103</v>
       </c>
       <c r="B48" t="n">
         <v>98450</v>
@@ -5403,7 +5417,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5417,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581899</v>
+        <v>581922</v>
       </c>
       <c r="R48" t="n">
-        <v>6957139</v>
+        <v>6957019</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5457,7 +5471,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>10 blommar</t>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5484,10 +5498,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127302103</v>
+        <v>127300916</v>
       </c>
       <c r="B49" t="n">
-        <v>98450</v>
+        <v>91786</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5495,43 +5509,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581922</v>
+        <v>582172</v>
       </c>
       <c r="R49" t="n">
-        <v>6957019</v>
+        <v>6956985</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5564,11 +5569,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5809,49 +5809,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127302307</v>
+        <v>127299666</v>
       </c>
       <c r="B52" t="n">
-        <v>98367</v>
+        <v>98450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581865</v>
+        <v>582264</v>
       </c>
       <c r="R52" t="n">
-        <v>6956984</v>
+        <v>6956698</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5910,52 +5910,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127299666</v>
+        <v>127301605</v>
       </c>
       <c r="B53" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582264</v>
+        <v>582068</v>
       </c>
       <c r="R53" t="n">
-        <v>6956698</v>
+        <v>6957026</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6011,7 +6007,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127301605</v>
+        <v>127300188</v>
       </c>
       <c r="B54" t="n">
         <v>79020</v>
@@ -6042,17 +6038,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582068</v>
+        <v>582277</v>
       </c>
       <c r="R54" t="n">
-        <v>6957026</v>
+        <v>6956837</v>
       </c>
       <c r="S54" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6108,45 +6104,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127300188</v>
+        <v>127302307</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>98367</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582277</v>
+        <v>581865</v>
       </c>
       <c r="R55" t="n">
-        <v>6956837</v>
+        <v>6956984</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6422,45 +6422,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127299508</v>
+        <v>127302082</v>
       </c>
       <c r="B58" t="n">
-        <v>97327</v>
+        <v>91350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>582284</v>
+        <v>581890</v>
       </c>
       <c r="R58" t="n">
-        <v>6956732</v>
+        <v>6957003</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,45 +6519,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127302082</v>
+        <v>127299508</v>
       </c>
       <c r="B59" t="n">
-        <v>91350</v>
+        <v>97327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581890</v>
+        <v>582284</v>
       </c>
       <c r="R59" t="n">
-        <v>6957003</v>
+        <v>6956732</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127301930</v>
+        <v>127302308</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581958</v>
+        <v>581865</v>
       </c>
       <c r="R4" t="n">
-        <v>6957039</v>
+        <v>6956984</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127302215</v>
+        <v>127301930</v>
       </c>
       <c r="B5" t="n">
         <v>57663</v>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581908</v>
+        <v>581958</v>
       </c>
       <c r="R5" t="n">
-        <v>6956967</v>
+        <v>6957039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,49 +1093,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299551</v>
+        <v>127302215</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582275</v>
+        <v>581908</v>
       </c>
       <c r="R6" t="n">
-        <v>6956695</v>
+        <v>6956967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,45 +1200,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127302308</v>
+        <v>127299551</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581865</v>
+        <v>582275</v>
       </c>
       <c r="R7" t="n">
-        <v>6956984</v>
+        <v>6956695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,45 +1301,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299890</v>
+        <v>127300097</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582226</v>
+        <v>582206</v>
       </c>
       <c r="R8" t="n">
-        <v>6956692</v>
+        <v>6956758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,50 +1402,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303073</v>
+        <v>127300854</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581907</v>
+        <v>582162</v>
       </c>
       <c r="R9" t="n">
-        <v>6957060</v>
+        <v>6956952</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,7 +1486,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127300124</v>
+        <v>127299890</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,39 +1524,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582206</v>
+        <v>582226</v>
       </c>
       <c r="R10" t="n">
-        <v>6956758</v>
+        <v>6956692</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,11 +1584,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,7 +1610,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127303143</v>
+        <v>127299838</v>
       </c>
       <c r="B11" t="n">
         <v>57663</v>
@@ -1643,19 +1641,19 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581903</v>
+        <v>582206</v>
       </c>
       <c r="R11" t="n">
-        <v>6957081</v>
+        <v>6956758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,7 +1690,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,49 +1717,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127300097</v>
+        <v>127299754</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582206</v>
+        <v>582249</v>
       </c>
       <c r="R12" t="n">
-        <v>6956758</v>
+        <v>6956701</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,54 +1814,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127300854</v>
+        <v>127303073</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582162</v>
+        <v>581907</v>
       </c>
       <c r="R13" t="n">
-        <v>6956952</v>
+        <v>6957060</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1894,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1931,45 +1921,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299754</v>
+        <v>127303143</v>
       </c>
       <c r="B14" t="n">
-        <v>98367</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582249</v>
+        <v>581903</v>
       </c>
       <c r="R14" t="n">
-        <v>6956701</v>
+        <v>6957081</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,6 +1997,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2028,45 +2028,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127301182</v>
+        <v>127301633</v>
       </c>
       <c r="B15" t="n">
-        <v>91297</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582156</v>
+        <v>582057</v>
       </c>
       <c r="R15" t="n">
-        <v>6957038</v>
+        <v>6957055</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,6 +2104,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2125,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127302377</v>
+        <v>127301388</v>
       </c>
       <c r="B16" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2136,34 +2146,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581842</v>
+        <v>582136</v>
       </c>
       <c r="R16" t="n">
-        <v>6957024</v>
+        <v>6957002</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,6 +2211,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2222,50 +2242,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127301633</v>
+        <v>127301182</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>91303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582057</v>
+        <v>582156</v>
       </c>
       <c r="R17" t="n">
-        <v>6957055</v>
+        <v>6957038</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,11 +2313,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2329,10 +2339,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127301388</v>
+        <v>127302377</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>91634</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,39 +2350,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582136</v>
+        <v>581842</v>
       </c>
       <c r="R18" t="n">
-        <v>6957002</v>
+        <v>6957024</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2405,11 +2410,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,7 +2439,7 @@
         <v>127302258</v>
       </c>
       <c r="B19" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>127300032</v>
       </c>
       <c r="B20" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>127302871</v>
       </c>
       <c r="B23" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>127302141</v>
       </c>
       <c r="B24" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>127302739</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3143,49 +3143,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127300270</v>
+        <v>127300730</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582284</v>
+        <v>582186</v>
       </c>
       <c r="R26" t="n">
-        <v>6956848</v>
+        <v>6956930</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3218,6 +3214,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3244,49 +3245,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127300382</v>
+        <v>127300070</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>91338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582237</v>
+        <v>582196</v>
       </c>
       <c r="R27" t="n">
-        <v>6956894</v>
+        <v>6956710</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3319,6 +3316,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3345,45 +3347,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127300070</v>
+        <v>127300270</v>
       </c>
       <c r="B28" t="n">
-        <v>91332</v>
+        <v>98456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582196</v>
+        <v>582284</v>
       </c>
       <c r="R28" t="n">
-        <v>6956710</v>
+        <v>6956848</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,11 +3422,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3447,45 +3448,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300730</v>
+        <v>127300382</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582186</v>
+        <v>582237</v>
       </c>
       <c r="R29" t="n">
-        <v>6956930</v>
+        <v>6956894</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,11 +3523,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3552,7 +3552,7 @@
         <v>127302555</v>
       </c>
       <c r="B30" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3646,49 +3646,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127302187</v>
+        <v>127302334</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>91634</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581887</v>
+        <v>581864</v>
       </c>
       <c r="R31" t="n">
-        <v>6957012</v>
+        <v>6957010</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3747,10 +3743,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127302336</v>
+        <v>127302173</v>
       </c>
       <c r="B32" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,10 +3778,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581858</v>
+        <v>581887</v>
       </c>
       <c r="R32" t="n">
-        <v>6957026</v>
+        <v>6957012</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,10 +3840,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127302334</v>
+        <v>127302336</v>
       </c>
       <c r="B33" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,10 +3875,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581864</v>
+        <v>581858</v>
       </c>
       <c r="R33" t="n">
-        <v>6957010</v>
+        <v>6957026</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,35 +3937,39 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127302173</v>
+        <v>127302187</v>
       </c>
       <c r="B34" t="n">
-        <v>91628</v>
+        <v>98456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
@@ -4255,7 +4255,7 @@
         <v>127300230</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4358,32 +4358,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127302387</v>
+        <v>127302275</v>
       </c>
       <c r="B38" t="n">
-        <v>91628</v>
+        <v>97333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581850</v>
+        <v>581923</v>
       </c>
       <c r="R38" t="n">
-        <v>6957027</v>
+        <v>6956949</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127300073</v>
+        <v>127302387</v>
       </c>
       <c r="B39" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4486,14 +4486,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582196</v>
+        <v>581850</v>
       </c>
       <c r="R39" t="n">
-        <v>6956710</v>
+        <v>6957027</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,10 +4552,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127301350</v>
+        <v>127300073</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>91634</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4563,39 +4563,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582135</v>
+        <v>582196</v>
       </c>
       <c r="R40" t="n">
-        <v>6957030</v>
+        <v>6956710</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4628,11 +4623,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4659,7 +4649,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127301261</v>
+        <v>127301350</v>
       </c>
       <c r="B41" t="n">
         <v>57663</v>
@@ -4699,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582156</v>
+        <v>582135</v>
       </c>
       <c r="R41" t="n">
-        <v>6957038</v>
+        <v>6957030</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4766,45 +4756,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127302275</v>
+        <v>127301261</v>
       </c>
       <c r="B42" t="n">
-        <v>97327</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581923</v>
+        <v>582156</v>
       </c>
       <c r="R42" t="n">
-        <v>6956949</v>
+        <v>6957038</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4837,6 +4832,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4863,10 +4863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127299697</v>
+        <v>127300324</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582264</v>
+        <v>582237</v>
       </c>
       <c r="R43" t="n">
-        <v>6956698</v>
+        <v>6956894</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4934,6 +4934,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4960,7 +4965,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127300324</v>
+        <v>127302594</v>
       </c>
       <c r="B44" t="n">
         <v>57663</v>
@@ -4989,16 +4994,21 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582237</v>
+        <v>581831</v>
       </c>
       <c r="R44" t="n">
-        <v>6956894</v>
+        <v>6957049</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5035,7 +5045,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5062,10 +5072,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127302594</v>
+        <v>127299697</v>
       </c>
       <c r="B45" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5073,39 +5083,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581831</v>
+        <v>582264</v>
       </c>
       <c r="R45" t="n">
-        <v>6957049</v>
+        <v>6956698</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5138,11 +5143,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5169,50 +5169,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127301651</v>
+        <v>127300916</v>
       </c>
       <c r="B46" t="n">
-        <v>57663</v>
+        <v>91792</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582042</v>
+        <v>582172</v>
       </c>
       <c r="R46" t="n">
-        <v>6957055</v>
+        <v>6956985</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5245,11 +5240,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5279,7 +5269,7 @@
         <v>127303284</v>
       </c>
       <c r="B47" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5390,7 +5380,7 @@
         <v>127302103</v>
       </c>
       <c r="B48" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5498,45 +5488,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127300916</v>
+        <v>127301651</v>
       </c>
       <c r="B49" t="n">
-        <v>91786</v>
+        <v>57663</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>582172</v>
+        <v>582042</v>
       </c>
       <c r="R49" t="n">
-        <v>6956985</v>
+        <v>6957055</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,6 +5564,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5809,52 +5809,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127299666</v>
+        <v>127301605</v>
       </c>
       <c r="B52" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>582264</v>
+        <v>582068</v>
       </c>
       <c r="R52" t="n">
-        <v>6956698</v>
+        <v>6957026</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5910,7 +5906,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127301605</v>
+        <v>127300188</v>
       </c>
       <c r="B53" t="n">
         <v>79020</v>
@@ -5941,17 +5937,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582068</v>
+        <v>582277</v>
       </c>
       <c r="R53" t="n">
-        <v>6957026</v>
+        <v>6956837</v>
       </c>
       <c r="S53" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6007,45 +6003,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127300188</v>
+        <v>127302307</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>98373</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582277</v>
+        <v>581865</v>
       </c>
       <c r="R54" t="n">
-        <v>6956837</v>
+        <v>6956984</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6104,49 +6104,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127302307</v>
+        <v>127300633</v>
       </c>
       <c r="B55" t="n">
-        <v>98367</v>
+        <v>98456</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581865</v>
+        <v>582186</v>
       </c>
       <c r="R55" t="n">
-        <v>6956984</v>
+        <v>6956930</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6179,6 +6179,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6205,10 +6210,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127300633</v>
+        <v>127301471</v>
       </c>
       <c r="B56" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6235,19 +6240,24 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582186</v>
+        <v>582122</v>
       </c>
       <c r="R56" t="n">
-        <v>6956930</v>
+        <v>6957012</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6284,7 +6294,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Mer kan förekomma i blåbärsriset</t>
+          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6311,10 +6321,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127301471</v>
+        <v>127299666</v>
       </c>
       <c r="B57" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6341,24 +6351,19 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>582122</v>
+        <v>582264</v>
       </c>
       <c r="R57" t="n">
-        <v>6957012</v>
+        <v>6956698</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6391,11 +6396,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6422,45 +6422,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127302082</v>
+        <v>127299508</v>
       </c>
       <c r="B58" t="n">
-        <v>91350</v>
+        <v>97333</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581890</v>
+        <v>582284</v>
       </c>
       <c r="R58" t="n">
-        <v>6957003</v>
+        <v>6956732</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,45 +6519,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127299508</v>
+        <v>127302082</v>
       </c>
       <c r="B59" t="n">
-        <v>97327</v>
+        <v>91356</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>582284</v>
+        <v>581890</v>
       </c>
       <c r="R59" t="n">
-        <v>6956732</v>
+        <v>6957003</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6619,7 +6619,7 @@
         <v>127302257</v>
       </c>
       <c r="B60" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6722,45 +6722,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127299731</v>
+        <v>127299437</v>
       </c>
       <c r="B61" t="n">
-        <v>98367</v>
+        <v>57663</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>582264</v>
+        <v>582322</v>
       </c>
       <c r="R61" t="n">
-        <v>6956698</v>
+        <v>6956708</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6793,6 +6798,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6819,50 +6829,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127299437</v>
+        <v>127299731</v>
       </c>
       <c r="B62" t="n">
-        <v>57663</v>
+        <v>98373</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>582322</v>
+        <v>582264</v>
       </c>
       <c r="R62" t="n">
-        <v>6956708</v>
+        <v>6956698</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6895,11 +6900,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7143,7 +7143,7 @@
         <v>127302060</v>
       </c>
       <c r="B65" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>127302544</v>
       </c>
       <c r="B66" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>127728746</v>
       </c>
       <c r="B69" t="n">
-        <v>91162</v>
+        <v>91168</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127300985</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127303157</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,45 +889,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127302308</v>
+        <v>127299551</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581865</v>
+        <v>582275</v>
       </c>
       <c r="R4" t="n">
-        <v>6956984</v>
+        <v>6956695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127301930</v>
+        <v>127302308</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,39 +1001,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581958</v>
+        <v>581865</v>
       </c>
       <c r="R5" t="n">
-        <v>6957039</v>
+        <v>6956984</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1061,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127302215</v>
+        <v>127301930</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581908</v>
+        <v>581958</v>
       </c>
       <c r="R6" t="n">
-        <v>6956967</v>
+        <v>6957039</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,49 +1194,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299551</v>
+        <v>127302215</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582275</v>
+        <v>581908</v>
       </c>
       <c r="R7" t="n">
-        <v>6956695</v>
+        <v>6956967</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,49 +1301,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127300097</v>
+        <v>127299754</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582206</v>
+        <v>582249</v>
       </c>
       <c r="R8" t="n">
-        <v>6956758</v>
+        <v>6956701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,54 +1398,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127300854</v>
+        <v>127299890</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582162</v>
+        <v>582226</v>
       </c>
       <c r="R9" t="n">
-        <v>6956952</v>
+        <v>6956692</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,11 +1469,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127299890</v>
+        <v>127299838</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1524,34 +1506,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582226</v>
+        <v>582206</v>
       </c>
       <c r="R10" t="n">
-        <v>6956692</v>
+        <v>6956758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,6 +1571,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299838</v>
+        <v>127303073</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,14 +1638,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582206</v>
+        <v>581907</v>
       </c>
       <c r="R11" t="n">
-        <v>6956758</v>
+        <v>6957060</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,7 +1682,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1717,45 +1709,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299754</v>
+        <v>127303143</v>
       </c>
       <c r="B12" t="n">
-        <v>98373</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582249</v>
+        <v>581903</v>
       </c>
       <c r="R12" t="n">
-        <v>6956701</v>
+        <v>6957081</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,6 +1785,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1814,50 +1816,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127303073</v>
+        <v>127300097</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581907</v>
+        <v>582206</v>
       </c>
       <c r="R13" t="n">
-        <v>6957060</v>
+        <v>6956758</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,11 +1891,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,50 +1917,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127303143</v>
+        <v>127300854</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581903</v>
+        <v>582162</v>
       </c>
       <c r="R14" t="n">
-        <v>6957081</v>
+        <v>6956952</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127301633</v>
+        <v>127302377</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>91637</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,39 +2039,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582057</v>
+        <v>581842</v>
       </c>
       <c r="R15" t="n">
-        <v>6957055</v>
+        <v>6957024</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,11 +2099,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2135,50 +2125,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127301388</v>
+        <v>127302258</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>98376</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582136</v>
+        <v>581887</v>
       </c>
       <c r="R16" t="n">
-        <v>6957002</v>
+        <v>6956944</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,11 +2196,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2245,7 +2225,7 @@
         <v>127301182</v>
       </c>
       <c r="B17" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,10 +2319,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127302377</v>
+        <v>127301633</v>
       </c>
       <c r="B18" t="n">
-        <v>91634</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2350,34 +2330,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581842</v>
+        <v>582057</v>
       </c>
       <c r="R18" t="n">
-        <v>6957024</v>
+        <v>6957055</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,6 +2395,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2436,45 +2426,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127302258</v>
+        <v>127301388</v>
       </c>
       <c r="B19" t="n">
-        <v>98373</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581887</v>
+        <v>582136</v>
       </c>
       <c r="R19" t="n">
-        <v>6956944</v>
+        <v>6957002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2507,6 +2502,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127300032</v>
+        <v>127301650</v>
       </c>
       <c r="B20" t="n">
-        <v>91338</v>
+        <v>57666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,37 +2544,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582219</v>
+        <v>582068</v>
       </c>
       <c r="R20" t="n">
-        <v>6956755</v>
+        <v>6957026</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2604,6 +2609,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2630,10 +2640,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127301650</v>
+        <v>127300573</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,17 +2676,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582068</v>
+        <v>582225</v>
       </c>
       <c r="R21" t="n">
-        <v>6957026</v>
+        <v>6956940</v>
       </c>
       <c r="S21" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2710,7 +2720,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2737,50 +2747,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127300573</v>
+        <v>127302871</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>97342</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582225</v>
+        <v>581866</v>
       </c>
       <c r="R22" t="n">
-        <v>6956940</v>
+        <v>6957054</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2813,11 +2822,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2844,10 +2848,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127302871</v>
+        <v>127302141</v>
       </c>
       <c r="B23" t="n">
-        <v>97339</v>
+        <v>97336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2855,16 +2859,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2872,21 +2876,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581866</v>
+        <v>581925</v>
       </c>
       <c r="R23" t="n">
-        <v>6957054</v>
+        <v>6957009</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2945,45 +2945,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127302141</v>
+        <v>127300032</v>
       </c>
       <c r="B24" t="n">
-        <v>97333</v>
+        <v>91341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581925</v>
+        <v>582219</v>
       </c>
       <c r="R24" t="n">
-        <v>6957009</v>
+        <v>6956755</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,7 +3045,7 @@
         <v>127302739</v>
       </c>
       <c r="B25" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3143,45 +3143,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127300730</v>
+        <v>127300270</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582186</v>
+        <v>582284</v>
       </c>
       <c r="R26" t="n">
-        <v>6956930</v>
+        <v>6956848</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3214,11 +3218,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3245,45 +3244,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127300070</v>
+        <v>127300382</v>
       </c>
       <c r="B27" t="n">
-        <v>91338</v>
+        <v>98459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582196</v>
+        <v>582237</v>
       </c>
       <c r="R27" t="n">
-        <v>6956710</v>
+        <v>6956894</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3316,11 +3319,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3347,49 +3345,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127300270</v>
+        <v>127302555</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>105497</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582284</v>
+        <v>581837</v>
       </c>
       <c r="R28" t="n">
-        <v>6956848</v>
+        <v>6957037</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3448,49 +3442,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300382</v>
+        <v>127300070</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>91341</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582237</v>
+        <v>582196</v>
       </c>
       <c r="R29" t="n">
-        <v>6956894</v>
+        <v>6956710</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3523,6 +3513,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3549,45 +3544,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127302555</v>
+        <v>127300730</v>
       </c>
       <c r="B30" t="n">
-        <v>105494</v>
+        <v>79023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581837</v>
+        <v>582186</v>
       </c>
       <c r="R30" t="n">
-        <v>6957037</v>
+        <v>6956930</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3620,6 +3615,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3646,45 +3646,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127302334</v>
+        <v>127302187</v>
       </c>
       <c r="B31" t="n">
-        <v>91634</v>
+        <v>98459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581864</v>
+        <v>581887</v>
       </c>
       <c r="R31" t="n">
-        <v>6957010</v>
+        <v>6957012</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3743,10 +3747,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127302173</v>
+        <v>127302334</v>
       </c>
       <c r="B32" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3778,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581887</v>
+        <v>581864</v>
       </c>
       <c r="R32" t="n">
-        <v>6957012</v>
+        <v>6957010</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3840,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127302336</v>
+        <v>127302173</v>
       </c>
       <c r="B33" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3875,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581858</v>
+        <v>581887</v>
       </c>
       <c r="R33" t="n">
-        <v>6957026</v>
+        <v>6957012</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,49 +3941,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127302187</v>
+        <v>127302336</v>
       </c>
       <c r="B34" t="n">
-        <v>98456</v>
+        <v>91637</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581887</v>
+        <v>581858</v>
       </c>
       <c r="R34" t="n">
-        <v>6957012</v>
+        <v>6957026</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
         <v>127300496</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>127300820</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>127300230</v>
       </c>
       <c r="B37" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4358,45 +4358,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127302275</v>
+        <v>127301350</v>
       </c>
       <c r="B38" t="n">
-        <v>97333</v>
+        <v>57666</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581923</v>
+        <v>582135</v>
       </c>
       <c r="R38" t="n">
-        <v>6956949</v>
+        <v>6957030</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4429,6 +4434,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4455,10 +4465,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127302387</v>
+        <v>127301261</v>
       </c>
       <c r="B39" t="n">
-        <v>91634</v>
+        <v>57666</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,34 +4476,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581850</v>
+        <v>582156</v>
       </c>
       <c r="R39" t="n">
-        <v>6957027</v>
+        <v>6957038</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4526,6 +4541,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4552,10 +4572,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127300073</v>
+        <v>127302387</v>
       </c>
       <c r="B40" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4583,14 +4603,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582196</v>
+        <v>581850</v>
       </c>
       <c r="R40" t="n">
-        <v>6956710</v>
+        <v>6957027</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4649,10 +4669,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127301350</v>
+        <v>127300073</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>91637</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4660,39 +4680,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582135</v>
+        <v>582196</v>
       </c>
       <c r="R41" t="n">
-        <v>6957030</v>
+        <v>6956710</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4725,11 +4740,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4756,50 +4766,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127301261</v>
+        <v>127302275</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>97336</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582156</v>
+        <v>581923</v>
       </c>
       <c r="R42" t="n">
-        <v>6957038</v>
+        <v>6956949</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4832,11 +4837,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4863,10 +4863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127300324</v>
+        <v>127299697</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582237</v>
+        <v>582264</v>
       </c>
       <c r="R43" t="n">
-        <v>6956894</v>
+        <v>6956698</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4934,11 +4934,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4965,10 +4960,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127302594</v>
+        <v>127300324</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4994,21 +4989,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581831</v>
+        <v>582237</v>
       </c>
       <c r="R44" t="n">
-        <v>6957049</v>
+        <v>6956894</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5045,7 +5035,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5072,10 +5062,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127299697</v>
+        <v>127302594</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,34 +5073,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582264</v>
+        <v>581831</v>
       </c>
       <c r="R45" t="n">
-        <v>6956698</v>
+        <v>6957049</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5143,6 +5138,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5172,7 +5172,7 @@
         <v>127300916</v>
       </c>
       <c r="B46" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5266,42 +5266,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127303284</v>
+        <v>127301651</v>
       </c>
       <c r="B47" t="n">
-        <v>98456</v>
+        <v>57666</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5310,10 +5306,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581899</v>
+        <v>582042</v>
       </c>
       <c r="R47" t="n">
-        <v>6957139</v>
+        <v>6957055</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5350,7 +5346,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>10 blommar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5377,10 +5373,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127302103</v>
+        <v>127303284</v>
       </c>
       <c r="B48" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5407,7 +5403,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5421,10 +5417,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581922</v>
+        <v>581899</v>
       </c>
       <c r="R48" t="n">
-        <v>6957019</v>
+        <v>6957139</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5461,7 +5457,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
+          <t>10 blommar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5488,38 +5484,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127301651</v>
+        <v>127302103</v>
       </c>
       <c r="B49" t="n">
-        <v>57663</v>
+        <v>98459</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>582042</v>
+        <v>581922</v>
       </c>
       <c r="R49" t="n">
-        <v>6957055</v>
+        <v>6957019</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5598,7 +5598,7 @@
         <v>127300716</v>
       </c>
       <c r="B50" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>127299940</v>
       </c>
       <c r="B51" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5809,48 +5809,52 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127301605</v>
+        <v>127299666</v>
       </c>
       <c r="B52" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>582068</v>
+        <v>582264</v>
       </c>
       <c r="R52" t="n">
-        <v>6957026</v>
+        <v>6956698</v>
       </c>
       <c r="S52" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5909,7 +5913,7 @@
         <v>127300188</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6003,52 +6007,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127302307</v>
+        <v>127301605</v>
       </c>
       <c r="B54" t="n">
-        <v>98373</v>
+        <v>79023</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581865</v>
+        <v>582068</v>
       </c>
       <c r="R54" t="n">
-        <v>6956984</v>
+        <v>6957026</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>127300633</v>
       </c>
       <c r="B55" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>127301471</v>
       </c>
       <c r="B56" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6321,49 +6321,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127299666</v>
+        <v>127302307</v>
       </c>
       <c r="B57" t="n">
-        <v>98456</v>
+        <v>98376</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>582264</v>
+        <v>581865</v>
       </c>
       <c r="R57" t="n">
-        <v>6956698</v>
+        <v>6956984</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6425,7 +6425,7 @@
         <v>127299508</v>
       </c>
       <c r="B58" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>127302082</v>
       </c>
       <c r="B59" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>127302257</v>
       </c>
       <c r="B60" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6722,10 +6722,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127299437</v>
+        <v>127302049</v>
       </c>
       <c r="B61" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6758,14 +6758,14 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>582322</v>
+        <v>581894</v>
       </c>
       <c r="R61" t="n">
-        <v>6956708</v>
+        <v>6957012</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6829,45 +6829,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127299731</v>
+        <v>127302243</v>
       </c>
       <c r="B62" t="n">
-        <v>98373</v>
+        <v>57666</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>582264</v>
+        <v>581956</v>
       </c>
       <c r="R62" t="n">
-        <v>6956698</v>
+        <v>6956930</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6900,6 +6905,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6926,10 +6936,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127302049</v>
+        <v>127299437</v>
       </c>
       <c r="B63" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6962,14 +6972,14 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581894</v>
+        <v>582322</v>
       </c>
       <c r="R63" t="n">
-        <v>6957012</v>
+        <v>6956708</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7006,7 +7016,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7033,50 +7043,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127302243</v>
+        <v>127299731</v>
       </c>
       <c r="B64" t="n">
-        <v>57663</v>
+        <v>98376</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581956</v>
+        <v>582264</v>
       </c>
       <c r="R64" t="n">
-        <v>6956930</v>
+        <v>6956698</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7109,11 +7114,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7143,7 +7143,7 @@
         <v>127302060</v>
       </c>
       <c r="B65" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>127302544</v>
       </c>
       <c r="B66" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>127300173</v>
       </c>
       <c r="B67" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>127300974</v>
       </c>
       <c r="B68" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>127728746</v>
       </c>
       <c r="B69" t="n">
-        <v>91168</v>
+        <v>91171</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127300985</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127303157</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127299551</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>127302308</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>127301930</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>127302215</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,45 +1301,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299754</v>
+        <v>127299838</v>
       </c>
       <c r="B8" t="n">
-        <v>98376</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582249</v>
+        <v>582206</v>
       </c>
       <c r="R8" t="n">
-        <v>6956701</v>
+        <v>6956758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,6 +1377,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,7 +1411,7 @@
         <v>127299890</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,38 +1505,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127299838</v>
+        <v>127300097</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1571,11 +1580,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,50 +1606,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127303073</v>
+        <v>127300854</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581907</v>
+        <v>582162</v>
       </c>
       <c r="R11" t="n">
-        <v>6957060</v>
+        <v>6956952</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,7 +1690,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1709,50 +1717,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127303143</v>
+        <v>127299754</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>98384</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581903</v>
+        <v>582249</v>
       </c>
       <c r="R12" t="n">
-        <v>6957081</v>
+        <v>6956701</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,11 +1788,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,49 +1814,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127300097</v>
+        <v>127303073</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582206</v>
+        <v>581907</v>
       </c>
       <c r="R13" t="n">
-        <v>6956758</v>
+        <v>6957060</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,6 +1890,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,54 +1921,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127300854</v>
+        <v>127303143</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582162</v>
+        <v>581903</v>
       </c>
       <c r="R14" t="n">
-        <v>6956952</v>
+        <v>6957081</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
+          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127302377</v>
+        <v>127301182</v>
       </c>
       <c r="B15" t="n">
-        <v>91637</v>
+        <v>91314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581842</v>
+        <v>582156</v>
       </c>
       <c r="R15" t="n">
-        <v>6957024</v>
+        <v>6957038</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2125,45 +2125,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127302258</v>
+        <v>127301633</v>
       </c>
       <c r="B16" t="n">
-        <v>98376</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581887</v>
+        <v>582057</v>
       </c>
       <c r="R16" t="n">
-        <v>6956944</v>
+        <v>6957055</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,6 +2201,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2222,45 +2232,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127301182</v>
+        <v>127301388</v>
       </c>
       <c r="B17" t="n">
-        <v>91306</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582156</v>
+        <v>582136</v>
       </c>
       <c r="R17" t="n">
-        <v>6957038</v>
+        <v>6957002</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,6 +2308,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,50 +2339,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127301633</v>
+        <v>127302258</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>98384</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582057</v>
+        <v>581887</v>
       </c>
       <c r="R18" t="n">
-        <v>6957055</v>
+        <v>6956944</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2395,11 +2410,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2426,10 +2436,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127301388</v>
+        <v>127302377</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>91645</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,39 +2447,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582136</v>
+        <v>581842</v>
       </c>
       <c r="R19" t="n">
-        <v>6957002</v>
+        <v>6957024</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,11 +2507,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127301650</v>
+        <v>127300032</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>91349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,42 +2544,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582068</v>
+        <v>582219</v>
       </c>
       <c r="R20" t="n">
-        <v>6957026</v>
+        <v>6956755</v>
       </c>
       <c r="S20" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2609,11 +2604,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2640,10 +2630,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127300573</v>
+        <v>127301650</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,17 +2666,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582225</v>
+        <v>582068</v>
       </c>
       <c r="R21" t="n">
-        <v>6956940</v>
+        <v>6957026</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,7 +2710,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2747,49 +2737,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127302871</v>
+        <v>127300573</v>
       </c>
       <c r="B22" t="n">
-        <v>97342</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581866</v>
+        <v>582225</v>
       </c>
       <c r="R22" t="n">
-        <v>6957054</v>
+        <v>6956940</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,6 +2813,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2848,45 +2844,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127302141</v>
+        <v>127302739</v>
       </c>
       <c r="B23" t="n">
-        <v>97336</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581925</v>
+        <v>581843</v>
       </c>
       <c r="R23" t="n">
-        <v>6957009</v>
+        <v>6957061</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2945,45 +2945,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127300032</v>
+        <v>127302871</v>
       </c>
       <c r="B24" t="n">
-        <v>91341</v>
+        <v>97350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582219</v>
+        <v>581866</v>
       </c>
       <c r="R24" t="n">
-        <v>6956755</v>
+        <v>6957054</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3042,49 +3046,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127302739</v>
+        <v>127302141</v>
       </c>
       <c r="B25" t="n">
-        <v>98459</v>
+        <v>97344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581843</v>
+        <v>581925</v>
       </c>
       <c r="R25" t="n">
-        <v>6957061</v>
+        <v>6957009</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,49 +3143,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127300270</v>
+        <v>127302555</v>
       </c>
       <c r="B26" t="n">
-        <v>98459</v>
+        <v>105505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582284</v>
+        <v>581837</v>
       </c>
       <c r="R26" t="n">
-        <v>6956848</v>
+        <v>6957037</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3244,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127300382</v>
+        <v>127300270</v>
       </c>
       <c r="B27" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3274,7 +3270,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3283,10 +3279,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582237</v>
+        <v>582284</v>
       </c>
       <c r="R27" t="n">
-        <v>6956894</v>
+        <v>6956848</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3345,45 +3341,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127302555</v>
+        <v>127300382</v>
       </c>
       <c r="B28" t="n">
-        <v>105497</v>
+        <v>98467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581837</v>
+        <v>582237</v>
       </c>
       <c r="R28" t="n">
-        <v>6957037</v>
+        <v>6956894</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3445,7 +3445,7 @@
         <v>127300070</v>
       </c>
       <c r="B29" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>127300730</v>
       </c>
       <c r="B30" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3646,39 +3646,35 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127302187</v>
+        <v>127302173</v>
       </c>
       <c r="B31" t="n">
-        <v>98459</v>
+        <v>91645</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
@@ -3747,10 +3743,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127302334</v>
+        <v>127302336</v>
       </c>
       <c r="B32" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,10 +3778,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581864</v>
+        <v>581858</v>
       </c>
       <c r="R32" t="n">
-        <v>6957010</v>
+        <v>6957026</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,10 +3840,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127302173</v>
+        <v>127302334</v>
       </c>
       <c r="B33" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,10 +3875,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581887</v>
+        <v>581864</v>
       </c>
       <c r="R33" t="n">
-        <v>6957012</v>
+        <v>6957010</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,45 +3937,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127302336</v>
+        <v>127302187</v>
       </c>
       <c r="B34" t="n">
-        <v>91637</v>
+        <v>98467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581858</v>
+        <v>581887</v>
       </c>
       <c r="R34" t="n">
-        <v>6957026</v>
+        <v>6957012</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
         <v>127300496</v>
       </c>
       <c r="B35" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>127300820</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>127300230</v>
       </c>
       <c r="B37" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>127301350</v>
       </c>
       <c r="B38" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>127301261</v>
       </c>
       <c r="B39" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4572,10 +4572,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127302387</v>
+        <v>127300073</v>
       </c>
       <c r="B40" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4603,14 +4603,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581850</v>
+        <v>582196</v>
       </c>
       <c r="R40" t="n">
-        <v>6957027</v>
+        <v>6956710</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127300073</v>
+        <v>127302387</v>
       </c>
       <c r="B41" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4700,14 +4700,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582196</v>
+        <v>581850</v>
       </c>
       <c r="R41" t="n">
-        <v>6956710</v>
+        <v>6957027</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
         <v>127302275</v>
       </c>
       <c r="B42" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>127299697</v>
       </c>
       <c r="B43" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>127300324</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>127302594</v>
       </c>
       <c r="B45" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>127300916</v>
       </c>
       <c r="B46" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>127301651</v>
       </c>
       <c r="B47" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>127303284</v>
       </c>
       <c r="B48" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>127302103</v>
       </c>
       <c r="B49" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>127300716</v>
       </c>
       <c r="B50" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>127299940</v>
       </c>
       <c r="B51" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>127299666</v>
       </c>
       <c r="B52" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5910,10 +5910,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127300188</v>
+        <v>127301605</v>
       </c>
       <c r="B53" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5941,17 +5941,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582277</v>
+        <v>582068</v>
       </c>
       <c r="R53" t="n">
-        <v>6956837</v>
+        <v>6957026</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6007,48 +6007,52 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127301605</v>
+        <v>127302307</v>
       </c>
       <c r="B54" t="n">
-        <v>79023</v>
+        <v>98384</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582068</v>
+        <v>581865</v>
       </c>
       <c r="R54" t="n">
-        <v>6957026</v>
+        <v>6956984</v>
       </c>
       <c r="S54" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6104,49 +6108,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127300633</v>
+        <v>127300188</v>
       </c>
       <c r="B55" t="n">
-        <v>98459</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582186</v>
+        <v>582277</v>
       </c>
       <c r="R55" t="n">
-        <v>6956930</v>
+        <v>6956837</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6179,11 +6179,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6210,10 +6205,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127301471</v>
+        <v>127300633</v>
       </c>
       <c r="B56" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6240,24 +6235,19 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582122</v>
+        <v>582186</v>
       </c>
       <c r="R56" t="n">
-        <v>6957012</v>
+        <v>6956930</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6294,7 +6284,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1 blommar</t>
+          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6321,37 +6311,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127302307</v>
+        <v>127301471</v>
       </c>
       <c r="B57" t="n">
-        <v>98376</v>
+        <v>98467</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6360,10 +6355,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581865</v>
+        <v>582122</v>
       </c>
       <c r="R57" t="n">
-        <v>6956984</v>
+        <v>6957012</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6396,6 +6391,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6422,45 +6422,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127299508</v>
+        <v>127302082</v>
       </c>
       <c r="B58" t="n">
-        <v>97336</v>
+        <v>91367</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>582284</v>
+        <v>581890</v>
       </c>
       <c r="R58" t="n">
-        <v>6956732</v>
+        <v>6957003</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,45 +6519,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127302082</v>
+        <v>127299508</v>
       </c>
       <c r="B59" t="n">
-        <v>91359</v>
+        <v>97344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581890</v>
+        <v>582284</v>
       </c>
       <c r="R59" t="n">
-        <v>6957003</v>
+        <v>6956732</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6619,7 +6619,7 @@
         <v>127302257</v>
       </c>
       <c r="B60" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6722,10 +6722,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127302049</v>
+        <v>127299437</v>
       </c>
       <c r="B61" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6758,14 +6758,14 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581894</v>
+        <v>582322</v>
       </c>
       <c r="R61" t="n">
-        <v>6957012</v>
+        <v>6956708</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6832,7 +6832,7 @@
         <v>127302243</v>
       </c>
       <c r="B62" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6936,50 +6936,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127299437</v>
+        <v>127299731</v>
       </c>
       <c r="B63" t="n">
-        <v>57666</v>
+        <v>98384</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582322</v>
+        <v>582264</v>
       </c>
       <c r="R63" t="n">
-        <v>6956708</v>
+        <v>6956698</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7012,11 +7007,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7043,45 +7033,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127299731</v>
+        <v>127302049</v>
       </c>
       <c r="B64" t="n">
-        <v>98376</v>
+        <v>57672</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582264</v>
+        <v>581894</v>
       </c>
       <c r="R64" t="n">
-        <v>6956698</v>
+        <v>6957012</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7114,6 +7109,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7143,7 +7143,7 @@
         <v>127302060</v>
       </c>
       <c r="B65" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>127302544</v>
       </c>
       <c r="B66" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>127300173</v>
       </c>
       <c r="B67" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>127300974</v>
       </c>
       <c r="B68" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>127728746</v>
       </c>
       <c r="B69" t="n">
-        <v>91171</v>
+        <v>91179</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -889,49 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299551</v>
+        <v>127302308</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582275</v>
+        <v>581865</v>
       </c>
       <c r="R4" t="n">
-        <v>6956695</v>
+        <v>6956984</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127302308</v>
+        <v>127301930</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,34 +997,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581865</v>
+        <v>581958</v>
       </c>
       <c r="R5" t="n">
-        <v>6956984</v>
+        <v>6957039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127301930</v>
+        <v>127302215</v>
       </c>
       <c r="B6" t="n">
         <v>57672</v>
@@ -1127,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581958</v>
+        <v>581908</v>
       </c>
       <c r="R6" t="n">
-        <v>6957039</v>
+        <v>6956967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,50 +1200,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127302215</v>
+        <v>127299551</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581908</v>
+        <v>582275</v>
       </c>
       <c r="R7" t="n">
-        <v>6956967</v>
+        <v>6956695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1275,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,7 +1301,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299838</v>
+        <v>127303073</v>
       </c>
       <c r="B8" t="n">
         <v>57672</v>
@@ -1337,14 +1337,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582206</v>
+        <v>581907</v>
       </c>
       <c r="R8" t="n">
-        <v>6956758</v>
+        <v>6957060</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299890</v>
+        <v>127300124</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,34 +1419,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582226</v>
+        <v>582206</v>
       </c>
       <c r="R9" t="n">
-        <v>6956692</v>
+        <v>6956758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,6 +1484,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,49 +1515,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127300097</v>
+        <v>127303143</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582206</v>
+        <v>581903</v>
       </c>
       <c r="R10" t="n">
-        <v>6956758</v>
+        <v>6957081</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,6 +1591,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,54 +1622,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127300854</v>
+        <v>127299890</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582162</v>
+        <v>582226</v>
       </c>
       <c r="R11" t="n">
-        <v>6956952</v>
+        <v>6956692</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,11 +1693,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,7 +1722,7 @@
         <v>127299754</v>
       </c>
       <c r="B12" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,50 +1816,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127303073</v>
+        <v>127300097</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581907</v>
+        <v>582206</v>
       </c>
       <c r="R13" t="n">
-        <v>6957060</v>
+        <v>6956758</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,11 +1891,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,50 +1917,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127303143</v>
+        <v>127300854</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581903</v>
+        <v>582162</v>
       </c>
       <c r="R14" t="n">
-        <v>6957081</v>
+        <v>6956952</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127301182</v>
+        <v>127302377</v>
       </c>
       <c r="B15" t="n">
-        <v>91314</v>
+        <v>91646</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582156</v>
+        <v>581842</v>
       </c>
       <c r="R15" t="n">
-        <v>6957038</v>
+        <v>6957024</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2125,50 +2125,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127301633</v>
+        <v>127301182</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>91315</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582057</v>
+        <v>582156</v>
       </c>
       <c r="R16" t="n">
-        <v>6957055</v>
+        <v>6957038</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2201,11 +2196,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2232,50 +2222,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127301388</v>
+        <v>127302258</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582136</v>
+        <v>581887</v>
       </c>
       <c r="R17" t="n">
-        <v>6957002</v>
+        <v>6956944</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,11 +2293,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2339,45 +2319,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127302258</v>
+        <v>127301633</v>
       </c>
       <c r="B18" t="n">
-        <v>98384</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581887</v>
+        <v>582057</v>
       </c>
       <c r="R18" t="n">
-        <v>6956944</v>
+        <v>6957055</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,6 +2395,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2436,10 +2426,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127302377</v>
+        <v>127301388</v>
       </c>
       <c r="B19" t="n">
-        <v>91645</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,34 +2437,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581842</v>
+        <v>582136</v>
       </c>
       <c r="R19" t="n">
-        <v>6957024</v>
+        <v>6957002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2507,6 +2502,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2536,7 +2536,7 @@
         <v>127300032</v>
       </c>
       <c r="B20" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>127302739</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>127302871</v>
       </c>
       <c r="B24" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>127302141</v>
       </c>
       <c r="B25" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3143,45 +3143,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127302555</v>
+        <v>127300730</v>
       </c>
       <c r="B26" t="n">
-        <v>105505</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581837</v>
+        <v>582186</v>
       </c>
       <c r="R26" t="n">
-        <v>6957037</v>
+        <v>6956930</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3214,6 +3214,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3243,7 +3248,7 @@
         <v>127300270</v>
       </c>
       <c r="B27" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3349,7 @@
         <v>127300382</v>
       </c>
       <c r="B28" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,45 +3447,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300070</v>
+        <v>127302555</v>
       </c>
       <c r="B29" t="n">
-        <v>91349</v>
+        <v>105506</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582196</v>
+        <v>581837</v>
       </c>
       <c r="R29" t="n">
-        <v>6956710</v>
+        <v>6957037</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,11 +3518,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127300730</v>
+        <v>127300070</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>91350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582186</v>
+        <v>582196</v>
       </c>
       <c r="R30" t="n">
-        <v>6956930</v>
+        <v>6956710</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3646,10 +3646,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127302173</v>
+        <v>127302334</v>
       </c>
       <c r="B31" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581887</v>
+        <v>581864</v>
       </c>
       <c r="R31" t="n">
-        <v>6957012</v>
+        <v>6957010</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3743,10 +3743,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127302336</v>
+        <v>127302173</v>
       </c>
       <c r="B32" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3778,10 +3778,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581858</v>
+        <v>581887</v>
       </c>
       <c r="R32" t="n">
-        <v>6957026</v>
+        <v>6957012</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3840,10 +3840,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127302334</v>
+        <v>127302336</v>
       </c>
       <c r="B33" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3875,10 +3875,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581864</v>
+        <v>581858</v>
       </c>
       <c r="R33" t="n">
-        <v>6957010</v>
+        <v>6957026</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
         <v>127302187</v>
       </c>
       <c r="B34" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>127300230</v>
       </c>
       <c r="B37" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4358,50 +4358,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127301350</v>
+        <v>127302275</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>97345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582135</v>
+        <v>581923</v>
       </c>
       <c r="R38" t="n">
-        <v>6957030</v>
+        <v>6956949</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,11 +4429,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4465,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127301261</v>
+        <v>127302387</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4476,39 +4466,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582156</v>
+        <v>581850</v>
       </c>
       <c r="R39" t="n">
-        <v>6957038</v>
+        <v>6957027</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4541,11 +4526,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4575,7 +4555,7 @@
         <v>127300073</v>
       </c>
       <c r="B40" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4669,10 +4649,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127302387</v>
+        <v>127301350</v>
       </c>
       <c r="B41" t="n">
-        <v>91645</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4680,34 +4660,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581850</v>
+        <v>582135</v>
       </c>
       <c r="R41" t="n">
-        <v>6957027</v>
+        <v>6957030</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4740,6 +4725,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4766,45 +4756,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127302275</v>
+        <v>127301261</v>
       </c>
       <c r="B42" t="n">
-        <v>97344</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581923</v>
+        <v>582156</v>
       </c>
       <c r="R42" t="n">
-        <v>6956949</v>
+        <v>6957038</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4837,6 +4832,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5172,7 +5172,7 @@
         <v>127300916</v>
       </c>
       <c r="B46" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>127303284</v>
       </c>
       <c r="B48" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>127302103</v>
       </c>
       <c r="B49" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>127299666</v>
       </c>
       <c r="B52" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6007,49 +6007,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127302307</v>
+        <v>127300188</v>
       </c>
       <c r="B54" t="n">
-        <v>98384</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581865</v>
+        <v>582277</v>
       </c>
       <c r="R54" t="n">
-        <v>6956984</v>
+        <v>6956837</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6108,45 +6104,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127300188</v>
+        <v>127302307</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>98385</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582277</v>
+        <v>581865</v>
       </c>
       <c r="R55" t="n">
-        <v>6956837</v>
+        <v>6956984</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6208,7 +6208,7 @@
         <v>127300633</v>
       </c>
       <c r="B56" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>127301471</v>
       </c>
       <c r="B57" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>127302082</v>
       </c>
       <c r="B58" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>127299508</v>
       </c>
       <c r="B59" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>127302257</v>
       </c>
       <c r="B60" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6722,50 +6722,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127299437</v>
+        <v>127299731</v>
       </c>
       <c r="B61" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>582322</v>
+        <v>582264</v>
       </c>
       <c r="R61" t="n">
-        <v>6956708</v>
+        <v>6956698</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6798,11 +6793,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6829,7 +6819,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127302243</v>
+        <v>127302049</v>
       </c>
       <c r="B62" t="n">
         <v>57672</v>
@@ -6869,10 +6859,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581956</v>
+        <v>581894</v>
       </c>
       <c r="R62" t="n">
-        <v>6956930</v>
+        <v>6957012</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6909,7 +6899,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6936,45 +6926,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127299731</v>
+        <v>127302243</v>
       </c>
       <c r="B63" t="n">
-        <v>98384</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582264</v>
+        <v>581956</v>
       </c>
       <c r="R63" t="n">
-        <v>6956698</v>
+        <v>6956930</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7007,6 +7002,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7033,7 +7033,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127302049</v>
+        <v>127299437</v>
       </c>
       <c r="B64" t="n">
         <v>57672</v>
@@ -7069,14 +7069,14 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581894</v>
+        <v>582322</v>
       </c>
       <c r="R64" t="n">
-        <v>6957012</v>
+        <v>6956708</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7140,10 +7140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127302060</v>
+        <v>127302544</v>
       </c>
       <c r="B65" t="n">
-        <v>91645</v>
+        <v>91350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7151,21 +7151,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7175,10 +7175,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581894</v>
+        <v>581837</v>
       </c>
       <c r="R65" t="n">
-        <v>6957012</v>
+        <v>6957037</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7237,10 +7237,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127302544</v>
+        <v>127302060</v>
       </c>
       <c r="B66" t="n">
-        <v>91349</v>
+        <v>91646</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7248,21 +7248,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581837</v>
+        <v>581894</v>
       </c>
       <c r="R66" t="n">
-        <v>6957037</v>
+        <v>6957012</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7551,7 +7551,7 @@
         <v>127728746</v>
       </c>
       <c r="B69" t="n">
-        <v>91179</v>
+        <v>91180</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303073</v>
+        <v>127299890</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,39 +1312,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581907</v>
+        <v>582226</v>
       </c>
       <c r="R8" t="n">
-        <v>6957060</v>
+        <v>6956692</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,11 +1372,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127300124</v>
+        <v>127299838</v>
       </c>
       <c r="B9" t="n">
         <v>57672</v>
@@ -1439,7 +1429,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1488,7 +1478,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,50 +1505,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127303143</v>
+        <v>127300097</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581903</v>
+        <v>582206</v>
       </c>
       <c r="R10" t="n">
-        <v>6957081</v>
+        <v>6956758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,11 +1580,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,45 +1606,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299890</v>
+        <v>127300854</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582226</v>
+        <v>582162</v>
       </c>
       <c r="R11" t="n">
-        <v>6956692</v>
+        <v>6956952</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,6 +1686,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,45 +1717,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299754</v>
+        <v>127303073</v>
       </c>
       <c r="B12" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582249</v>
+        <v>581907</v>
       </c>
       <c r="R12" t="n">
-        <v>6956701</v>
+        <v>6957060</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1790,6 +1793,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,49 +1824,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127300097</v>
+        <v>127303143</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582206</v>
+        <v>581903</v>
       </c>
       <c r="R13" t="n">
-        <v>6956758</v>
+        <v>6957081</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,6 +1900,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,54 +1931,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127300854</v>
+        <v>127299754</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98385</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582162</v>
+        <v>582249</v>
       </c>
       <c r="R14" t="n">
-        <v>6956952</v>
+        <v>6956701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,11 +2002,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2222,45 +2222,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127302258</v>
+        <v>127301633</v>
       </c>
       <c r="B17" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581887</v>
+        <v>582057</v>
       </c>
       <c r="R17" t="n">
-        <v>6956944</v>
+        <v>6957055</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,6 +2298,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,7 +2329,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127301633</v>
+        <v>127301388</v>
       </c>
       <c r="B18" t="n">
         <v>57672</v>
@@ -2359,10 +2369,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582057</v>
+        <v>582136</v>
       </c>
       <c r="R18" t="n">
-        <v>6957055</v>
+        <v>6957002</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2399,7 +2409,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2426,50 +2436,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127301388</v>
+        <v>127302258</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582136</v>
+        <v>581887</v>
       </c>
       <c r="R19" t="n">
-        <v>6957002</v>
+        <v>6956944</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,11 +2507,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127300032</v>
+        <v>127301650</v>
       </c>
       <c r="B20" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,37 +2544,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582219</v>
+        <v>582068</v>
       </c>
       <c r="R20" t="n">
-        <v>6956755</v>
+        <v>6957026</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2604,6 +2609,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2630,7 +2640,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127301650</v>
+        <v>127300573</v>
       </c>
       <c r="B21" t="n">
         <v>57672</v>
@@ -2666,17 +2676,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582068</v>
+        <v>582225</v>
       </c>
       <c r="R21" t="n">
-        <v>6957026</v>
+        <v>6956940</v>
       </c>
       <c r="S21" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2710,7 +2720,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2737,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127300573</v>
+        <v>127300032</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2748,39 +2758,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582225</v>
+        <v>582219</v>
       </c>
       <c r="R22" t="n">
-        <v>6956940</v>
+        <v>6956755</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2813,11 +2818,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3143,45 +3143,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127300730</v>
+        <v>127300270</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582186</v>
+        <v>582284</v>
       </c>
       <c r="R26" t="n">
-        <v>6956930</v>
+        <v>6956848</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3214,11 +3218,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3245,7 +3244,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127300270</v>
+        <v>127300382</v>
       </c>
       <c r="B27" t="n">
         <v>98468</v>
@@ -3275,7 +3274,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3284,10 +3283,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582284</v>
+        <v>582237</v>
       </c>
       <c r="R27" t="n">
-        <v>6956848</v>
+        <v>6956894</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,49 +3345,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127300382</v>
+        <v>127300070</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>91350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582237</v>
+        <v>582196</v>
       </c>
       <c r="R28" t="n">
-        <v>6956894</v>
+        <v>6956710</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3421,6 +3416,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3447,45 +3447,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127302555</v>
+        <v>127300730</v>
       </c>
       <c r="B29" t="n">
-        <v>105506</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581837</v>
+        <v>582186</v>
       </c>
       <c r="R29" t="n">
-        <v>6957037</v>
+        <v>6956930</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,6 +3518,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3544,45 +3549,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127300070</v>
+        <v>127302555</v>
       </c>
       <c r="B30" t="n">
-        <v>91350</v>
+        <v>105506</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582196</v>
+        <v>581837</v>
       </c>
       <c r="R30" t="n">
-        <v>6956710</v>
+        <v>6957037</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,11 +3620,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4358,45 +4358,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127302275</v>
+        <v>127301350</v>
       </c>
       <c r="B38" t="n">
-        <v>97345</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581923</v>
+        <v>582135</v>
       </c>
       <c r="R38" t="n">
-        <v>6956949</v>
+        <v>6957030</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4429,6 +4434,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4455,10 +4465,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127302387</v>
+        <v>127301261</v>
       </c>
       <c r="B39" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,34 +4476,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581850</v>
+        <v>582156</v>
       </c>
       <c r="R39" t="n">
-        <v>6957027</v>
+        <v>6957038</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4526,6 +4541,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4552,7 +4572,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127300073</v>
+        <v>127302387</v>
       </c>
       <c r="B40" t="n">
         <v>91646</v>
@@ -4583,14 +4603,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582196</v>
+        <v>581850</v>
       </c>
       <c r="R40" t="n">
-        <v>6956710</v>
+        <v>6957027</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4649,10 +4669,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127301350</v>
+        <v>127300073</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4660,39 +4680,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582135</v>
+        <v>582196</v>
       </c>
       <c r="R41" t="n">
-        <v>6957030</v>
+        <v>6956710</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4725,11 +4740,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4756,50 +4766,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127301261</v>
+        <v>127302275</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>97345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582156</v>
+        <v>581923</v>
       </c>
       <c r="R42" t="n">
-        <v>6957038</v>
+        <v>6956949</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4832,11 +4837,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4863,10 +4863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127299697</v>
+        <v>127300324</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582264</v>
+        <v>582237</v>
       </c>
       <c r="R43" t="n">
-        <v>6956698</v>
+        <v>6956894</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4934,6 +4934,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4960,7 +4965,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127300324</v>
+        <v>127302594</v>
       </c>
       <c r="B44" t="n">
         <v>57672</v>
@@ -4989,16 +4994,21 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582237</v>
+        <v>581831</v>
       </c>
       <c r="R44" t="n">
-        <v>6956894</v>
+        <v>6957049</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5035,7 +5045,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5062,10 +5072,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127302594</v>
+        <v>127299697</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5073,39 +5083,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581831</v>
+        <v>582264</v>
       </c>
       <c r="R45" t="n">
-        <v>6957049</v>
+        <v>6956698</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5138,11 +5143,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5169,45 +5169,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127300916</v>
+        <v>127301651</v>
       </c>
       <c r="B46" t="n">
-        <v>91804</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582172</v>
+        <v>582042</v>
       </c>
       <c r="R46" t="n">
-        <v>6956985</v>
+        <v>6957055</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5240,6 +5245,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5266,38 +5276,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127301651</v>
+        <v>127302103</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5306,10 +5320,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>582042</v>
+        <v>581922</v>
       </c>
       <c r="R47" t="n">
-        <v>6957055</v>
+        <v>6957019</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5346,7 +5360,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5484,10 +5498,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127302103</v>
+        <v>127300916</v>
       </c>
       <c r="B49" t="n">
-        <v>98468</v>
+        <v>91804</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5495,43 +5509,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581922</v>
+        <v>582172</v>
       </c>
       <c r="R49" t="n">
-        <v>6957019</v>
+        <v>6956985</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5564,11 +5569,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5809,7 +5809,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127299666</v>
+        <v>127300776</v>
       </c>
       <c r="B52" t="n">
         <v>98468</v>
@@ -5839,7 +5839,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5848,10 +5853,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>582264</v>
+        <v>582186</v>
       </c>
       <c r="R52" t="n">
-        <v>6956698</v>
+        <v>6956930</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5884,6 +5889,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>16 av dom blommar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5910,48 +5920,57 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127301605</v>
+        <v>127301471</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582068</v>
+        <v>582122</v>
       </c>
       <c r="R53" t="n">
-        <v>6957026</v>
+        <v>6957012</v>
       </c>
       <c r="S53" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5981,6 +6000,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6007,45 +6031,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127300188</v>
+        <v>127299666</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582277</v>
+        <v>582264</v>
       </c>
       <c r="R54" t="n">
-        <v>6956837</v>
+        <v>6956698</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6104,52 +6132,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127302307</v>
+        <v>127301605</v>
       </c>
       <c r="B55" t="n">
-        <v>98385</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581865</v>
+        <v>582068</v>
       </c>
       <c r="R55" t="n">
-        <v>6956984</v>
+        <v>6957026</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6205,49 +6229,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127300633</v>
+        <v>127300188</v>
       </c>
       <c r="B56" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582186</v>
+        <v>582277</v>
       </c>
       <c r="R56" t="n">
-        <v>6956930</v>
+        <v>6956837</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6280,11 +6300,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6311,42 +6326,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127301471</v>
+        <v>127302307</v>
       </c>
       <c r="B57" t="n">
-        <v>98468</v>
+        <v>98385</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6355,10 +6365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>582122</v>
+        <v>581865</v>
       </c>
       <c r="R57" t="n">
-        <v>6957012</v>
+        <v>6956984</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6391,11 +6401,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6422,45 +6427,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127302082</v>
+        <v>127299508</v>
       </c>
       <c r="B58" t="n">
-        <v>91368</v>
+        <v>97345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581890</v>
+        <v>582284</v>
       </c>
       <c r="R58" t="n">
-        <v>6957003</v>
+        <v>6956732</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,45 +6524,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127299508</v>
+        <v>127302082</v>
       </c>
       <c r="B59" t="n">
-        <v>97345</v>
+        <v>91368</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>582284</v>
+        <v>581890</v>
       </c>
       <c r="R59" t="n">
-        <v>6956732</v>
+        <v>6957003</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6819,7 +6824,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127302049</v>
+        <v>127299437</v>
       </c>
       <c r="B62" t="n">
         <v>57672</v>
@@ -6855,14 +6860,14 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581894</v>
+        <v>582322</v>
       </c>
       <c r="R62" t="n">
-        <v>6957012</v>
+        <v>6956708</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6899,7 +6904,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6926,7 +6931,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127302243</v>
+        <v>127302049</v>
       </c>
       <c r="B63" t="n">
         <v>57672</v>
@@ -6966,10 +6971,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581956</v>
+        <v>581894</v>
       </c>
       <c r="R63" t="n">
-        <v>6956930</v>
+        <v>6957012</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7006,7 +7011,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7033,7 +7038,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127299437</v>
+        <v>127302243</v>
       </c>
       <c r="B64" t="n">
         <v>57672</v>
@@ -7069,14 +7074,14 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582322</v>
+        <v>581956</v>
       </c>
       <c r="R64" t="n">
-        <v>6956708</v>
+        <v>6956930</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7113,7 +7118,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7140,10 +7145,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127302544</v>
+        <v>127300173</v>
       </c>
       <c r="B65" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7151,34 +7156,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581837</v>
+        <v>582260</v>
       </c>
       <c r="R65" t="n">
-        <v>6957037</v>
+        <v>6956842</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7211,6 +7221,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7237,10 +7252,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127302060</v>
+        <v>127300974</v>
       </c>
       <c r="B66" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7248,34 +7263,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581894</v>
+        <v>582172</v>
       </c>
       <c r="R66" t="n">
-        <v>6957012</v>
+        <v>6956985</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7308,6 +7328,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7334,10 +7359,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127300173</v>
+        <v>127302544</v>
       </c>
       <c r="B67" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7345,39 +7370,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>582260</v>
+        <v>581837</v>
       </c>
       <c r="R67" t="n">
-        <v>6956842</v>
+        <v>6957037</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7410,11 +7430,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7441,10 +7456,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127300974</v>
+        <v>127302060</v>
       </c>
       <c r="B68" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7452,39 +7467,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>582172</v>
+        <v>581894</v>
       </c>
       <c r="R68" t="n">
-        <v>6956985</v>
+        <v>6957012</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7517,11 +7527,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -986,50 +986,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127301930</v>
+        <v>127299551</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581958</v>
+        <v>582275</v>
       </c>
       <c r="R5" t="n">
-        <v>6957039</v>
+        <v>6956695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1061,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1087,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127302215</v>
+        <v>127301930</v>
       </c>
       <c r="B6" t="n">
         <v>57672</v>
@@ -1133,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581908</v>
+        <v>581958</v>
       </c>
       <c r="R6" t="n">
-        <v>6956967</v>
+        <v>6957039</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,49 +1194,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299551</v>
+        <v>127302215</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582275</v>
+        <v>581908</v>
       </c>
       <c r="R7" t="n">
-        <v>6956695</v>
+        <v>6956967</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,45 +1301,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299890</v>
+        <v>127300097</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582226</v>
+        <v>582206</v>
       </c>
       <c r="R8" t="n">
-        <v>6956692</v>
+        <v>6956758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,38 +1402,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299838</v>
+        <v>127300854</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1438,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582206</v>
+        <v>582162</v>
       </c>
       <c r="R9" t="n">
-        <v>6956758</v>
+        <v>6956952</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,7 +1486,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,37 +1513,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127300097</v>
+        <v>127299838</v>
       </c>
       <c r="B10" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1580,6 +1589,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,54 +1620,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127300854</v>
+        <v>127299890</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582162</v>
+        <v>582226</v>
       </c>
       <c r="R11" t="n">
-        <v>6956952</v>
+        <v>6956692</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,11 +1691,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kan gömma sig mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1717,50 +1717,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127303073</v>
+        <v>127299754</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>98386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581907</v>
+        <v>582249</v>
       </c>
       <c r="R12" t="n">
-        <v>6957060</v>
+        <v>6956701</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,11 +1788,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,7 +1814,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127303143</v>
+        <v>127303073</v>
       </c>
       <c r="B13" t="n">
         <v>57672</v>
@@ -1855,7 +1845,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1864,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581903</v>
+        <v>581907</v>
       </c>
       <c r="R13" t="n">
-        <v>6957081</v>
+        <v>6957060</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1894,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1931,45 +1921,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299754</v>
+        <v>127303143</v>
       </c>
       <c r="B14" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582249</v>
+        <v>581903</v>
       </c>
       <c r="R14" t="n">
-        <v>6956701</v>
+        <v>6957081</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,6 +1997,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall både äldre och färska spår!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,7 +2031,7 @@
         <v>127302377</v>
       </c>
       <c r="B15" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,10 +2125,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127301182</v>
+        <v>127302258</v>
       </c>
       <c r="B16" t="n">
-        <v>91315</v>
+        <v>98386</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2136,21 +2136,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582156</v>
+        <v>581887</v>
       </c>
       <c r="R16" t="n">
-        <v>6957038</v>
+        <v>6956944</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2222,50 +2222,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127301633</v>
+        <v>127301182</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>91316</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582057</v>
+        <v>582156</v>
       </c>
       <c r="R17" t="n">
-        <v>6957055</v>
+        <v>6957038</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,11 +2293,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2329,7 +2319,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127301388</v>
+        <v>127301633</v>
       </c>
       <c r="B18" t="n">
         <v>57672</v>
@@ -2369,10 +2359,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582136</v>
+        <v>582057</v>
       </c>
       <c r="R18" t="n">
-        <v>6957002</v>
+        <v>6957055</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2399,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2436,45 +2426,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127302258</v>
+        <v>127301388</v>
       </c>
       <c r="B19" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581887</v>
+        <v>582136</v>
       </c>
       <c r="R19" t="n">
-        <v>6956944</v>
+        <v>6957002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2507,6 +2502,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127301650</v>
+        <v>127300032</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>91351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,42 +2544,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582068</v>
+        <v>582219</v>
       </c>
       <c r="R20" t="n">
-        <v>6957026</v>
+        <v>6956755</v>
       </c>
       <c r="S20" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2609,11 +2604,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2640,7 +2630,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127300573</v>
+        <v>127301650</v>
       </c>
       <c r="B21" t="n">
         <v>57672</v>
@@ -2676,17 +2666,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582225</v>
+        <v>582068</v>
       </c>
       <c r="R21" t="n">
-        <v>6956940</v>
+        <v>6957026</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,7 +2710,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2747,10 +2737,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127300032</v>
+        <v>127300573</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,34 +2748,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582219</v>
+        <v>582225</v>
       </c>
       <c r="R22" t="n">
-        <v>6956755</v>
+        <v>6956940</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,6 +2813,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2844,32 +2844,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127302739</v>
+        <v>127302871</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>97352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2883,10 +2883,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581843</v>
+        <v>581866</v>
       </c>
       <c r="R23" t="n">
-        <v>6957061</v>
+        <v>6957054</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2945,10 +2945,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127302871</v>
+        <v>127302141</v>
       </c>
       <c r="B24" t="n">
-        <v>97351</v>
+        <v>97346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,16 +2956,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2973,21 +2973,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581866</v>
+        <v>581925</v>
       </c>
       <c r="R24" t="n">
-        <v>6957054</v>
+        <v>6957009</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,45 +3042,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127302141</v>
+        <v>127302739</v>
       </c>
       <c r="B25" t="n">
-        <v>97345</v>
+        <v>98469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581925</v>
+        <v>581843</v>
       </c>
       <c r="R25" t="n">
-        <v>6957009</v>
+        <v>6957061</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,49 +3143,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127300270</v>
+        <v>127300070</v>
       </c>
       <c r="B26" t="n">
-        <v>98468</v>
+        <v>91351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582284</v>
+        <v>582196</v>
       </c>
       <c r="R26" t="n">
-        <v>6956848</v>
+        <v>6956710</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3218,6 +3214,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3244,49 +3245,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127300382</v>
+        <v>127300730</v>
       </c>
       <c r="B27" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582237</v>
+        <v>582186</v>
       </c>
       <c r="R27" t="n">
-        <v>6956894</v>
+        <v>6956930</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3319,6 +3316,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3345,45 +3347,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127300070</v>
+        <v>127302555</v>
       </c>
       <c r="B28" t="n">
-        <v>91350</v>
+        <v>105507</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582196</v>
+        <v>581837</v>
       </c>
       <c r="R28" t="n">
-        <v>6956710</v>
+        <v>6957037</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,11 +3418,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ullticka på 2 lågor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3447,45 +3444,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127300730</v>
+        <v>127300270</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582186</v>
+        <v>582284</v>
       </c>
       <c r="R29" t="n">
-        <v>6956930</v>
+        <v>6956848</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,11 +3519,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3549,45 +3545,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127302555</v>
+        <v>127300382</v>
       </c>
       <c r="B30" t="n">
-        <v>105506</v>
+        <v>98469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581837</v>
+        <v>582237</v>
       </c>
       <c r="R30" t="n">
-        <v>6957037</v>
+        <v>6956894</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3649,7 +3649,7 @@
         <v>127302334</v>
       </c>
       <c r="B31" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>127302173</v>
       </c>
       <c r="B32" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>127302336</v>
       </c>
       <c r="B33" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>127302187</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>127300230</v>
       </c>
       <c r="B37" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4358,50 +4358,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127301350</v>
+        <v>127302275</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>97346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582135</v>
+        <v>581923</v>
       </c>
       <c r="R38" t="n">
-        <v>6957030</v>
+        <v>6956949</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,11 +4429,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4465,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127301261</v>
+        <v>127302387</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>91647</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4476,39 +4466,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582156</v>
+        <v>581850</v>
       </c>
       <c r="R39" t="n">
-        <v>6957038</v>
+        <v>6957027</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4541,11 +4526,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4572,10 +4552,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127302387</v>
+        <v>127300073</v>
       </c>
       <c r="B40" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4603,14 +4583,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581850</v>
+        <v>582196</v>
       </c>
       <c r="R40" t="n">
-        <v>6957027</v>
+        <v>6956710</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4669,10 +4649,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127300073</v>
+        <v>127301350</v>
       </c>
       <c r="B41" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4680,34 +4660,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582196</v>
+        <v>582135</v>
       </c>
       <c r="R41" t="n">
-        <v>6956710</v>
+        <v>6957030</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4740,6 +4725,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4766,45 +4756,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127302275</v>
+        <v>127301261</v>
       </c>
       <c r="B42" t="n">
-        <v>97345</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581923</v>
+        <v>582156</v>
       </c>
       <c r="R42" t="n">
-        <v>6956949</v>
+        <v>6957038</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4837,6 +4832,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4863,10 +4863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127300324</v>
+        <v>127299697</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582237</v>
+        <v>582264</v>
       </c>
       <c r="R43" t="n">
-        <v>6956894</v>
+        <v>6956698</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4934,11 +4934,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4965,7 +4960,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127302594</v>
+        <v>127300324</v>
       </c>
       <c r="B44" t="n">
         <v>57672</v>
@@ -4994,21 +4989,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581831</v>
+        <v>582237</v>
       </c>
       <c r="R44" t="n">
-        <v>6957049</v>
+        <v>6956894</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5045,7 +5035,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre exemplar av tretåig hackspett ( ringhack av tretåig hackspett på Tall)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5072,10 +5062,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127299697</v>
+        <v>127302594</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,34 +5073,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582264</v>
+        <v>581831</v>
       </c>
       <c r="R45" t="n">
-        <v>6956698</v>
+        <v>6957049</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5143,6 +5138,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5169,50 +5169,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127301651</v>
+        <v>127300916</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>91805</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582042</v>
+        <v>582172</v>
       </c>
       <c r="R46" t="n">
-        <v>6957055</v>
+        <v>6956985</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5245,11 +5240,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5276,42 +5266,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127302103</v>
+        <v>127301651</v>
       </c>
       <c r="B47" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5320,10 +5306,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581922</v>
+        <v>582042</v>
       </c>
       <c r="R47" t="n">
-        <v>6957019</v>
+        <v>6957055</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5360,7 +5346,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5390,7 +5376,7 @@
         <v>127303284</v>
       </c>
       <c r="B48" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5498,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127300916</v>
+        <v>127302103</v>
       </c>
       <c r="B49" t="n">
-        <v>91804</v>
+        <v>98469</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5509,34 +5495,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>582172</v>
+        <v>581922</v>
       </c>
       <c r="R49" t="n">
-        <v>6956985</v>
+        <v>6957019</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,6 +5564,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>1 blommar kan finnas mer gömda i blåbärsriset</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5809,57 +5809,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127300776</v>
+        <v>127301605</v>
       </c>
       <c r="B52" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>582186</v>
+        <v>582068</v>
       </c>
       <c r="R52" t="n">
-        <v>6956930</v>
+        <v>6957026</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5889,11 +5880,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>16 av dom blommar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5920,54 +5906,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127301471</v>
+        <v>127300188</v>
       </c>
       <c r="B53" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582122</v>
+        <v>582277</v>
       </c>
       <c r="R53" t="n">
-        <v>6957012</v>
+        <v>6956837</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6000,11 +5977,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6034,7 +6006,7 @@
         <v>127299666</v>
       </c>
       <c r="B54" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6132,48 +6104,52 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127301605</v>
+        <v>127302307</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>98386</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582068</v>
+        <v>581865</v>
       </c>
       <c r="R55" t="n">
-        <v>6957026</v>
+        <v>6956984</v>
       </c>
       <c r="S55" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6229,45 +6205,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127300188</v>
+        <v>127300633</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582277</v>
+        <v>582186</v>
       </c>
       <c r="R56" t="n">
-        <v>6956837</v>
+        <v>6956930</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6300,6 +6280,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Mer kan förekomma i blåbärsriset</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6326,37 +6311,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127302307</v>
+        <v>127301471</v>
       </c>
       <c r="B57" t="n">
-        <v>98385</v>
+        <v>98469</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6365,10 +6355,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581865</v>
+        <v>582122</v>
       </c>
       <c r="R57" t="n">
-        <v>6956984</v>
+        <v>6957012</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6401,6 +6391,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>1 blommar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6430,7 +6425,7 @@
         <v>127299508</v>
       </c>
       <c r="B58" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6527,7 +6522,7 @@
         <v>127302082</v>
       </c>
       <c r="B59" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6624,7 +6619,7 @@
         <v>127302257</v>
       </c>
       <c r="B60" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6727,45 +6722,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127299731</v>
+        <v>127299437</v>
       </c>
       <c r="B61" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>582264</v>
+        <v>582322</v>
       </c>
       <c r="R61" t="n">
-        <v>6956698</v>
+        <v>6956708</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6798,6 +6798,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6824,50 +6829,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127299437</v>
+        <v>127299731</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>98386</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>582322</v>
+        <v>582264</v>
       </c>
       <c r="R62" t="n">
-        <v>6956708</v>
+        <v>6956698</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6900,11 +6900,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7145,10 +7140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127300173</v>
+        <v>127302060</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>91647</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7156,39 +7151,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582260</v>
+        <v>581894</v>
       </c>
       <c r="R65" t="n">
-        <v>6956842</v>
+        <v>6957012</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7221,11 +7211,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7252,10 +7237,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127300974</v>
+        <v>127302544</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>91351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7263,39 +7248,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>582172</v>
+        <v>581837</v>
       </c>
       <c r="R66" t="n">
-        <v>6956985</v>
+        <v>6957037</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7328,11 +7308,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7359,10 +7334,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127302544</v>
+        <v>127300173</v>
       </c>
       <c r="B67" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7370,34 +7345,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bjärtbergsslåtten, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581837</v>
+        <v>582260</v>
       </c>
       <c r="R67" t="n">
-        <v>6957037</v>
+        <v>6956842</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7430,6 +7410,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7456,10 +7441,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127302060</v>
+        <v>127300974</v>
       </c>
       <c r="B68" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7467,34 +7452,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bjärtbergsslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581894</v>
+        <v>582172</v>
       </c>
       <c r="R68" t="n">
-        <v>6957012</v>
+        <v>6956985</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7527,6 +7517,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7556,7 +7551,7 @@
         <v>127728746</v>
       </c>
       <c r="B69" t="n">
-        <v>91180</v>
+        <v>91181</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 34221-2025 artfynd.xlsx
+++ b/artfynd/A 34221-2025 artfynd.xlsx
@@ -7551,7 +7551,7 @@
         <v>127728746</v>
       </c>
       <c r="B69" t="n">
-        <v>91181</v>
+        <v>91182</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
